--- a/activitereelford-2026.xlsx
+++ b/activitereelford-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542FBBE8-0032-492C-ABFF-5DD4EE2964D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5991DB-9EEF-47EB-AA12-59E07C899DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3955" uniqueCount="627">
   <si>
     <t>N°commande</t>
   </si>
@@ -1531,6 +1531,393 @@
   </si>
   <si>
     <t xml:space="preserve">26406324                 </t>
+  </si>
+  <si>
+    <t>26403176</t>
+  </si>
+  <si>
+    <t>26603448</t>
+  </si>
+  <si>
+    <t>26403177</t>
+  </si>
+  <si>
+    <t>26603449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GUILLAUME G          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85694 22                 </t>
+  </si>
+  <si>
+    <t>85694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DILUANT HS CLEAR COAT 1L                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85822 11                 </t>
+  </si>
+  <si>
+    <t>85822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT SELF GUIDE EVO GRIS 85815 + 85816                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85815 22                 </t>
+  </si>
+  <si>
+    <t>85815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELF GUIDE EVO GRIS 4:1                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85816 22                 </t>
+  </si>
+  <si>
+    <t>85816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DURCISSEUR SELF GUIDE EVO                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86190 34                 </t>
+  </si>
+  <si>
+    <t>86190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PISTOLET ANTI GRAVILLON                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86191 34                 </t>
+  </si>
+  <si>
+    <t>86191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUSES REMPLACEMENT PISTOLET KCG                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87723 22                 </t>
+  </si>
+  <si>
+    <t>87723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTI GRAVILLON TOUGHCOAT BLANC BOUT 1L                       </t>
+  </si>
+  <si>
+    <t>26403222</t>
+  </si>
+  <si>
+    <t>26603513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE STOCK MAG HEROUVILLE </t>
+  </si>
+  <si>
+    <t>26403409</t>
+  </si>
+  <si>
+    <t>26603685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34501 22                 </t>
+  </si>
+  <si>
+    <t>34501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUICK SEAL BLANC 290 ML                                      </t>
+  </si>
+  <si>
+    <t>CDE HEROUVILLE CARROSSERI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86885 00                 </t>
+  </si>
+  <si>
+    <t>86885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUSE PLATE LARGE (10) M15x1,5 10/PK                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1294 33                 </t>
+  </si>
+  <si>
+    <t>A1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISQUES DURALITE 150MM P240                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34502 22                 </t>
+  </si>
+  <si>
+    <t>34502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUICK SEAL GRIS 290 ML                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50180 10                 </t>
+  </si>
+  <si>
+    <t>50180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRY LUBE - LUBRIFIANT A SEC 400 ML                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86354 22                 </t>
+  </si>
+  <si>
+    <t>86354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPPER WELDPRIMER SOUDURE                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86720 10                 </t>
+  </si>
+  <si>
+    <t>86720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTFE LUBRICANT ES AER 500 ML (BUSE EASY STRAW)               </t>
+  </si>
+  <si>
+    <t>26403907</t>
+  </si>
+  <si>
+    <t>26604157</t>
+  </si>
+  <si>
+    <t>26403951</t>
+  </si>
+  <si>
+    <t>26604238</t>
+  </si>
+  <si>
+    <t>26403992</t>
+  </si>
+  <si>
+    <t>26604241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE FORD BERNAY          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7191 10                 </t>
+  </si>
+  <si>
+    <t>C7191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCREEN WASH ETE 1:100 - B TO C CAR CARE - 250ML              </t>
+  </si>
+  <si>
+    <t>26404057</t>
+  </si>
+  <si>
+    <t>26604285</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CDE RS AUTOMOBILES BERNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87008 00                 </t>
+  </si>
+  <si>
+    <t>87008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORET TUNGSTENE                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1351 33                 </t>
+  </si>
+  <si>
+    <t>A1351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERFACE FINECUT MEDIUM 5MM 150 MM                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85119 22                 </t>
+  </si>
+  <si>
+    <t>85119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROSEAL 303 JOINT PULVERISABLE NOIR 290ML                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85988 10                 </t>
+  </si>
+  <si>
+    <t>85988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BODY FINISH PAINT VERT 500ML PEINTURE ACRYLIQUE MONOCOMPO.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85989 10                 </t>
+  </si>
+  <si>
+    <t>85989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BODY FINISH PAINT BEIGE 500ML PEINTURE ACRYLIQUE MONOCOMPO.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86504 22                 </t>
+  </si>
+  <si>
+    <t>86504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETTOYANT PEINTURE POUR MAINS PAINT HAND CLEANER 2           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86547 10                 </t>
+  </si>
+  <si>
+    <t>86547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPF FOAM CLEANER 500ML                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86936 22                 </t>
+  </si>
+  <si>
+    <t>86936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUICK FREEZE - AER 400 ML                                    </t>
+  </si>
+  <si>
+    <t>26404261</t>
+  </si>
+  <si>
+    <t>26604597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85403 10                 </t>
+  </si>
+  <si>
+    <t>85403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLISH NANO LONGUE DUREE 500ML                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE BARBE            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1354 33                 </t>
+  </si>
+  <si>
+    <t>A1354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERFACE FINECUT HIGH 77MM                                  </t>
+  </si>
+  <si>
+    <t>26404488</t>
+  </si>
+  <si>
+    <t>26604788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86596 22                 </t>
+  </si>
+  <si>
+    <t>86596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UREFIX 60 CART 310 ML                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE STOCK ET GGE TRAJIN  </t>
+  </si>
+  <si>
+    <t>26404680</t>
+  </si>
+  <si>
+    <t>26605041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGE GOULAIN              </t>
+  </si>
+  <si>
+    <t>26404686</t>
+  </si>
+  <si>
+    <t>26605047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0209 00                 </t>
+  </si>
+  <si>
+    <t>E0209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDE A PIANO CARREE 22M                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGE MICHEL MONTFORT      </t>
+  </si>
+  <si>
+    <t>26404914</t>
+  </si>
+  <si>
+    <t>26605229</t>
+  </si>
+  <si>
+    <t>26405252</t>
+  </si>
+  <si>
+    <t>26605628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE BL AUTO BEAUMONTEL   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86176 90                 </t>
+  </si>
+  <si>
+    <t>86176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT SELF GUIDE EVO BLANC 86171 + 85816                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86171 22                 </t>
+  </si>
+  <si>
+    <t>86171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELF GUIDE EVO APPRET BICOMPOSANT BLANC                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87058 22                 </t>
+  </si>
+  <si>
+    <t>87058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAPHENE PRIMER GRIS AER 500ML GRIS CLAIR                    </t>
+  </si>
+  <si>
+    <t>Février</t>
   </si>
 </sst>
 </file>
@@ -1906,7 +2293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W162"/>
+  <dimension ref="A1:W219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -13435,6 +13822,4053 @@
         <v>334</v>
       </c>
     </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>498</v>
+      </c>
+      <c r="B163" t="s">
+        <v>499</v>
+      </c>
+      <c r="C163" t="s">
+        <v>34</v>
+      </c>
+      <c r="D163" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" t="s">
+        <v>36</v>
+      </c>
+      <c r="F163" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G163" t="s">
+        <v>105</v>
+      </c>
+      <c r="H163" t="s">
+        <v>106</v>
+      </c>
+      <c r="I163" t="s">
+        <v>107</v>
+      </c>
+      <c r="J163">
+        <v>3</v>
+      </c>
+      <c r="K163">
+        <v>13.87</v>
+      </c>
+      <c r="L163">
+        <v>41.61</v>
+      </c>
+      <c r="M163" t="s">
+        <v>22</v>
+      </c>
+      <c r="N163" t="s">
+        <v>23</v>
+      </c>
+      <c r="O163" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P163" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>24</v>
+      </c>
+      <c r="R163" t="s">
+        <v>41</v>
+      </c>
+      <c r="S163" t="s">
+        <v>25</v>
+      </c>
+      <c r="T163" t="s">
+        <v>42</v>
+      </c>
+      <c r="U163" t="s">
+        <v>43</v>
+      </c>
+      <c r="V163" t="s">
+        <v>44</v>
+      </c>
+      <c r="W163" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>500</v>
+      </c>
+      <c r="B164" t="s">
+        <v>501</v>
+      </c>
+      <c r="C164" t="s">
+        <v>34</v>
+      </c>
+      <c r="D164" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" t="s">
+        <v>36</v>
+      </c>
+      <c r="F164" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G164" t="s">
+        <v>89</v>
+      </c>
+      <c r="H164" t="s">
+        <v>90</v>
+      </c>
+      <c r="I164" t="s">
+        <v>91</v>
+      </c>
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>14.85</v>
+      </c>
+      <c r="L164">
+        <v>14.85</v>
+      </c>
+      <c r="M164" t="s">
+        <v>22</v>
+      </c>
+      <c r="N164" t="s">
+        <v>23</v>
+      </c>
+      <c r="O164" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P164" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>24</v>
+      </c>
+      <c r="R164" t="s">
+        <v>41</v>
+      </c>
+      <c r="S164" t="s">
+        <v>25</v>
+      </c>
+      <c r="T164" t="s">
+        <v>42</v>
+      </c>
+      <c r="U164" t="s">
+        <v>43</v>
+      </c>
+      <c r="V164" t="s">
+        <v>44</v>
+      </c>
+      <c r="W164" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>500</v>
+      </c>
+      <c r="B165" t="s">
+        <v>501</v>
+      </c>
+      <c r="C165" t="s">
+        <v>34</v>
+      </c>
+      <c r="D165" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" t="s">
+        <v>36</v>
+      </c>
+      <c r="F165" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G165" t="s">
+        <v>503</v>
+      </c>
+      <c r="H165" t="s">
+        <v>504</v>
+      </c>
+      <c r="I165" t="s">
+        <v>505</v>
+      </c>
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="K165">
+        <v>13.06</v>
+      </c>
+      <c r="L165">
+        <v>13.06</v>
+      </c>
+      <c r="M165" t="s">
+        <v>22</v>
+      </c>
+      <c r="N165" t="s">
+        <v>23</v>
+      </c>
+      <c r="O165" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P165" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>24</v>
+      </c>
+      <c r="R165" t="s">
+        <v>41</v>
+      </c>
+      <c r="S165" t="s">
+        <v>25</v>
+      </c>
+      <c r="T165" t="s">
+        <v>42</v>
+      </c>
+      <c r="U165" t="s">
+        <v>43</v>
+      </c>
+      <c r="V165" t="s">
+        <v>44</v>
+      </c>
+      <c r="W165" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>500</v>
+      </c>
+      <c r="B166" t="s">
+        <v>501</v>
+      </c>
+      <c r="C166" t="s">
+        <v>34</v>
+      </c>
+      <c r="D166" t="s">
+        <v>35</v>
+      </c>
+      <c r="E166" t="s">
+        <v>36</v>
+      </c>
+      <c r="F166" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G166" t="s">
+        <v>506</v>
+      </c>
+      <c r="H166" t="s">
+        <v>507</v>
+      </c>
+      <c r="I166" t="s">
+        <v>508</v>
+      </c>
+      <c r="J166">
+        <v>1</v>
+      </c>
+      <c r="K166">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="L166">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="M166" t="s">
+        <v>22</v>
+      </c>
+      <c r="N166" t="s">
+        <v>23</v>
+      </c>
+      <c r="O166" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P166" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>24</v>
+      </c>
+      <c r="R166" t="s">
+        <v>41</v>
+      </c>
+      <c r="S166" t="s">
+        <v>25</v>
+      </c>
+      <c r="T166" t="s">
+        <v>42</v>
+      </c>
+      <c r="U166" t="s">
+        <v>43</v>
+      </c>
+      <c r="V166" t="s">
+        <v>44</v>
+      </c>
+      <c r="W166" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>500</v>
+      </c>
+      <c r="B167" t="s">
+        <v>501</v>
+      </c>
+      <c r="C167" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" t="s">
+        <v>36</v>
+      </c>
+      <c r="F167" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G167" t="s">
+        <v>509</v>
+      </c>
+      <c r="H167" t="s">
+        <v>510</v>
+      </c>
+      <c r="I167" t="s">
+        <v>511</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>64.89</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167" t="s">
+        <v>22</v>
+      </c>
+      <c r="N167" t="s">
+        <v>23</v>
+      </c>
+      <c r="O167" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P167" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>24</v>
+      </c>
+      <c r="R167" t="s">
+        <v>41</v>
+      </c>
+      <c r="S167" t="s">
+        <v>25</v>
+      </c>
+      <c r="T167" t="s">
+        <v>42</v>
+      </c>
+      <c r="U167" t="s">
+        <v>43</v>
+      </c>
+      <c r="V167" t="s">
+        <v>44</v>
+      </c>
+      <c r="W167" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>500</v>
+      </c>
+      <c r="B168" t="s">
+        <v>501</v>
+      </c>
+      <c r="C168" t="s">
+        <v>34</v>
+      </c>
+      <c r="D168" t="s">
+        <v>35</v>
+      </c>
+      <c r="E168" t="s">
+        <v>36</v>
+      </c>
+      <c r="F168" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G168" t="s">
+        <v>512</v>
+      </c>
+      <c r="H168" t="s">
+        <v>513</v>
+      </c>
+      <c r="I168" t="s">
+        <v>514</v>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+      <c r="K168">
+        <v>15.99</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168" t="s">
+        <v>22</v>
+      </c>
+      <c r="N168" t="s">
+        <v>23</v>
+      </c>
+      <c r="O168" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P168" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>24</v>
+      </c>
+      <c r="R168" t="s">
+        <v>41</v>
+      </c>
+      <c r="S168" t="s">
+        <v>25</v>
+      </c>
+      <c r="T168" t="s">
+        <v>42</v>
+      </c>
+      <c r="U168" t="s">
+        <v>43</v>
+      </c>
+      <c r="V168" t="s">
+        <v>44</v>
+      </c>
+      <c r="W168" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>500</v>
+      </c>
+      <c r="B169" t="s">
+        <v>501</v>
+      </c>
+      <c r="C169" t="s">
+        <v>34</v>
+      </c>
+      <c r="D169" t="s">
+        <v>35</v>
+      </c>
+      <c r="E169" t="s">
+        <v>36</v>
+      </c>
+      <c r="F169" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G169" t="s">
+        <v>515</v>
+      </c>
+      <c r="H169" t="s">
+        <v>516</v>
+      </c>
+      <c r="I169" t="s">
+        <v>517</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>15.04</v>
+      </c>
+      <c r="L169">
+        <v>15.04</v>
+      </c>
+      <c r="M169" t="s">
+        <v>22</v>
+      </c>
+      <c r="N169" t="s">
+        <v>23</v>
+      </c>
+      <c r="O169" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P169" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>24</v>
+      </c>
+      <c r="R169" t="s">
+        <v>41</v>
+      </c>
+      <c r="S169" t="s">
+        <v>25</v>
+      </c>
+      <c r="T169" t="s">
+        <v>42</v>
+      </c>
+      <c r="U169" t="s">
+        <v>43</v>
+      </c>
+      <c r="V169" t="s">
+        <v>44</v>
+      </c>
+      <c r="W169" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>500</v>
+      </c>
+      <c r="B170" t="s">
+        <v>501</v>
+      </c>
+      <c r="C170" t="s">
+        <v>34</v>
+      </c>
+      <c r="D170" t="s">
+        <v>35</v>
+      </c>
+      <c r="E170" t="s">
+        <v>36</v>
+      </c>
+      <c r="F170" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G170" t="s">
+        <v>518</v>
+      </c>
+      <c r="H170" t="s">
+        <v>519</v>
+      </c>
+      <c r="I170" t="s">
+        <v>520</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>5.14</v>
+      </c>
+      <c r="L170">
+        <v>5.14</v>
+      </c>
+      <c r="M170" t="s">
+        <v>22</v>
+      </c>
+      <c r="N170" t="s">
+        <v>23</v>
+      </c>
+      <c r="O170" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P170" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>24</v>
+      </c>
+      <c r="R170" t="s">
+        <v>41</v>
+      </c>
+      <c r="S170" t="s">
+        <v>25</v>
+      </c>
+      <c r="T170" t="s">
+        <v>42</v>
+      </c>
+      <c r="U170" t="s">
+        <v>43</v>
+      </c>
+      <c r="V170" t="s">
+        <v>44</v>
+      </c>
+      <c r="W170" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>500</v>
+      </c>
+      <c r="B171" t="s">
+        <v>501</v>
+      </c>
+      <c r="C171" t="s">
+        <v>34</v>
+      </c>
+      <c r="D171" t="s">
+        <v>35</v>
+      </c>
+      <c r="E171" t="s">
+        <v>36</v>
+      </c>
+      <c r="F171" s="1">
+        <v>46055</v>
+      </c>
+      <c r="G171" t="s">
+        <v>521</v>
+      </c>
+      <c r="H171" t="s">
+        <v>522</v>
+      </c>
+      <c r="I171" t="s">
+        <v>523</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>10.46</v>
+      </c>
+      <c r="L171">
+        <v>10.46</v>
+      </c>
+      <c r="M171" t="s">
+        <v>22</v>
+      </c>
+      <c r="N171" t="s">
+        <v>23</v>
+      </c>
+      <c r="O171" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P171" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>24</v>
+      </c>
+      <c r="R171" t="s">
+        <v>41</v>
+      </c>
+      <c r="S171" t="s">
+        <v>25</v>
+      </c>
+      <c r="T171" t="s">
+        <v>42</v>
+      </c>
+      <c r="U171" t="s">
+        <v>43</v>
+      </c>
+      <c r="V171" t="s">
+        <v>44</v>
+      </c>
+      <c r="W171" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>524</v>
+      </c>
+      <c r="B172" t="s">
+        <v>525</v>
+      </c>
+      <c r="C172" t="s">
+        <v>34</v>
+      </c>
+      <c r="D172" t="s">
+        <v>35</v>
+      </c>
+      <c r="E172" t="s">
+        <v>36</v>
+      </c>
+      <c r="F172" s="1">
+        <v>46056</v>
+      </c>
+      <c r="G172" t="s">
+        <v>287</v>
+      </c>
+      <c r="H172" t="s">
+        <v>288</v>
+      </c>
+      <c r="I172" t="s">
+        <v>289</v>
+      </c>
+      <c r="J172">
+        <v>12</v>
+      </c>
+      <c r="K172">
+        <v>10.8</v>
+      </c>
+      <c r="L172">
+        <v>129.6</v>
+      </c>
+      <c r="M172" t="s">
+        <v>22</v>
+      </c>
+      <c r="N172" t="s">
+        <v>23</v>
+      </c>
+      <c r="O172" s="1">
+        <v>46055</v>
+      </c>
+      <c r="P172" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>24</v>
+      </c>
+      <c r="R172" t="s">
+        <v>41</v>
+      </c>
+      <c r="S172" t="s">
+        <v>25</v>
+      </c>
+      <c r="T172" t="s">
+        <v>42</v>
+      </c>
+      <c r="U172" t="s">
+        <v>43</v>
+      </c>
+      <c r="V172" t="s">
+        <v>44</v>
+      </c>
+      <c r="W172" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>527</v>
+      </c>
+      <c r="B173" t="s">
+        <v>528</v>
+      </c>
+      <c r="C173" t="s">
+        <v>34</v>
+      </c>
+      <c r="D173" t="s">
+        <v>35</v>
+      </c>
+      <c r="E173" t="s">
+        <v>36</v>
+      </c>
+      <c r="F173" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G173" t="s">
+        <v>529</v>
+      </c>
+      <c r="H173" t="s">
+        <v>530</v>
+      </c>
+      <c r="I173" t="s">
+        <v>531</v>
+      </c>
+      <c r="J173">
+        <v>2</v>
+      </c>
+      <c r="K173">
+        <v>13.67</v>
+      </c>
+      <c r="L173">
+        <v>27.34</v>
+      </c>
+      <c r="M173" t="s">
+        <v>22</v>
+      </c>
+      <c r="N173" t="s">
+        <v>23</v>
+      </c>
+      <c r="O173" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P173" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>24</v>
+      </c>
+      <c r="R173" t="s">
+        <v>41</v>
+      </c>
+      <c r="S173" t="s">
+        <v>25</v>
+      </c>
+      <c r="T173" t="s">
+        <v>42</v>
+      </c>
+      <c r="U173" t="s">
+        <v>43</v>
+      </c>
+      <c r="V173" t="s">
+        <v>44</v>
+      </c>
+      <c r="W173" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>527</v>
+      </c>
+      <c r="B174" t="s">
+        <v>528</v>
+      </c>
+      <c r="C174" t="s">
+        <v>34</v>
+      </c>
+      <c r="D174" t="s">
+        <v>35</v>
+      </c>
+      <c r="E174" t="s">
+        <v>36</v>
+      </c>
+      <c r="F174" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G174" t="s">
+        <v>185</v>
+      </c>
+      <c r="H174" t="s">
+        <v>186</v>
+      </c>
+      <c r="I174" t="s">
+        <v>187</v>
+      </c>
+      <c r="J174">
+        <v>6</v>
+      </c>
+      <c r="K174">
+        <v>7.49</v>
+      </c>
+      <c r="L174">
+        <v>44.94</v>
+      </c>
+      <c r="M174" t="s">
+        <v>22</v>
+      </c>
+      <c r="N174" t="s">
+        <v>23</v>
+      </c>
+      <c r="O174" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P174" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>24</v>
+      </c>
+      <c r="R174" t="s">
+        <v>41</v>
+      </c>
+      <c r="S174" t="s">
+        <v>25</v>
+      </c>
+      <c r="T174" t="s">
+        <v>42</v>
+      </c>
+      <c r="U174" t="s">
+        <v>43</v>
+      </c>
+      <c r="V174" t="s">
+        <v>44</v>
+      </c>
+      <c r="W174" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>527</v>
+      </c>
+      <c r="B175" t="s">
+        <v>528</v>
+      </c>
+      <c r="C175" t="s">
+        <v>34</v>
+      </c>
+      <c r="D175" t="s">
+        <v>35</v>
+      </c>
+      <c r="E175" t="s">
+        <v>36</v>
+      </c>
+      <c r="F175" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G175" t="s">
+        <v>533</v>
+      </c>
+      <c r="H175" t="s">
+        <v>534</v>
+      </c>
+      <c r="I175" t="s">
+        <v>535</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>7.88</v>
+      </c>
+      <c r="L175">
+        <v>7.88</v>
+      </c>
+      <c r="M175" t="s">
+        <v>22</v>
+      </c>
+      <c r="N175" t="s">
+        <v>23</v>
+      </c>
+      <c r="O175" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P175" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>24</v>
+      </c>
+      <c r="R175" t="s">
+        <v>41</v>
+      </c>
+      <c r="S175" t="s">
+        <v>25</v>
+      </c>
+      <c r="T175" t="s">
+        <v>42</v>
+      </c>
+      <c r="U175" t="s">
+        <v>43</v>
+      </c>
+      <c r="V175" t="s">
+        <v>44</v>
+      </c>
+      <c r="W175" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>527</v>
+      </c>
+      <c r="B176" t="s">
+        <v>528</v>
+      </c>
+      <c r="C176" t="s">
+        <v>34</v>
+      </c>
+      <c r="D176" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176" t="s">
+        <v>36</v>
+      </c>
+      <c r="F176" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G176" t="s">
+        <v>26</v>
+      </c>
+      <c r="H176" t="s">
+        <v>27</v>
+      </c>
+      <c r="I176" t="s">
+        <v>28</v>
+      </c>
+      <c r="J176">
+        <v>24</v>
+      </c>
+      <c r="K176">
+        <v>3.14</v>
+      </c>
+      <c r="L176">
+        <v>75.36</v>
+      </c>
+      <c r="M176" t="s">
+        <v>22</v>
+      </c>
+      <c r="N176" t="s">
+        <v>23</v>
+      </c>
+      <c r="O176" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P176" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>24</v>
+      </c>
+      <c r="R176" t="s">
+        <v>41</v>
+      </c>
+      <c r="S176" t="s">
+        <v>25</v>
+      </c>
+      <c r="T176" t="s">
+        <v>42</v>
+      </c>
+      <c r="U176" t="s">
+        <v>43</v>
+      </c>
+      <c r="V176" t="s">
+        <v>44</v>
+      </c>
+      <c r="W176" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>527</v>
+      </c>
+      <c r="B177" t="s">
+        <v>528</v>
+      </c>
+      <c r="C177" t="s">
+        <v>34</v>
+      </c>
+      <c r="D177" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" t="s">
+        <v>36</v>
+      </c>
+      <c r="F177" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G177" t="s">
+        <v>227</v>
+      </c>
+      <c r="H177" t="s">
+        <v>228</v>
+      </c>
+      <c r="I177" t="s">
+        <v>229</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>16.09</v>
+      </c>
+      <c r="L177">
+        <v>16.09</v>
+      </c>
+      <c r="M177" t="s">
+        <v>22</v>
+      </c>
+      <c r="N177" t="s">
+        <v>23</v>
+      </c>
+      <c r="O177" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P177" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>24</v>
+      </c>
+      <c r="R177" t="s">
+        <v>41</v>
+      </c>
+      <c r="S177" t="s">
+        <v>25</v>
+      </c>
+      <c r="T177" t="s">
+        <v>42</v>
+      </c>
+      <c r="U177" t="s">
+        <v>43</v>
+      </c>
+      <c r="V177" t="s">
+        <v>44</v>
+      </c>
+      <c r="W177" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>527</v>
+      </c>
+      <c r="B178" t="s">
+        <v>528</v>
+      </c>
+      <c r="C178" t="s">
+        <v>34</v>
+      </c>
+      <c r="D178" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" t="s">
+        <v>36</v>
+      </c>
+      <c r="F178" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G178" t="s">
+        <v>536</v>
+      </c>
+      <c r="H178" t="s">
+        <v>537</v>
+      </c>
+      <c r="I178" t="s">
+        <v>538</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178">
+        <v>23.65</v>
+      </c>
+      <c r="L178">
+        <v>23.65</v>
+      </c>
+      <c r="M178" t="s">
+        <v>22</v>
+      </c>
+      <c r="N178" t="s">
+        <v>23</v>
+      </c>
+      <c r="O178" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P178" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>24</v>
+      </c>
+      <c r="R178" t="s">
+        <v>41</v>
+      </c>
+      <c r="S178" t="s">
+        <v>25</v>
+      </c>
+      <c r="T178" t="s">
+        <v>42</v>
+      </c>
+      <c r="U178" t="s">
+        <v>43</v>
+      </c>
+      <c r="V178" t="s">
+        <v>44</v>
+      </c>
+      <c r="W178" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>527</v>
+      </c>
+      <c r="B179" t="s">
+        <v>528</v>
+      </c>
+      <c r="C179" t="s">
+        <v>34</v>
+      </c>
+      <c r="D179" t="s">
+        <v>35</v>
+      </c>
+      <c r="E179" t="s">
+        <v>36</v>
+      </c>
+      <c r="F179" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G179" t="s">
+        <v>539</v>
+      </c>
+      <c r="H179" t="s">
+        <v>540</v>
+      </c>
+      <c r="I179" t="s">
+        <v>541</v>
+      </c>
+      <c r="J179">
+        <v>2</v>
+      </c>
+      <c r="K179">
+        <v>13.67</v>
+      </c>
+      <c r="L179">
+        <v>27.34</v>
+      </c>
+      <c r="M179" t="s">
+        <v>22</v>
+      </c>
+      <c r="N179" t="s">
+        <v>23</v>
+      </c>
+      <c r="O179" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P179" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>24</v>
+      </c>
+      <c r="R179" t="s">
+        <v>41</v>
+      </c>
+      <c r="S179" t="s">
+        <v>25</v>
+      </c>
+      <c r="T179" t="s">
+        <v>42</v>
+      </c>
+      <c r="U179" t="s">
+        <v>43</v>
+      </c>
+      <c r="V179" t="s">
+        <v>44</v>
+      </c>
+      <c r="W179" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>527</v>
+      </c>
+      <c r="B180" t="s">
+        <v>528</v>
+      </c>
+      <c r="C180" t="s">
+        <v>34</v>
+      </c>
+      <c r="D180" t="s">
+        <v>35</v>
+      </c>
+      <c r="E180" t="s">
+        <v>36</v>
+      </c>
+      <c r="F180" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G180" t="s">
+        <v>542</v>
+      </c>
+      <c r="H180" t="s">
+        <v>543</v>
+      </c>
+      <c r="I180" t="s">
+        <v>544</v>
+      </c>
+      <c r="J180">
+        <v>3</v>
+      </c>
+      <c r="K180">
+        <v>15.96</v>
+      </c>
+      <c r="L180">
+        <v>47.88</v>
+      </c>
+      <c r="M180" t="s">
+        <v>22</v>
+      </c>
+      <c r="N180" t="s">
+        <v>23</v>
+      </c>
+      <c r="O180" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P180" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>24</v>
+      </c>
+      <c r="R180" t="s">
+        <v>41</v>
+      </c>
+      <c r="S180" t="s">
+        <v>25</v>
+      </c>
+      <c r="T180" t="s">
+        <v>42</v>
+      </c>
+      <c r="U180" t="s">
+        <v>43</v>
+      </c>
+      <c r="V180" t="s">
+        <v>44</v>
+      </c>
+      <c r="W180" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>527</v>
+      </c>
+      <c r="B181" t="s">
+        <v>528</v>
+      </c>
+      <c r="C181" t="s">
+        <v>34</v>
+      </c>
+      <c r="D181" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181" t="s">
+        <v>36</v>
+      </c>
+      <c r="F181" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G181" t="s">
+        <v>96</v>
+      </c>
+      <c r="H181" t="s">
+        <v>97</v>
+      </c>
+      <c r="I181" t="s">
+        <v>98</v>
+      </c>
+      <c r="J181">
+        <v>6</v>
+      </c>
+      <c r="K181">
+        <v>11.64</v>
+      </c>
+      <c r="L181">
+        <v>69.84</v>
+      </c>
+      <c r="M181" t="s">
+        <v>22</v>
+      </c>
+      <c r="N181" t="s">
+        <v>23</v>
+      </c>
+      <c r="O181" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P181" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>24</v>
+      </c>
+      <c r="R181" t="s">
+        <v>41</v>
+      </c>
+      <c r="S181" t="s">
+        <v>25</v>
+      </c>
+      <c r="T181" t="s">
+        <v>42</v>
+      </c>
+      <c r="U181" t="s">
+        <v>43</v>
+      </c>
+      <c r="V181" t="s">
+        <v>44</v>
+      </c>
+      <c r="W181" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>527</v>
+      </c>
+      <c r="B182" t="s">
+        <v>528</v>
+      </c>
+      <c r="C182" t="s">
+        <v>34</v>
+      </c>
+      <c r="D182" t="s">
+        <v>35</v>
+      </c>
+      <c r="E182" t="s">
+        <v>36</v>
+      </c>
+      <c r="F182" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G182" t="s">
+        <v>29</v>
+      </c>
+      <c r="H182" t="s">
+        <v>30</v>
+      </c>
+      <c r="I182" t="s">
+        <v>31</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182">
+        <v>20.18</v>
+      </c>
+      <c r="L182">
+        <v>20.18</v>
+      </c>
+      <c r="M182" t="s">
+        <v>22</v>
+      </c>
+      <c r="N182" t="s">
+        <v>23</v>
+      </c>
+      <c r="O182" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P182" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>24</v>
+      </c>
+      <c r="R182" t="s">
+        <v>41</v>
+      </c>
+      <c r="S182" t="s">
+        <v>25</v>
+      </c>
+      <c r="T182" t="s">
+        <v>42</v>
+      </c>
+      <c r="U182" t="s">
+        <v>43</v>
+      </c>
+      <c r="V182" t="s">
+        <v>44</v>
+      </c>
+      <c r="W182" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>527</v>
+      </c>
+      <c r="B183" t="s">
+        <v>528</v>
+      </c>
+      <c r="C183" t="s">
+        <v>34</v>
+      </c>
+      <c r="D183" t="s">
+        <v>35</v>
+      </c>
+      <c r="E183" t="s">
+        <v>36</v>
+      </c>
+      <c r="F183" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G183" t="s">
+        <v>386</v>
+      </c>
+      <c r="H183" t="s">
+        <v>387</v>
+      </c>
+      <c r="I183" t="s">
+        <v>388</v>
+      </c>
+      <c r="J183">
+        <v>24</v>
+      </c>
+      <c r="K183">
+        <v>10.83</v>
+      </c>
+      <c r="L183">
+        <v>259.92</v>
+      </c>
+      <c r="M183" t="s">
+        <v>22</v>
+      </c>
+      <c r="N183" t="s">
+        <v>23</v>
+      </c>
+      <c r="O183" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P183" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>24</v>
+      </c>
+      <c r="R183" t="s">
+        <v>41</v>
+      </c>
+      <c r="S183" t="s">
+        <v>25</v>
+      </c>
+      <c r="T183" t="s">
+        <v>42</v>
+      </c>
+      <c r="U183" t="s">
+        <v>43</v>
+      </c>
+      <c r="V183" t="s">
+        <v>44</v>
+      </c>
+      <c r="W183" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>527</v>
+      </c>
+      <c r="B184" t="s">
+        <v>528</v>
+      </c>
+      <c r="C184" t="s">
+        <v>34</v>
+      </c>
+      <c r="D184" t="s">
+        <v>35</v>
+      </c>
+      <c r="E184" t="s">
+        <v>36</v>
+      </c>
+      <c r="F184" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G184" t="s">
+        <v>545</v>
+      </c>
+      <c r="H184" t="s">
+        <v>546</v>
+      </c>
+      <c r="I184" t="s">
+        <v>547</v>
+      </c>
+      <c r="J184">
+        <v>2</v>
+      </c>
+      <c r="K184">
+        <v>9.57</v>
+      </c>
+      <c r="L184">
+        <v>19.14</v>
+      </c>
+      <c r="M184" t="s">
+        <v>22</v>
+      </c>
+      <c r="N184" t="s">
+        <v>23</v>
+      </c>
+      <c r="O184" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P184" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>24</v>
+      </c>
+      <c r="R184" t="s">
+        <v>41</v>
+      </c>
+      <c r="S184" t="s">
+        <v>25</v>
+      </c>
+      <c r="T184" t="s">
+        <v>42</v>
+      </c>
+      <c r="U184" t="s">
+        <v>43</v>
+      </c>
+      <c r="V184" t="s">
+        <v>44</v>
+      </c>
+      <c r="W184" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>527</v>
+      </c>
+      <c r="B185" t="s">
+        <v>528</v>
+      </c>
+      <c r="C185" t="s">
+        <v>34</v>
+      </c>
+      <c r="D185" t="s">
+        <v>35</v>
+      </c>
+      <c r="E185" t="s">
+        <v>36</v>
+      </c>
+      <c r="F185" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G185" t="s">
+        <v>548</v>
+      </c>
+      <c r="H185" t="s">
+        <v>549</v>
+      </c>
+      <c r="I185" t="s">
+        <v>550</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>13.99</v>
+      </c>
+      <c r="L185">
+        <v>13.99</v>
+      </c>
+      <c r="M185" t="s">
+        <v>22</v>
+      </c>
+      <c r="N185" t="s">
+        <v>23</v>
+      </c>
+      <c r="O185" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P185" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>24</v>
+      </c>
+      <c r="R185" t="s">
+        <v>41</v>
+      </c>
+      <c r="S185" t="s">
+        <v>25</v>
+      </c>
+      <c r="T185" t="s">
+        <v>42</v>
+      </c>
+      <c r="U185" t="s">
+        <v>43</v>
+      </c>
+      <c r="V185" t="s">
+        <v>44</v>
+      </c>
+      <c r="W185" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>527</v>
+      </c>
+      <c r="B186" t="s">
+        <v>528</v>
+      </c>
+      <c r="C186" t="s">
+        <v>34</v>
+      </c>
+      <c r="D186" t="s">
+        <v>35</v>
+      </c>
+      <c r="E186" t="s">
+        <v>36</v>
+      </c>
+      <c r="F186" s="1">
+        <v>46057</v>
+      </c>
+      <c r="G186" t="s">
+        <v>221</v>
+      </c>
+      <c r="H186" t="s">
+        <v>222</v>
+      </c>
+      <c r="I186" t="s">
+        <v>223</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>15.86</v>
+      </c>
+      <c r="L186">
+        <v>15.86</v>
+      </c>
+      <c r="M186" t="s">
+        <v>22</v>
+      </c>
+      <c r="N186" t="s">
+        <v>23</v>
+      </c>
+      <c r="O186" s="1">
+        <v>46057</v>
+      </c>
+      <c r="P186" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>24</v>
+      </c>
+      <c r="R186" t="s">
+        <v>41</v>
+      </c>
+      <c r="S186" t="s">
+        <v>25</v>
+      </c>
+      <c r="T186" t="s">
+        <v>42</v>
+      </c>
+      <c r="U186" t="s">
+        <v>43</v>
+      </c>
+      <c r="V186" t="s">
+        <v>44</v>
+      </c>
+      <c r="W186" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>551</v>
+      </c>
+      <c r="B187" t="s">
+        <v>552</v>
+      </c>
+      <c r="C187" t="s">
+        <v>34</v>
+      </c>
+      <c r="D187" t="s">
+        <v>35</v>
+      </c>
+      <c r="E187" t="s">
+        <v>36</v>
+      </c>
+      <c r="F187" s="1">
+        <v>46062</v>
+      </c>
+      <c r="G187" t="s">
+        <v>150</v>
+      </c>
+      <c r="H187" t="s">
+        <v>151</v>
+      </c>
+      <c r="I187" t="s">
+        <v>152</v>
+      </c>
+      <c r="J187">
+        <v>2</v>
+      </c>
+      <c r="K187">
+        <v>13.42</v>
+      </c>
+      <c r="L187">
+        <v>26.84</v>
+      </c>
+      <c r="M187" t="s">
+        <v>22</v>
+      </c>
+      <c r="N187" t="s">
+        <v>23</v>
+      </c>
+      <c r="O187" s="1">
+        <v>46062</v>
+      </c>
+      <c r="P187" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>24</v>
+      </c>
+      <c r="R187" t="s">
+        <v>41</v>
+      </c>
+      <c r="S187" t="s">
+        <v>25</v>
+      </c>
+      <c r="T187" t="s">
+        <v>42</v>
+      </c>
+      <c r="U187" t="s">
+        <v>43</v>
+      </c>
+      <c r="V187" t="s">
+        <v>44</v>
+      </c>
+      <c r="W187" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>551</v>
+      </c>
+      <c r="B188" t="s">
+        <v>552</v>
+      </c>
+      <c r="C188" t="s">
+        <v>34</v>
+      </c>
+      <c r="D188" t="s">
+        <v>35</v>
+      </c>
+      <c r="E188" t="s">
+        <v>36</v>
+      </c>
+      <c r="F188" s="1">
+        <v>46062</v>
+      </c>
+      <c r="G188" t="s">
+        <v>125</v>
+      </c>
+      <c r="H188" t="s">
+        <v>126</v>
+      </c>
+      <c r="I188" t="s">
+        <v>127</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="K188">
+        <v>59.4</v>
+      </c>
+      <c r="L188">
+        <v>59.4</v>
+      </c>
+      <c r="M188" t="s">
+        <v>22</v>
+      </c>
+      <c r="N188" t="s">
+        <v>23</v>
+      </c>
+      <c r="O188" s="1">
+        <v>46062</v>
+      </c>
+      <c r="P188" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>24</v>
+      </c>
+      <c r="R188" t="s">
+        <v>41</v>
+      </c>
+      <c r="S188" t="s">
+        <v>25</v>
+      </c>
+      <c r="T188" t="s">
+        <v>42</v>
+      </c>
+      <c r="U188" t="s">
+        <v>43</v>
+      </c>
+      <c r="V188" t="s">
+        <v>44</v>
+      </c>
+      <c r="W188" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>553</v>
+      </c>
+      <c r="B189" t="s">
+        <v>554</v>
+      </c>
+      <c r="C189" t="s">
+        <v>34</v>
+      </c>
+      <c r="D189" t="s">
+        <v>35</v>
+      </c>
+      <c r="E189" t="s">
+        <v>36</v>
+      </c>
+      <c r="F189" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G189" t="s">
+        <v>202</v>
+      </c>
+      <c r="H189" t="s">
+        <v>203</v>
+      </c>
+      <c r="I189" t="s">
+        <v>204</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="L189">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="M189" t="s">
+        <v>22</v>
+      </c>
+      <c r="N189" t="s">
+        <v>23</v>
+      </c>
+      <c r="O189" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P189" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>24</v>
+      </c>
+      <c r="R189" t="s">
+        <v>41</v>
+      </c>
+      <c r="S189" t="s">
+        <v>25</v>
+      </c>
+      <c r="T189" t="s">
+        <v>42</v>
+      </c>
+      <c r="U189" t="s">
+        <v>43</v>
+      </c>
+      <c r="V189" t="s">
+        <v>44</v>
+      </c>
+      <c r="W189" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>553</v>
+      </c>
+      <c r="B190" t="s">
+        <v>554</v>
+      </c>
+      <c r="C190" t="s">
+        <v>34</v>
+      </c>
+      <c r="D190" t="s">
+        <v>35</v>
+      </c>
+      <c r="E190" t="s">
+        <v>36</v>
+      </c>
+      <c r="F190" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G190" t="s">
+        <v>206</v>
+      </c>
+      <c r="H190" t="s">
+        <v>207</v>
+      </c>
+      <c r="I190" t="s">
+        <v>208</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="L190">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="M190" t="s">
+        <v>22</v>
+      </c>
+      <c r="N190" t="s">
+        <v>23</v>
+      </c>
+      <c r="O190" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P190" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>24</v>
+      </c>
+      <c r="R190" t="s">
+        <v>41</v>
+      </c>
+      <c r="S190" t="s">
+        <v>25</v>
+      </c>
+      <c r="T190" t="s">
+        <v>42</v>
+      </c>
+      <c r="U190" t="s">
+        <v>43</v>
+      </c>
+      <c r="V190" t="s">
+        <v>44</v>
+      </c>
+      <c r="W190" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>555</v>
+      </c>
+      <c r="B191" t="s">
+        <v>556</v>
+      </c>
+      <c r="C191" t="s">
+        <v>34</v>
+      </c>
+      <c r="D191" t="s">
+        <v>35</v>
+      </c>
+      <c r="E191" t="s">
+        <v>36</v>
+      </c>
+      <c r="F191" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G191" t="s">
+        <v>129</v>
+      </c>
+      <c r="H191" t="s">
+        <v>130</v>
+      </c>
+      <c r="I191" t="s">
+        <v>131</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>19.559999999999999</v>
+      </c>
+      <c r="L191">
+        <v>19.559999999999999</v>
+      </c>
+      <c r="M191" t="s">
+        <v>22</v>
+      </c>
+      <c r="N191" t="s">
+        <v>23</v>
+      </c>
+      <c r="O191" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P191" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>24</v>
+      </c>
+      <c r="R191" t="s">
+        <v>41</v>
+      </c>
+      <c r="S191" t="s">
+        <v>25</v>
+      </c>
+      <c r="T191" t="s">
+        <v>42</v>
+      </c>
+      <c r="U191" t="s">
+        <v>43</v>
+      </c>
+      <c r="V191" t="s">
+        <v>44</v>
+      </c>
+      <c r="W191" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>555</v>
+      </c>
+      <c r="B192" t="s">
+        <v>556</v>
+      </c>
+      <c r="C192" t="s">
+        <v>34</v>
+      </c>
+      <c r="D192" t="s">
+        <v>35</v>
+      </c>
+      <c r="E192" t="s">
+        <v>36</v>
+      </c>
+      <c r="F192" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G192" t="s">
+        <v>260</v>
+      </c>
+      <c r="H192" t="s">
+        <v>261</v>
+      </c>
+      <c r="I192" t="s">
+        <v>262</v>
+      </c>
+      <c r="J192">
+        <v>1</v>
+      </c>
+      <c r="K192">
+        <v>20.32</v>
+      </c>
+      <c r="L192">
+        <v>20.32</v>
+      </c>
+      <c r="M192" t="s">
+        <v>22</v>
+      </c>
+      <c r="N192" t="s">
+        <v>23</v>
+      </c>
+      <c r="O192" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P192" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>24</v>
+      </c>
+      <c r="R192" t="s">
+        <v>41</v>
+      </c>
+      <c r="S192" t="s">
+        <v>25</v>
+      </c>
+      <c r="T192" t="s">
+        <v>42</v>
+      </c>
+      <c r="U192" t="s">
+        <v>43</v>
+      </c>
+      <c r="V192" t="s">
+        <v>44</v>
+      </c>
+      <c r="W192" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>555</v>
+      </c>
+      <c r="B193" t="s">
+        <v>556</v>
+      </c>
+      <c r="C193" t="s">
+        <v>34</v>
+      </c>
+      <c r="D193" t="s">
+        <v>35</v>
+      </c>
+      <c r="E193" t="s">
+        <v>36</v>
+      </c>
+      <c r="F193" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G193" t="s">
+        <v>558</v>
+      </c>
+      <c r="H193" t="s">
+        <v>559</v>
+      </c>
+      <c r="I193" t="s">
+        <v>560</v>
+      </c>
+      <c r="J193">
+        <v>12</v>
+      </c>
+      <c r="K193">
+        <v>2.39</v>
+      </c>
+      <c r="L193">
+        <v>28.68</v>
+      </c>
+      <c r="M193" t="s">
+        <v>22</v>
+      </c>
+      <c r="N193" t="s">
+        <v>23</v>
+      </c>
+      <c r="O193" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P193" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>24</v>
+      </c>
+      <c r="R193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S193" t="s">
+        <v>25</v>
+      </c>
+      <c r="T193" t="s">
+        <v>42</v>
+      </c>
+      <c r="U193" t="s">
+        <v>43</v>
+      </c>
+      <c r="V193" t="s">
+        <v>44</v>
+      </c>
+      <c r="W193" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>561</v>
+      </c>
+      <c r="B194" t="s">
+        <v>562</v>
+      </c>
+      <c r="C194" t="s">
+        <v>34</v>
+      </c>
+      <c r="D194" t="s">
+        <v>35</v>
+      </c>
+      <c r="E194" t="s">
+        <v>36</v>
+      </c>
+      <c r="F194" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G194" t="s">
+        <v>37</v>
+      </c>
+      <c r="H194" t="s">
+        <v>38</v>
+      </c>
+      <c r="I194" t="s">
+        <v>39</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>17.63</v>
+      </c>
+      <c r="L194">
+        <v>17.63</v>
+      </c>
+      <c r="M194" t="s">
+        <v>22</v>
+      </c>
+      <c r="N194" t="s">
+        <v>23</v>
+      </c>
+      <c r="O194" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P194" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>24</v>
+      </c>
+      <c r="R194" t="s">
+        <v>41</v>
+      </c>
+      <c r="S194" t="s">
+        <v>25</v>
+      </c>
+      <c r="T194" t="s">
+        <v>42</v>
+      </c>
+      <c r="U194" t="s">
+        <v>43</v>
+      </c>
+      <c r="V194" t="s">
+        <v>44</v>
+      </c>
+      <c r="W194" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>561</v>
+      </c>
+      <c r="B195" t="s">
+        <v>562</v>
+      </c>
+      <c r="C195" t="s">
+        <v>34</v>
+      </c>
+      <c r="D195" t="s">
+        <v>35</v>
+      </c>
+      <c r="E195" t="s">
+        <v>36</v>
+      </c>
+      <c r="F195" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G195" t="s">
+        <v>564</v>
+      </c>
+      <c r="H195" t="s">
+        <v>565</v>
+      </c>
+      <c r="I195" t="s">
+        <v>566</v>
+      </c>
+      <c r="J195">
+        <v>5</v>
+      </c>
+      <c r="K195">
+        <v>6.28</v>
+      </c>
+      <c r="L195">
+        <v>31.4</v>
+      </c>
+      <c r="M195" t="s">
+        <v>22</v>
+      </c>
+      <c r="N195" t="s">
+        <v>23</v>
+      </c>
+      <c r="O195" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P195" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>24</v>
+      </c>
+      <c r="R195" t="s">
+        <v>41</v>
+      </c>
+      <c r="S195" t="s">
+        <v>25</v>
+      </c>
+      <c r="T195" t="s">
+        <v>42</v>
+      </c>
+      <c r="U195" t="s">
+        <v>43</v>
+      </c>
+      <c r="V195" t="s">
+        <v>44</v>
+      </c>
+      <c r="W195" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>561</v>
+      </c>
+      <c r="B196" t="s">
+        <v>562</v>
+      </c>
+      <c r="C196" t="s">
+        <v>34</v>
+      </c>
+      <c r="D196" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196" t="s">
+        <v>36</v>
+      </c>
+      <c r="F196" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G196" t="s">
+        <v>567</v>
+      </c>
+      <c r="H196" t="s">
+        <v>568</v>
+      </c>
+      <c r="I196" t="s">
+        <v>569</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>6.78</v>
+      </c>
+      <c r="L196">
+        <v>6.78</v>
+      </c>
+      <c r="M196" t="s">
+        <v>22</v>
+      </c>
+      <c r="N196" t="s">
+        <v>23</v>
+      </c>
+      <c r="O196" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P196" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>24</v>
+      </c>
+      <c r="R196" t="s">
+        <v>41</v>
+      </c>
+      <c r="S196" t="s">
+        <v>25</v>
+      </c>
+      <c r="T196" t="s">
+        <v>42</v>
+      </c>
+      <c r="U196" t="s">
+        <v>43</v>
+      </c>
+      <c r="V196" t="s">
+        <v>44</v>
+      </c>
+      <c r="W196" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>561</v>
+      </c>
+      <c r="B197" t="s">
+        <v>562</v>
+      </c>
+      <c r="C197" t="s">
+        <v>34</v>
+      </c>
+      <c r="D197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E197" t="s">
+        <v>36</v>
+      </c>
+      <c r="F197" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G197" t="s">
+        <v>570</v>
+      </c>
+      <c r="H197" t="s">
+        <v>571</v>
+      </c>
+      <c r="I197" t="s">
+        <v>572</v>
+      </c>
+      <c r="J197">
+        <v>1</v>
+      </c>
+      <c r="K197">
+        <v>12.29</v>
+      </c>
+      <c r="L197">
+        <v>12.29</v>
+      </c>
+      <c r="M197" t="s">
+        <v>22</v>
+      </c>
+      <c r="N197" t="s">
+        <v>23</v>
+      </c>
+      <c r="O197" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P197" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>24</v>
+      </c>
+      <c r="R197" t="s">
+        <v>41</v>
+      </c>
+      <c r="S197" t="s">
+        <v>25</v>
+      </c>
+      <c r="T197" t="s">
+        <v>42</v>
+      </c>
+      <c r="U197" t="s">
+        <v>43</v>
+      </c>
+      <c r="V197" t="s">
+        <v>44</v>
+      </c>
+      <c r="W197" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>561</v>
+      </c>
+      <c r="B198" t="s">
+        <v>562</v>
+      </c>
+      <c r="C198" t="s">
+        <v>34</v>
+      </c>
+      <c r="D198" t="s">
+        <v>35</v>
+      </c>
+      <c r="E198" t="s">
+        <v>36</v>
+      </c>
+      <c r="F198" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G198" t="s">
+        <v>573</v>
+      </c>
+      <c r="H198" t="s">
+        <v>574</v>
+      </c>
+      <c r="I198" t="s">
+        <v>575</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>8.25</v>
+      </c>
+      <c r="L198">
+        <v>8.25</v>
+      </c>
+      <c r="M198" t="s">
+        <v>22</v>
+      </c>
+      <c r="N198" t="s">
+        <v>23</v>
+      </c>
+      <c r="O198" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P198" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>24</v>
+      </c>
+      <c r="R198" t="s">
+        <v>41</v>
+      </c>
+      <c r="S198" t="s">
+        <v>25</v>
+      </c>
+      <c r="T198" t="s">
+        <v>42</v>
+      </c>
+      <c r="U198" t="s">
+        <v>43</v>
+      </c>
+      <c r="V198" t="s">
+        <v>44</v>
+      </c>
+      <c r="W198" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>561</v>
+      </c>
+      <c r="B199" t="s">
+        <v>562</v>
+      </c>
+      <c r="C199" t="s">
+        <v>34</v>
+      </c>
+      <c r="D199" t="s">
+        <v>35</v>
+      </c>
+      <c r="E199" t="s">
+        <v>36</v>
+      </c>
+      <c r="F199" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G199" t="s">
+        <v>576</v>
+      </c>
+      <c r="H199" t="s">
+        <v>577</v>
+      </c>
+      <c r="I199" t="s">
+        <v>578</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>8.25</v>
+      </c>
+      <c r="L199">
+        <v>8.25</v>
+      </c>
+      <c r="M199" t="s">
+        <v>22</v>
+      </c>
+      <c r="N199" t="s">
+        <v>23</v>
+      </c>
+      <c r="O199" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P199" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>24</v>
+      </c>
+      <c r="R199" t="s">
+        <v>41</v>
+      </c>
+      <c r="S199" t="s">
+        <v>25</v>
+      </c>
+      <c r="T199" t="s">
+        <v>42</v>
+      </c>
+      <c r="U199" t="s">
+        <v>43</v>
+      </c>
+      <c r="V199" t="s">
+        <v>44</v>
+      </c>
+      <c r="W199" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>561</v>
+      </c>
+      <c r="B200" t="s">
+        <v>562</v>
+      </c>
+      <c r="C200" t="s">
+        <v>34</v>
+      </c>
+      <c r="D200" t="s">
+        <v>35</v>
+      </c>
+      <c r="E200" t="s">
+        <v>36</v>
+      </c>
+      <c r="F200" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G200" t="s">
+        <v>60</v>
+      </c>
+      <c r="H200" t="s">
+        <v>61</v>
+      </c>
+      <c r="I200" t="s">
+        <v>62</v>
+      </c>
+      <c r="J200">
+        <v>2</v>
+      </c>
+      <c r="K200">
+        <v>17.63</v>
+      </c>
+      <c r="L200">
+        <v>35.26</v>
+      </c>
+      <c r="M200" t="s">
+        <v>22</v>
+      </c>
+      <c r="N200" t="s">
+        <v>23</v>
+      </c>
+      <c r="O200" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P200" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>24</v>
+      </c>
+      <c r="R200" t="s">
+        <v>41</v>
+      </c>
+      <c r="S200" t="s">
+        <v>25</v>
+      </c>
+      <c r="T200" t="s">
+        <v>42</v>
+      </c>
+      <c r="U200" t="s">
+        <v>43</v>
+      </c>
+      <c r="V200" t="s">
+        <v>44</v>
+      </c>
+      <c r="W200" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>561</v>
+      </c>
+      <c r="B201" t="s">
+        <v>562</v>
+      </c>
+      <c r="C201" t="s">
+        <v>34</v>
+      </c>
+      <c r="D201" t="s">
+        <v>35</v>
+      </c>
+      <c r="E201" t="s">
+        <v>36</v>
+      </c>
+      <c r="F201" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G201" t="s">
+        <v>579</v>
+      </c>
+      <c r="H201" t="s">
+        <v>580</v>
+      </c>
+      <c r="I201" t="s">
+        <v>581</v>
+      </c>
+      <c r="J201">
+        <v>2</v>
+      </c>
+      <c r="K201">
+        <v>6.6</v>
+      </c>
+      <c r="L201">
+        <v>13.2</v>
+      </c>
+      <c r="M201" t="s">
+        <v>22</v>
+      </c>
+      <c r="N201" t="s">
+        <v>23</v>
+      </c>
+      <c r="O201" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P201" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>24</v>
+      </c>
+      <c r="R201" t="s">
+        <v>41</v>
+      </c>
+      <c r="S201" t="s">
+        <v>25</v>
+      </c>
+      <c r="T201" t="s">
+        <v>42</v>
+      </c>
+      <c r="U201" t="s">
+        <v>43</v>
+      </c>
+      <c r="V201" t="s">
+        <v>44</v>
+      </c>
+      <c r="W201" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>561</v>
+      </c>
+      <c r="B202" t="s">
+        <v>562</v>
+      </c>
+      <c r="C202" t="s">
+        <v>34</v>
+      </c>
+      <c r="D202" t="s">
+        <v>35</v>
+      </c>
+      <c r="E202" t="s">
+        <v>36</v>
+      </c>
+      <c r="F202" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G202" t="s">
+        <v>582</v>
+      </c>
+      <c r="H202" t="s">
+        <v>583</v>
+      </c>
+      <c r="I202" t="s">
+        <v>584</v>
+      </c>
+      <c r="J202">
+        <v>2</v>
+      </c>
+      <c r="K202">
+        <v>11.4</v>
+      </c>
+      <c r="L202">
+        <v>22.8</v>
+      </c>
+      <c r="M202" t="s">
+        <v>22</v>
+      </c>
+      <c r="N202" t="s">
+        <v>23</v>
+      </c>
+      <c r="O202" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P202" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>24</v>
+      </c>
+      <c r="R202" t="s">
+        <v>41</v>
+      </c>
+      <c r="S202" t="s">
+        <v>25</v>
+      </c>
+      <c r="T202" t="s">
+        <v>42</v>
+      </c>
+      <c r="U202" t="s">
+        <v>43</v>
+      </c>
+      <c r="V202" t="s">
+        <v>44</v>
+      </c>
+      <c r="W202" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>561</v>
+      </c>
+      <c r="B203" t="s">
+        <v>562</v>
+      </c>
+      <c r="C203" t="s">
+        <v>34</v>
+      </c>
+      <c r="D203" t="s">
+        <v>35</v>
+      </c>
+      <c r="E203" t="s">
+        <v>36</v>
+      </c>
+      <c r="F203" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G203" t="s">
+        <v>375</v>
+      </c>
+      <c r="H203" t="s">
+        <v>376</v>
+      </c>
+      <c r="I203" t="s">
+        <v>377</v>
+      </c>
+      <c r="J203">
+        <v>1</v>
+      </c>
+      <c r="K203">
+        <v>12.29</v>
+      </c>
+      <c r="L203">
+        <v>12.29</v>
+      </c>
+      <c r="M203" t="s">
+        <v>22</v>
+      </c>
+      <c r="N203" t="s">
+        <v>23</v>
+      </c>
+      <c r="O203" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P203" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>24</v>
+      </c>
+      <c r="R203" t="s">
+        <v>41</v>
+      </c>
+      <c r="S203" t="s">
+        <v>25</v>
+      </c>
+      <c r="T203" t="s">
+        <v>42</v>
+      </c>
+      <c r="U203" t="s">
+        <v>43</v>
+      </c>
+      <c r="V203" t="s">
+        <v>44</v>
+      </c>
+      <c r="W203" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>561</v>
+      </c>
+      <c r="B204" t="s">
+        <v>562</v>
+      </c>
+      <c r="C204" t="s">
+        <v>34</v>
+      </c>
+      <c r="D204" t="s">
+        <v>35</v>
+      </c>
+      <c r="E204" t="s">
+        <v>36</v>
+      </c>
+      <c r="F204" s="1">
+        <v>46063</v>
+      </c>
+      <c r="G204" t="s">
+        <v>585</v>
+      </c>
+      <c r="H204" t="s">
+        <v>586</v>
+      </c>
+      <c r="I204" t="s">
+        <v>587</v>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="K204">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="L204">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="M204" t="s">
+        <v>22</v>
+      </c>
+      <c r="N204" t="s">
+        <v>23</v>
+      </c>
+      <c r="O204" s="1">
+        <v>46063</v>
+      </c>
+      <c r="P204" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>24</v>
+      </c>
+      <c r="R204" t="s">
+        <v>41</v>
+      </c>
+      <c r="S204" t="s">
+        <v>25</v>
+      </c>
+      <c r="T204" t="s">
+        <v>42</v>
+      </c>
+      <c r="U204" t="s">
+        <v>43</v>
+      </c>
+      <c r="V204" t="s">
+        <v>44</v>
+      </c>
+      <c r="W204" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>588</v>
+      </c>
+      <c r="B205" t="s">
+        <v>589</v>
+      </c>
+      <c r="C205" t="s">
+        <v>34</v>
+      </c>
+      <c r="D205" t="s">
+        <v>35</v>
+      </c>
+      <c r="E205" t="s">
+        <v>36</v>
+      </c>
+      <c r="F205" s="1">
+        <v>46065</v>
+      </c>
+      <c r="G205" t="s">
+        <v>590</v>
+      </c>
+      <c r="H205" t="s">
+        <v>591</v>
+      </c>
+      <c r="I205" t="s">
+        <v>592</v>
+      </c>
+      <c r="J205">
+        <v>1</v>
+      </c>
+      <c r="K205">
+        <v>15.19</v>
+      </c>
+      <c r="L205">
+        <v>15.19</v>
+      </c>
+      <c r="M205" t="s">
+        <v>22</v>
+      </c>
+      <c r="N205" t="s">
+        <v>23</v>
+      </c>
+      <c r="O205" s="1">
+        <v>46065</v>
+      </c>
+      <c r="P205" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>24</v>
+      </c>
+      <c r="R205" t="s">
+        <v>41</v>
+      </c>
+      <c r="S205" t="s">
+        <v>25</v>
+      </c>
+      <c r="T205" t="s">
+        <v>42</v>
+      </c>
+      <c r="U205" t="s">
+        <v>43</v>
+      </c>
+      <c r="V205" t="s">
+        <v>44</v>
+      </c>
+      <c r="W205" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>588</v>
+      </c>
+      <c r="B206" t="s">
+        <v>589</v>
+      </c>
+      <c r="C206" t="s">
+        <v>34</v>
+      </c>
+      <c r="D206" t="s">
+        <v>35</v>
+      </c>
+      <c r="E206" t="s">
+        <v>36</v>
+      </c>
+      <c r="F206" s="1">
+        <v>46065</v>
+      </c>
+      <c r="G206" t="s">
+        <v>594</v>
+      </c>
+      <c r="H206" t="s">
+        <v>595</v>
+      </c>
+      <c r="I206" t="s">
+        <v>596</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="K206">
+        <v>3.94</v>
+      </c>
+      <c r="L206">
+        <v>3.94</v>
+      </c>
+      <c r="M206" t="s">
+        <v>22</v>
+      </c>
+      <c r="N206" t="s">
+        <v>23</v>
+      </c>
+      <c r="O206" s="1">
+        <v>46065</v>
+      </c>
+      <c r="P206" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>24</v>
+      </c>
+      <c r="R206" t="s">
+        <v>41</v>
+      </c>
+      <c r="S206" t="s">
+        <v>25</v>
+      </c>
+      <c r="T206" t="s">
+        <v>42</v>
+      </c>
+      <c r="U206" t="s">
+        <v>43</v>
+      </c>
+      <c r="V206" t="s">
+        <v>44</v>
+      </c>
+      <c r="W206" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>597</v>
+      </c>
+      <c r="B207" t="s">
+        <v>598</v>
+      </c>
+      <c r="C207" t="s">
+        <v>34</v>
+      </c>
+      <c r="D207" t="s">
+        <v>35</v>
+      </c>
+      <c r="E207" t="s">
+        <v>36</v>
+      </c>
+      <c r="F207" s="1">
+        <v>46066</v>
+      </c>
+      <c r="G207" t="s">
+        <v>599</v>
+      </c>
+      <c r="H207" t="s">
+        <v>600</v>
+      </c>
+      <c r="I207" t="s">
+        <v>601</v>
+      </c>
+      <c r="J207">
+        <v>12</v>
+      </c>
+      <c r="K207">
+        <v>9.5</v>
+      </c>
+      <c r="L207">
+        <v>114</v>
+      </c>
+      <c r="M207" t="s">
+        <v>22</v>
+      </c>
+      <c r="N207" t="s">
+        <v>23</v>
+      </c>
+      <c r="O207" s="1">
+        <v>46066</v>
+      </c>
+      <c r="P207" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>24</v>
+      </c>
+      <c r="R207" t="s">
+        <v>41</v>
+      </c>
+      <c r="S207" t="s">
+        <v>25</v>
+      </c>
+      <c r="T207" t="s">
+        <v>42</v>
+      </c>
+      <c r="U207" t="s">
+        <v>43</v>
+      </c>
+      <c r="V207" t="s">
+        <v>44</v>
+      </c>
+      <c r="W207" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>603</v>
+      </c>
+      <c r="B208" t="s">
+        <v>604</v>
+      </c>
+      <c r="C208" t="s">
+        <v>34</v>
+      </c>
+      <c r="D208" t="s">
+        <v>35</v>
+      </c>
+      <c r="E208" t="s">
+        <v>36</v>
+      </c>
+      <c r="F208" s="1">
+        <v>46070</v>
+      </c>
+      <c r="G208" t="s">
+        <v>29</v>
+      </c>
+      <c r="H208" t="s">
+        <v>30</v>
+      </c>
+      <c r="I208" t="s">
+        <v>31</v>
+      </c>
+      <c r="J208">
+        <v>1</v>
+      </c>
+      <c r="K208">
+        <v>20.18</v>
+      </c>
+      <c r="L208">
+        <v>20.18</v>
+      </c>
+      <c r="M208" t="s">
+        <v>22</v>
+      </c>
+      <c r="N208" t="s">
+        <v>23</v>
+      </c>
+      <c r="O208" s="1">
+        <v>46069</v>
+      </c>
+      <c r="P208" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>24</v>
+      </c>
+      <c r="R208" t="s">
+        <v>41</v>
+      </c>
+      <c r="S208" t="s">
+        <v>25</v>
+      </c>
+      <c r="T208" t="s">
+        <v>42</v>
+      </c>
+      <c r="U208" t="s">
+        <v>43</v>
+      </c>
+      <c r="V208" t="s">
+        <v>44</v>
+      </c>
+      <c r="W208" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="209" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>606</v>
+      </c>
+      <c r="B209" t="s">
+        <v>607</v>
+      </c>
+      <c r="C209" t="s">
+        <v>34</v>
+      </c>
+      <c r="D209" t="s">
+        <v>35</v>
+      </c>
+      <c r="E209" t="s">
+        <v>36</v>
+      </c>
+      <c r="F209" s="1">
+        <v>46070</v>
+      </c>
+      <c r="G209" t="s">
+        <v>608</v>
+      </c>
+      <c r="H209" t="s">
+        <v>609</v>
+      </c>
+      <c r="I209" t="s">
+        <v>610</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>30.74</v>
+      </c>
+      <c r="L209">
+        <v>30.74</v>
+      </c>
+      <c r="M209" t="s">
+        <v>22</v>
+      </c>
+      <c r="N209" t="s">
+        <v>23</v>
+      </c>
+      <c r="O209" s="1">
+        <v>46070</v>
+      </c>
+      <c r="P209" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>24</v>
+      </c>
+      <c r="R209" t="s">
+        <v>41</v>
+      </c>
+      <c r="S209" t="s">
+        <v>25</v>
+      </c>
+      <c r="T209" t="s">
+        <v>42</v>
+      </c>
+      <c r="U209" t="s">
+        <v>43</v>
+      </c>
+      <c r="V209" t="s">
+        <v>44</v>
+      </c>
+      <c r="W209" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="210" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>612</v>
+      </c>
+      <c r="B210" t="s">
+        <v>613</v>
+      </c>
+      <c r="C210" t="s">
+        <v>34</v>
+      </c>
+      <c r="D210" t="s">
+        <v>35</v>
+      </c>
+      <c r="E210" t="s">
+        <v>36</v>
+      </c>
+      <c r="F210" s="1">
+        <v>46071</v>
+      </c>
+      <c r="G210" t="s">
+        <v>158</v>
+      </c>
+      <c r="H210" t="s">
+        <v>159</v>
+      </c>
+      <c r="I210" t="s">
+        <v>160</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>38.24</v>
+      </c>
+      <c r="L210">
+        <v>38.24</v>
+      </c>
+      <c r="M210" t="s">
+        <v>22</v>
+      </c>
+      <c r="N210" t="s">
+        <v>23</v>
+      </c>
+      <c r="O210" s="1">
+        <v>46071</v>
+      </c>
+      <c r="P210" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>24</v>
+      </c>
+      <c r="R210" t="s">
+        <v>41</v>
+      </c>
+      <c r="S210" t="s">
+        <v>25</v>
+      </c>
+      <c r="T210" t="s">
+        <v>42</v>
+      </c>
+      <c r="U210" t="s">
+        <v>43</v>
+      </c>
+      <c r="V210" t="s">
+        <v>44</v>
+      </c>
+      <c r="W210" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>614</v>
+      </c>
+      <c r="B211" t="s">
+        <v>615</v>
+      </c>
+      <c r="C211" t="s">
+        <v>34</v>
+      </c>
+      <c r="D211" t="s">
+        <v>35</v>
+      </c>
+      <c r="E211" t="s">
+        <v>36</v>
+      </c>
+      <c r="F211" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G211" t="s">
+        <v>503</v>
+      </c>
+      <c r="H211" t="s">
+        <v>504</v>
+      </c>
+      <c r="I211" t="s">
+        <v>505</v>
+      </c>
+      <c r="J211">
+        <v>1</v>
+      </c>
+      <c r="K211">
+        <v>13.06</v>
+      </c>
+      <c r="L211">
+        <v>13.06</v>
+      </c>
+      <c r="M211" t="s">
+        <v>22</v>
+      </c>
+      <c r="N211" t="s">
+        <v>23</v>
+      </c>
+      <c r="O211" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P211" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>24</v>
+      </c>
+      <c r="R211" t="s">
+        <v>41</v>
+      </c>
+      <c r="S211" t="s">
+        <v>25</v>
+      </c>
+      <c r="T211" t="s">
+        <v>42</v>
+      </c>
+      <c r="U211" t="s">
+        <v>43</v>
+      </c>
+      <c r="V211" t="s">
+        <v>44</v>
+      </c>
+      <c r="W211" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>614</v>
+      </c>
+      <c r="B212" t="s">
+        <v>615</v>
+      </c>
+      <c r="C212" t="s">
+        <v>34</v>
+      </c>
+      <c r="D212" t="s">
+        <v>35</v>
+      </c>
+      <c r="E212" t="s">
+        <v>36</v>
+      </c>
+      <c r="F212" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G212" t="s">
+        <v>617</v>
+      </c>
+      <c r="H212" t="s">
+        <v>618</v>
+      </c>
+      <c r="I212" t="s">
+        <v>619</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="L212">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="M212" t="s">
+        <v>22</v>
+      </c>
+      <c r="N212" t="s">
+        <v>23</v>
+      </c>
+      <c r="O212" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P212" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>24</v>
+      </c>
+      <c r="R212" t="s">
+        <v>41</v>
+      </c>
+      <c r="S212" t="s">
+        <v>25</v>
+      </c>
+      <c r="T212" t="s">
+        <v>42</v>
+      </c>
+      <c r="U212" t="s">
+        <v>43</v>
+      </c>
+      <c r="V212" t="s">
+        <v>44</v>
+      </c>
+      <c r="W212" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>614</v>
+      </c>
+      <c r="B213" t="s">
+        <v>615</v>
+      </c>
+      <c r="C213" t="s">
+        <v>34</v>
+      </c>
+      <c r="D213" t="s">
+        <v>35</v>
+      </c>
+      <c r="E213" t="s">
+        <v>36</v>
+      </c>
+      <c r="F213" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G213" t="s">
+        <v>620</v>
+      </c>
+      <c r="H213" t="s">
+        <v>621</v>
+      </c>
+      <c r="I213" t="s">
+        <v>622</v>
+      </c>
+      <c r="J213">
+        <v>1</v>
+      </c>
+      <c r="K213">
+        <v>64.89</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213" t="s">
+        <v>22</v>
+      </c>
+      <c r="N213" t="s">
+        <v>23</v>
+      </c>
+      <c r="O213" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P213" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>24</v>
+      </c>
+      <c r="R213" t="s">
+        <v>41</v>
+      </c>
+      <c r="S213" t="s">
+        <v>25</v>
+      </c>
+      <c r="T213" t="s">
+        <v>42</v>
+      </c>
+      <c r="U213" t="s">
+        <v>43</v>
+      </c>
+      <c r="V213" t="s">
+        <v>44</v>
+      </c>
+      <c r="W213" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="214" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>614</v>
+      </c>
+      <c r="B214" t="s">
+        <v>615</v>
+      </c>
+      <c r="C214" t="s">
+        <v>34</v>
+      </c>
+      <c r="D214" t="s">
+        <v>35</v>
+      </c>
+      <c r="E214" t="s">
+        <v>36</v>
+      </c>
+      <c r="F214" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G214" t="s">
+        <v>512</v>
+      </c>
+      <c r="H214" t="s">
+        <v>513</v>
+      </c>
+      <c r="I214" t="s">
+        <v>514</v>
+      </c>
+      <c r="J214">
+        <v>1</v>
+      </c>
+      <c r="K214">
+        <v>15.99</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214" t="s">
+        <v>22</v>
+      </c>
+      <c r="N214" t="s">
+        <v>23</v>
+      </c>
+      <c r="O214" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P214" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>24</v>
+      </c>
+      <c r="R214" t="s">
+        <v>41</v>
+      </c>
+      <c r="S214" t="s">
+        <v>25</v>
+      </c>
+      <c r="T214" t="s">
+        <v>42</v>
+      </c>
+      <c r="U214" t="s">
+        <v>43</v>
+      </c>
+      <c r="V214" t="s">
+        <v>44</v>
+      </c>
+      <c r="W214" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="215" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>614</v>
+      </c>
+      <c r="B215" t="s">
+        <v>615</v>
+      </c>
+      <c r="C215" t="s">
+        <v>34</v>
+      </c>
+      <c r="D215" t="s">
+        <v>35</v>
+      </c>
+      <c r="E215" t="s">
+        <v>36</v>
+      </c>
+      <c r="F215" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G215" t="s">
+        <v>69</v>
+      </c>
+      <c r="H215" t="s">
+        <v>70</v>
+      </c>
+      <c r="I215" t="s">
+        <v>71</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215">
+        <v>10.59</v>
+      </c>
+      <c r="L215">
+        <v>10.59</v>
+      </c>
+      <c r="M215" t="s">
+        <v>22</v>
+      </c>
+      <c r="N215" t="s">
+        <v>23</v>
+      </c>
+      <c r="O215" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P215" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>24</v>
+      </c>
+      <c r="R215" t="s">
+        <v>41</v>
+      </c>
+      <c r="S215" t="s">
+        <v>25</v>
+      </c>
+      <c r="T215" t="s">
+        <v>42</v>
+      </c>
+      <c r="U215" t="s">
+        <v>43</v>
+      </c>
+      <c r="V215" t="s">
+        <v>44</v>
+      </c>
+      <c r="W215" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="216" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>614</v>
+      </c>
+      <c r="B216" t="s">
+        <v>615</v>
+      </c>
+      <c r="C216" t="s">
+        <v>34</v>
+      </c>
+      <c r="D216" t="s">
+        <v>35</v>
+      </c>
+      <c r="E216" t="s">
+        <v>36</v>
+      </c>
+      <c r="F216" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G216" t="s">
+        <v>623</v>
+      </c>
+      <c r="H216" t="s">
+        <v>624</v>
+      </c>
+      <c r="I216" t="s">
+        <v>625</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216">
+        <v>23.48</v>
+      </c>
+      <c r="L216">
+        <v>23.48</v>
+      </c>
+      <c r="M216" t="s">
+        <v>22</v>
+      </c>
+      <c r="N216" t="s">
+        <v>23</v>
+      </c>
+      <c r="O216" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P216" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>24</v>
+      </c>
+      <c r="R216" t="s">
+        <v>41</v>
+      </c>
+      <c r="S216" t="s">
+        <v>25</v>
+      </c>
+      <c r="T216" t="s">
+        <v>42</v>
+      </c>
+      <c r="U216" t="s">
+        <v>43</v>
+      </c>
+      <c r="V216" t="s">
+        <v>44</v>
+      </c>
+      <c r="W216" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="217" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>614</v>
+      </c>
+      <c r="B217" t="s">
+        <v>615</v>
+      </c>
+      <c r="C217" t="s">
+        <v>34</v>
+      </c>
+      <c r="D217" t="s">
+        <v>35</v>
+      </c>
+      <c r="E217" t="s">
+        <v>36</v>
+      </c>
+      <c r="F217" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G217" t="s">
+        <v>291</v>
+      </c>
+      <c r="H217" t="s">
+        <v>292</v>
+      </c>
+      <c r="I217" t="s">
+        <v>293</v>
+      </c>
+      <c r="J217">
+        <v>1</v>
+      </c>
+      <c r="K217">
+        <v>11.33</v>
+      </c>
+      <c r="L217">
+        <v>11.33</v>
+      </c>
+      <c r="M217" t="s">
+        <v>22</v>
+      </c>
+      <c r="N217" t="s">
+        <v>23</v>
+      </c>
+      <c r="O217" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P217" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>24</v>
+      </c>
+      <c r="R217" t="s">
+        <v>41</v>
+      </c>
+      <c r="S217" t="s">
+        <v>25</v>
+      </c>
+      <c r="T217" t="s">
+        <v>42</v>
+      </c>
+      <c r="U217" t="s">
+        <v>43</v>
+      </c>
+      <c r="V217" t="s">
+        <v>44</v>
+      </c>
+      <c r="W217" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>614</v>
+      </c>
+      <c r="B218" t="s">
+        <v>615</v>
+      </c>
+      <c r="C218" t="s">
+        <v>34</v>
+      </c>
+      <c r="D218" t="s">
+        <v>35</v>
+      </c>
+      <c r="E218" t="s">
+        <v>36</v>
+      </c>
+      <c r="F218" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G218" t="s">
+        <v>199</v>
+      </c>
+      <c r="H218" t="s">
+        <v>200</v>
+      </c>
+      <c r="I218" t="s">
+        <v>201</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="L218">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="M218" t="s">
+        <v>22</v>
+      </c>
+      <c r="N218" t="s">
+        <v>23</v>
+      </c>
+      <c r="O218" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P218" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>24</v>
+      </c>
+      <c r="R218" t="s">
+        <v>41</v>
+      </c>
+      <c r="S218" t="s">
+        <v>25</v>
+      </c>
+      <c r="T218" t="s">
+        <v>42</v>
+      </c>
+      <c r="U218" t="s">
+        <v>43</v>
+      </c>
+      <c r="V218" t="s">
+        <v>44</v>
+      </c>
+      <c r="W218" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>614</v>
+      </c>
+      <c r="B219" t="s">
+        <v>615</v>
+      </c>
+      <c r="C219" t="s">
+        <v>34</v>
+      </c>
+      <c r="D219" t="s">
+        <v>35</v>
+      </c>
+      <c r="E219" t="s">
+        <v>36</v>
+      </c>
+      <c r="F219" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G219" t="s">
+        <v>202</v>
+      </c>
+      <c r="H219" t="s">
+        <v>203</v>
+      </c>
+      <c r="I219" t="s">
+        <v>204</v>
+      </c>
+      <c r="J219">
+        <v>1</v>
+      </c>
+      <c r="K219">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="L219">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="M219" t="s">
+        <v>22</v>
+      </c>
+      <c r="N219" t="s">
+        <v>23</v>
+      </c>
+      <c r="O219" s="1">
+        <v>46073</v>
+      </c>
+      <c r="P219" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>24</v>
+      </c>
+      <c r="R219" t="s">
+        <v>41</v>
+      </c>
+      <c r="S219" t="s">
+        <v>25</v>
+      </c>
+      <c r="T219" t="s">
+        <v>42</v>
+      </c>
+      <c r="U219" t="s">
+        <v>43</v>
+      </c>
+      <c r="V219" t="s">
+        <v>44</v>
+      </c>
+      <c r="W219" t="s">
+        <v>626</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13481,12 +17915,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13628,15 +18059,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13660,10 +18095,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/activitereelford-2026.xlsx
+++ b/activitereelford-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5991DB-9EEF-47EB-AA12-59E07C899DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39E769E-EF47-4FCE-80C4-CD660CBA5383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3955" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4837" uniqueCount="701">
   <si>
     <t>N°commande</t>
   </si>
@@ -1918,6 +1918,228 @@
   </si>
   <si>
     <t>Février</t>
+  </si>
+  <si>
+    <t>26409522</t>
+  </si>
+  <si>
+    <t>26610127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE CONCEPT AUTO     </t>
+  </si>
+  <si>
+    <t>TEAM CAPIN SEBASTIEN</t>
+  </si>
+  <si>
+    <t>26409698</t>
+  </si>
+  <si>
+    <t>26610399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2001 28                 </t>
+  </si>
+  <si>
+    <t>V2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRANULES ABSORBANT  SAC 20L                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGE MIKA AUTOMOBILES     </t>
+  </si>
+  <si>
+    <t>26409836</t>
+  </si>
+  <si>
+    <t>26610534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE RS AUTOMOBILES   </t>
+  </si>
+  <si>
+    <t>26410276</t>
+  </si>
+  <si>
+    <t>26610979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86377 22                 </t>
+  </si>
+  <si>
+    <t>86377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENSOR GEL CAPTEUR PLUIE PB                                  </t>
+  </si>
+  <si>
+    <t>26410404</t>
+  </si>
+  <si>
+    <t>26611157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE CARROSSERIE+MAG FORD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86957 22                 </t>
+  </si>
+  <si>
+    <t>86957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRA FLEX 1KG                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86961 22                 </t>
+  </si>
+  <si>
+    <t>86961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRA ALU THX - POT 1,8KG                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1188 33                 </t>
+  </si>
+  <si>
+    <t>A1188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD2 DISQUES EPONGES SUPERFINS 150MM P800-P1200               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1189 33                 </t>
+  </si>
+  <si>
+    <t>A1189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD3 DISQUES EPONGES MICROFINS 150MM P1500-P2000              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1298 33                 </t>
+  </si>
+  <si>
+    <t>A1298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISQUES DURALITE 150MM P600                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">84909 22                 </t>
+  </si>
+  <si>
+    <t>84909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAPFC NX NETTOYANT TOUS USAGES                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85092 10                 </t>
+  </si>
+  <si>
+    <t>85092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANO PERFORMANCE POLISH - 1L                                 </t>
+  </si>
+  <si>
+    <t>26410405</t>
+  </si>
+  <si>
+    <t>26611158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84595 24                 </t>
+  </si>
+  <si>
+    <t>84595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETTOYANT INJECTION DIESEL 250 ML                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE JDM AUTO             </t>
+  </si>
+  <si>
+    <t>26410554</t>
+  </si>
+  <si>
+    <t>26611335</t>
+  </si>
+  <si>
+    <t>GGE MAPS AUTO GGE DESCHAM</t>
+  </si>
+  <si>
+    <t>26410841</t>
+  </si>
+  <si>
+    <t>26611699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGE LEXO PERF            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87091 00                 </t>
+  </si>
+  <si>
+    <t>87091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHIFFON DE FINITION - 40 X 40 PAQUET DE 3                    </t>
+  </si>
+  <si>
+    <t>26410842</t>
+  </si>
+  <si>
+    <t>26611700</t>
+  </si>
+  <si>
+    <t>26410967</t>
+  </si>
+  <si>
+    <t>26611828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE FORD PONT AUDEMER    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87215 00                 </t>
+  </si>
+  <si>
+    <t>87215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT JOINTS DE REMPLACEMENT POUR PULVERISATEUR 87214          </t>
+  </si>
+  <si>
+    <t>26410968</t>
+  </si>
+  <si>
+    <t>26611829</t>
+  </si>
+  <si>
+    <t>26411303</t>
+  </si>
+  <si>
+    <t>26612124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85742 22                 </t>
+  </si>
+  <si>
+    <t>85742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPARAFFINANT SUPER CO-POLYMER 25L                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE VHA              </t>
+  </si>
+  <si>
+    <t>Avril</t>
   </si>
 </sst>
 </file>
@@ -2293,7 +2515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W219"/>
+  <dimension ref="A1:W268"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -17869,6 +18091,3485 @@
         <v>626</v>
       </c>
     </row>
+    <row r="220" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>627</v>
+      </c>
+      <c r="B220" t="s">
+        <v>628</v>
+      </c>
+      <c r="C220" t="s">
+        <v>34</v>
+      </c>
+      <c r="D220" t="s">
+        <v>35</v>
+      </c>
+      <c r="E220" t="s">
+        <v>36</v>
+      </c>
+      <c r="F220" s="1">
+        <v>46115</v>
+      </c>
+      <c r="G220" t="s">
+        <v>287</v>
+      </c>
+      <c r="H220" t="s">
+        <v>288</v>
+      </c>
+      <c r="I220" t="s">
+        <v>289</v>
+      </c>
+      <c r="J220">
+        <v>12</v>
+      </c>
+      <c r="K220">
+        <v>10.8</v>
+      </c>
+      <c r="L220">
+        <v>129.6</v>
+      </c>
+      <c r="M220" t="s">
+        <v>22</v>
+      </c>
+      <c r="N220" t="s">
+        <v>23</v>
+      </c>
+      <c r="O220" s="1">
+        <v>46115</v>
+      </c>
+      <c r="P220" t="s">
+        <v>629</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>24</v>
+      </c>
+      <c r="R220" t="s">
+        <v>41</v>
+      </c>
+      <c r="S220" t="s">
+        <v>630</v>
+      </c>
+      <c r="T220" t="s">
+        <v>42</v>
+      </c>
+      <c r="U220" t="s">
+        <v>43</v>
+      </c>
+      <c r="V220" t="s">
+        <v>44</v>
+      </c>
+      <c r="W220" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>627</v>
+      </c>
+      <c r="B221" t="s">
+        <v>628</v>
+      </c>
+      <c r="C221" t="s">
+        <v>34</v>
+      </c>
+      <c r="D221" t="s">
+        <v>35</v>
+      </c>
+      <c r="E221" t="s">
+        <v>36</v>
+      </c>
+      <c r="F221" s="1">
+        <v>46115</v>
+      </c>
+      <c r="G221" t="s">
+        <v>414</v>
+      </c>
+      <c r="H221" t="s">
+        <v>415</v>
+      </c>
+      <c r="I221" t="s">
+        <v>416</v>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="K221">
+        <v>15.87</v>
+      </c>
+      <c r="L221">
+        <v>15.87</v>
+      </c>
+      <c r="M221" t="s">
+        <v>22</v>
+      </c>
+      <c r="N221" t="s">
+        <v>23</v>
+      </c>
+      <c r="O221" s="1">
+        <v>46115</v>
+      </c>
+      <c r="P221" t="s">
+        <v>629</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>24</v>
+      </c>
+      <c r="R221" t="s">
+        <v>41</v>
+      </c>
+      <c r="S221" t="s">
+        <v>630</v>
+      </c>
+      <c r="T221" t="s">
+        <v>42</v>
+      </c>
+      <c r="U221" t="s">
+        <v>43</v>
+      </c>
+      <c r="V221" t="s">
+        <v>44</v>
+      </c>
+      <c r="W221" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="222" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>631</v>
+      </c>
+      <c r="B222" t="s">
+        <v>632</v>
+      </c>
+      <c r="C222" t="s">
+        <v>34</v>
+      </c>
+      <c r="D222" t="s">
+        <v>35</v>
+      </c>
+      <c r="E222" t="s">
+        <v>36</v>
+      </c>
+      <c r="F222" s="1">
+        <v>46120</v>
+      </c>
+      <c r="G222" t="s">
+        <v>633</v>
+      </c>
+      <c r="H222" t="s">
+        <v>634</v>
+      </c>
+      <c r="I222" t="s">
+        <v>635</v>
+      </c>
+      <c r="J222">
+        <v>6</v>
+      </c>
+      <c r="K222">
+        <v>10.17</v>
+      </c>
+      <c r="L222">
+        <v>61.02</v>
+      </c>
+      <c r="M222" t="s">
+        <v>22</v>
+      </c>
+      <c r="N222" t="s">
+        <v>23</v>
+      </c>
+      <c r="O222" s="1">
+        <v>46119</v>
+      </c>
+      <c r="P222" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>24</v>
+      </c>
+      <c r="R222" t="s">
+        <v>41</v>
+      </c>
+      <c r="S222" t="s">
+        <v>630</v>
+      </c>
+      <c r="T222" t="s">
+        <v>42</v>
+      </c>
+      <c r="U222" t="s">
+        <v>43</v>
+      </c>
+      <c r="V222" t="s">
+        <v>44</v>
+      </c>
+      <c r="W222" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="223" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>637</v>
+      </c>
+      <c r="B223" t="s">
+        <v>638</v>
+      </c>
+      <c r="C223" t="s">
+        <v>34</v>
+      </c>
+      <c r="D223" t="s">
+        <v>35</v>
+      </c>
+      <c r="E223" t="s">
+        <v>36</v>
+      </c>
+      <c r="F223" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G223" t="s">
+        <v>37</v>
+      </c>
+      <c r="H223" t="s">
+        <v>38</v>
+      </c>
+      <c r="I223" t="s">
+        <v>39</v>
+      </c>
+      <c r="J223">
+        <v>5</v>
+      </c>
+      <c r="K223">
+        <v>17.63</v>
+      </c>
+      <c r="L223">
+        <v>88.15</v>
+      </c>
+      <c r="M223" t="s">
+        <v>22</v>
+      </c>
+      <c r="N223" t="s">
+        <v>23</v>
+      </c>
+      <c r="O223" s="1">
+        <v>46120</v>
+      </c>
+      <c r="P223" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>24</v>
+      </c>
+      <c r="R223" t="s">
+        <v>41</v>
+      </c>
+      <c r="S223" t="s">
+        <v>630</v>
+      </c>
+      <c r="T223" t="s">
+        <v>42</v>
+      </c>
+      <c r="U223" t="s">
+        <v>43</v>
+      </c>
+      <c r="V223" t="s">
+        <v>44</v>
+      </c>
+      <c r="W223" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="224" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>637</v>
+      </c>
+      <c r="B224" t="s">
+        <v>638</v>
+      </c>
+      <c r="C224" t="s">
+        <v>34</v>
+      </c>
+      <c r="D224" t="s">
+        <v>35</v>
+      </c>
+      <c r="E224" t="s">
+        <v>36</v>
+      </c>
+      <c r="F224" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G224" t="s">
+        <v>518</v>
+      </c>
+      <c r="H224" t="s">
+        <v>519</v>
+      </c>
+      <c r="I224" t="s">
+        <v>520</v>
+      </c>
+      <c r="J224">
+        <v>2</v>
+      </c>
+      <c r="K224">
+        <v>5.14</v>
+      </c>
+      <c r="L224">
+        <v>10.28</v>
+      </c>
+      <c r="M224" t="s">
+        <v>22</v>
+      </c>
+      <c r="N224" t="s">
+        <v>23</v>
+      </c>
+      <c r="O224" s="1">
+        <v>46120</v>
+      </c>
+      <c r="P224" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>24</v>
+      </c>
+      <c r="R224" t="s">
+        <v>41</v>
+      </c>
+      <c r="S224" t="s">
+        <v>630</v>
+      </c>
+      <c r="T224" t="s">
+        <v>42</v>
+      </c>
+      <c r="U224" t="s">
+        <v>43</v>
+      </c>
+      <c r="V224" t="s">
+        <v>44</v>
+      </c>
+      <c r="W224" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>637</v>
+      </c>
+      <c r="B225" t="s">
+        <v>638</v>
+      </c>
+      <c r="C225" t="s">
+        <v>34</v>
+      </c>
+      <c r="D225" t="s">
+        <v>35</v>
+      </c>
+      <c r="E225" t="s">
+        <v>36</v>
+      </c>
+      <c r="F225" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G225" t="s">
+        <v>63</v>
+      </c>
+      <c r="H225" t="s">
+        <v>64</v>
+      </c>
+      <c r="I225" t="s">
+        <v>65</v>
+      </c>
+      <c r="J225">
+        <v>2</v>
+      </c>
+      <c r="K225">
+        <v>7.39</v>
+      </c>
+      <c r="L225">
+        <v>14.78</v>
+      </c>
+      <c r="M225" t="s">
+        <v>22</v>
+      </c>
+      <c r="N225" t="s">
+        <v>23</v>
+      </c>
+      <c r="O225" s="1">
+        <v>46120</v>
+      </c>
+      <c r="P225" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>24</v>
+      </c>
+      <c r="R225" t="s">
+        <v>41</v>
+      </c>
+      <c r="S225" t="s">
+        <v>630</v>
+      </c>
+      <c r="T225" t="s">
+        <v>42</v>
+      </c>
+      <c r="U225" t="s">
+        <v>43</v>
+      </c>
+      <c r="V225" t="s">
+        <v>44</v>
+      </c>
+      <c r="W225" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="226" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>637</v>
+      </c>
+      <c r="B226" t="s">
+        <v>638</v>
+      </c>
+      <c r="C226" t="s">
+        <v>34</v>
+      </c>
+      <c r="D226" t="s">
+        <v>35</v>
+      </c>
+      <c r="E226" t="s">
+        <v>36</v>
+      </c>
+      <c r="F226" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G226" t="s">
+        <v>369</v>
+      </c>
+      <c r="H226" t="s">
+        <v>370</v>
+      </c>
+      <c r="I226" t="s">
+        <v>371</v>
+      </c>
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="K226">
+        <v>7.39</v>
+      </c>
+      <c r="L226">
+        <v>7.39</v>
+      </c>
+      <c r="M226" t="s">
+        <v>22</v>
+      </c>
+      <c r="N226" t="s">
+        <v>23</v>
+      </c>
+      <c r="O226" s="1">
+        <v>46120</v>
+      </c>
+      <c r="P226" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>24</v>
+      </c>
+      <c r="R226" t="s">
+        <v>41</v>
+      </c>
+      <c r="S226" t="s">
+        <v>630</v>
+      </c>
+      <c r="T226" t="s">
+        <v>42</v>
+      </c>
+      <c r="U226" t="s">
+        <v>43</v>
+      </c>
+      <c r="V226" t="s">
+        <v>44</v>
+      </c>
+      <c r="W226" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="227" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>637</v>
+      </c>
+      <c r="B227" t="s">
+        <v>638</v>
+      </c>
+      <c r="C227" t="s">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>35</v>
+      </c>
+      <c r="E227" t="s">
+        <v>36</v>
+      </c>
+      <c r="F227" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G227" t="s">
+        <v>579</v>
+      </c>
+      <c r="H227" t="s">
+        <v>580</v>
+      </c>
+      <c r="I227" t="s">
+        <v>581</v>
+      </c>
+      <c r="J227">
+        <v>2</v>
+      </c>
+      <c r="K227">
+        <v>6.6</v>
+      </c>
+      <c r="L227">
+        <v>13.2</v>
+      </c>
+      <c r="M227" t="s">
+        <v>22</v>
+      </c>
+      <c r="N227" t="s">
+        <v>23</v>
+      </c>
+      <c r="O227" s="1">
+        <v>46120</v>
+      </c>
+      <c r="P227" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>24</v>
+      </c>
+      <c r="R227" t="s">
+        <v>41</v>
+      </c>
+      <c r="S227" t="s">
+        <v>630</v>
+      </c>
+      <c r="T227" t="s">
+        <v>42</v>
+      </c>
+      <c r="U227" t="s">
+        <v>43</v>
+      </c>
+      <c r="V227" t="s">
+        <v>44</v>
+      </c>
+      <c r="W227" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="228" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>637</v>
+      </c>
+      <c r="B228" t="s">
+        <v>638</v>
+      </c>
+      <c r="C228" t="s">
+        <v>34</v>
+      </c>
+      <c r="D228" t="s">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>36</v>
+      </c>
+      <c r="F228" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G228" t="s">
+        <v>260</v>
+      </c>
+      <c r="H228" t="s">
+        <v>261</v>
+      </c>
+      <c r="I228" t="s">
+        <v>262</v>
+      </c>
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="K228">
+        <v>20.32</v>
+      </c>
+      <c r="L228">
+        <v>20.32</v>
+      </c>
+      <c r="M228" t="s">
+        <v>22</v>
+      </c>
+      <c r="N228" t="s">
+        <v>23</v>
+      </c>
+      <c r="O228" s="1">
+        <v>46120</v>
+      </c>
+      <c r="P228" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>24</v>
+      </c>
+      <c r="R228" t="s">
+        <v>41</v>
+      </c>
+      <c r="S228" t="s">
+        <v>630</v>
+      </c>
+      <c r="T228" t="s">
+        <v>42</v>
+      </c>
+      <c r="U228" t="s">
+        <v>43</v>
+      </c>
+      <c r="V228" t="s">
+        <v>44</v>
+      </c>
+      <c r="W228" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="229" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>637</v>
+      </c>
+      <c r="B229" t="s">
+        <v>638</v>
+      </c>
+      <c r="C229" t="s">
+        <v>34</v>
+      </c>
+      <c r="D229" t="s">
+        <v>35</v>
+      </c>
+      <c r="E229" t="s">
+        <v>36</v>
+      </c>
+      <c r="F229" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G229" t="s">
+        <v>460</v>
+      </c>
+      <c r="H229" t="s">
+        <v>461</v>
+      </c>
+      <c r="I229" t="s">
+        <v>462</v>
+      </c>
+      <c r="J229">
+        <v>2</v>
+      </c>
+      <c r="K229">
+        <v>13.12</v>
+      </c>
+      <c r="L229">
+        <v>26.24</v>
+      </c>
+      <c r="M229" t="s">
+        <v>22</v>
+      </c>
+      <c r="N229" t="s">
+        <v>23</v>
+      </c>
+      <c r="O229" s="1">
+        <v>46120</v>
+      </c>
+      <c r="P229" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>24</v>
+      </c>
+      <c r="R229" t="s">
+        <v>41</v>
+      </c>
+      <c r="S229" t="s">
+        <v>630</v>
+      </c>
+      <c r="T229" t="s">
+        <v>42</v>
+      </c>
+      <c r="U229" t="s">
+        <v>43</v>
+      </c>
+      <c r="V229" t="s">
+        <v>44</v>
+      </c>
+      <c r="W229" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>637</v>
+      </c>
+      <c r="B230" t="s">
+        <v>638</v>
+      </c>
+      <c r="C230" t="s">
+        <v>34</v>
+      </c>
+      <c r="D230" t="s">
+        <v>35</v>
+      </c>
+      <c r="E230" t="s">
+        <v>36</v>
+      </c>
+      <c r="F230" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G230" t="s">
+        <v>405</v>
+      </c>
+      <c r="H230" t="s">
+        <v>406</v>
+      </c>
+      <c r="I230" t="s">
+        <v>407</v>
+      </c>
+      <c r="J230">
+        <v>1</v>
+      </c>
+      <c r="K230">
+        <v>28.29</v>
+      </c>
+      <c r="L230">
+        <v>28.29</v>
+      </c>
+      <c r="M230" t="s">
+        <v>22</v>
+      </c>
+      <c r="N230" t="s">
+        <v>23</v>
+      </c>
+      <c r="O230" s="1">
+        <v>46120</v>
+      </c>
+      <c r="P230" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>24</v>
+      </c>
+      <c r="R230" t="s">
+        <v>41</v>
+      </c>
+      <c r="S230" t="s">
+        <v>630</v>
+      </c>
+      <c r="T230" t="s">
+        <v>42</v>
+      </c>
+      <c r="U230" t="s">
+        <v>43</v>
+      </c>
+      <c r="V230" t="s">
+        <v>44</v>
+      </c>
+      <c r="W230" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>640</v>
+      </c>
+      <c r="B231" t="s">
+        <v>641</v>
+      </c>
+      <c r="C231" t="s">
+        <v>34</v>
+      </c>
+      <c r="D231" t="s">
+        <v>35</v>
+      </c>
+      <c r="E231" t="s">
+        <v>36</v>
+      </c>
+      <c r="F231" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G231" t="s">
+        <v>29</v>
+      </c>
+      <c r="H231" t="s">
+        <v>30</v>
+      </c>
+      <c r="I231" t="s">
+        <v>31</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="L231">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="M231" t="s">
+        <v>22</v>
+      </c>
+      <c r="N231" t="s">
+        <v>23</v>
+      </c>
+      <c r="O231" s="1">
+        <v>46126</v>
+      </c>
+      <c r="P231" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>24</v>
+      </c>
+      <c r="R231" t="s">
+        <v>41</v>
+      </c>
+      <c r="S231" t="s">
+        <v>630</v>
+      </c>
+      <c r="T231" t="s">
+        <v>42</v>
+      </c>
+      <c r="U231" t="s">
+        <v>43</v>
+      </c>
+      <c r="V231" t="s">
+        <v>44</v>
+      </c>
+      <c r="W231" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>640</v>
+      </c>
+      <c r="B232" t="s">
+        <v>641</v>
+      </c>
+      <c r="C232" t="s">
+        <v>34</v>
+      </c>
+      <c r="D232" t="s">
+        <v>35</v>
+      </c>
+      <c r="E232" t="s">
+        <v>36</v>
+      </c>
+      <c r="F232" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G232" t="s">
+        <v>642</v>
+      </c>
+      <c r="H232" t="s">
+        <v>643</v>
+      </c>
+      <c r="I232" t="s">
+        <v>644</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>10.63</v>
+      </c>
+      <c r="L232">
+        <v>10.63</v>
+      </c>
+      <c r="M232" t="s">
+        <v>22</v>
+      </c>
+      <c r="N232" t="s">
+        <v>23</v>
+      </c>
+      <c r="O232" s="1">
+        <v>46126</v>
+      </c>
+      <c r="P232" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>24</v>
+      </c>
+      <c r="R232" t="s">
+        <v>41</v>
+      </c>
+      <c r="S232" t="s">
+        <v>630</v>
+      </c>
+      <c r="T232" t="s">
+        <v>42</v>
+      </c>
+      <c r="U232" t="s">
+        <v>43</v>
+      </c>
+      <c r="V232" t="s">
+        <v>44</v>
+      </c>
+      <c r="W232" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>640</v>
+      </c>
+      <c r="B233" t="s">
+        <v>641</v>
+      </c>
+      <c r="C233" t="s">
+        <v>34</v>
+      </c>
+      <c r="D233" t="s">
+        <v>35</v>
+      </c>
+      <c r="E233" t="s">
+        <v>36</v>
+      </c>
+      <c r="F233" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G233" t="s">
+        <v>414</v>
+      </c>
+      <c r="H233" t="s">
+        <v>415</v>
+      </c>
+      <c r="I233" t="s">
+        <v>416</v>
+      </c>
+      <c r="J233">
+        <v>4</v>
+      </c>
+      <c r="K233">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="L233">
+        <v>66.680000000000007</v>
+      </c>
+      <c r="M233" t="s">
+        <v>22</v>
+      </c>
+      <c r="N233" t="s">
+        <v>23</v>
+      </c>
+      <c r="O233" s="1">
+        <v>46126</v>
+      </c>
+      <c r="P233" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>24</v>
+      </c>
+      <c r="R233" t="s">
+        <v>41</v>
+      </c>
+      <c r="S233" t="s">
+        <v>630</v>
+      </c>
+      <c r="T233" t="s">
+        <v>42</v>
+      </c>
+      <c r="U233" t="s">
+        <v>43</v>
+      </c>
+      <c r="V233" t="s">
+        <v>44</v>
+      </c>
+      <c r="W233" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>645</v>
+      </c>
+      <c r="B234" t="s">
+        <v>646</v>
+      </c>
+      <c r="C234" t="s">
+        <v>34</v>
+      </c>
+      <c r="D234" t="s">
+        <v>35</v>
+      </c>
+      <c r="E234" t="s">
+        <v>36</v>
+      </c>
+      <c r="F234" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G234" t="s">
+        <v>89</v>
+      </c>
+      <c r="H234" t="s">
+        <v>90</v>
+      </c>
+      <c r="I234" t="s">
+        <v>91</v>
+      </c>
+      <c r="J234">
+        <v>1</v>
+      </c>
+      <c r="K234">
+        <v>15.02</v>
+      </c>
+      <c r="L234">
+        <v>15.02</v>
+      </c>
+      <c r="M234" t="s">
+        <v>22</v>
+      </c>
+      <c r="N234" t="s">
+        <v>23</v>
+      </c>
+      <c r="O234" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P234" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>24</v>
+      </c>
+      <c r="R234" t="s">
+        <v>41</v>
+      </c>
+      <c r="S234" t="s">
+        <v>630</v>
+      </c>
+      <c r="T234" t="s">
+        <v>42</v>
+      </c>
+      <c r="U234" t="s">
+        <v>43</v>
+      </c>
+      <c r="V234" t="s">
+        <v>44</v>
+      </c>
+      <c r="W234" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>645</v>
+      </c>
+      <c r="B235" t="s">
+        <v>646</v>
+      </c>
+      <c r="C235" t="s">
+        <v>34</v>
+      </c>
+      <c r="D235" t="s">
+        <v>35</v>
+      </c>
+      <c r="E235" t="s">
+        <v>36</v>
+      </c>
+      <c r="F235" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G235" t="s">
+        <v>648</v>
+      </c>
+      <c r="H235" t="s">
+        <v>649</v>
+      </c>
+      <c r="I235" t="s">
+        <v>650</v>
+      </c>
+      <c r="J235">
+        <v>4</v>
+      </c>
+      <c r="K235">
+        <v>19.78</v>
+      </c>
+      <c r="L235">
+        <v>79.12</v>
+      </c>
+      <c r="M235" t="s">
+        <v>22</v>
+      </c>
+      <c r="N235" t="s">
+        <v>23</v>
+      </c>
+      <c r="O235" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P235" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>24</v>
+      </c>
+      <c r="R235" t="s">
+        <v>41</v>
+      </c>
+      <c r="S235" t="s">
+        <v>630</v>
+      </c>
+      <c r="T235" t="s">
+        <v>42</v>
+      </c>
+      <c r="U235" t="s">
+        <v>43</v>
+      </c>
+      <c r="V235" t="s">
+        <v>44</v>
+      </c>
+      <c r="W235" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>645</v>
+      </c>
+      <c r="B236" t="s">
+        <v>646</v>
+      </c>
+      <c r="C236" t="s">
+        <v>34</v>
+      </c>
+      <c r="D236" t="s">
+        <v>35</v>
+      </c>
+      <c r="E236" t="s">
+        <v>36</v>
+      </c>
+      <c r="F236" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G236" t="s">
+        <v>651</v>
+      </c>
+      <c r="H236" t="s">
+        <v>652</v>
+      </c>
+      <c r="I236" t="s">
+        <v>653</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>11.99</v>
+      </c>
+      <c r="L236">
+        <v>11.99</v>
+      </c>
+      <c r="M236" t="s">
+        <v>22</v>
+      </c>
+      <c r="N236" t="s">
+        <v>23</v>
+      </c>
+      <c r="O236" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P236" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>24</v>
+      </c>
+      <c r="R236" t="s">
+        <v>41</v>
+      </c>
+      <c r="S236" t="s">
+        <v>630</v>
+      </c>
+      <c r="T236" t="s">
+        <v>42</v>
+      </c>
+      <c r="U236" t="s">
+        <v>43</v>
+      </c>
+      <c r="V236" t="s">
+        <v>44</v>
+      </c>
+      <c r="W236" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>645</v>
+      </c>
+      <c r="B237" t="s">
+        <v>646</v>
+      </c>
+      <c r="C237" t="s">
+        <v>34</v>
+      </c>
+      <c r="D237" t="s">
+        <v>35</v>
+      </c>
+      <c r="E237" t="s">
+        <v>36</v>
+      </c>
+      <c r="F237" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G237" t="s">
+        <v>93</v>
+      </c>
+      <c r="H237" t="s">
+        <v>94</v>
+      </c>
+      <c r="I237" t="s">
+        <v>95</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>13.72</v>
+      </c>
+      <c r="L237">
+        <v>13.72</v>
+      </c>
+      <c r="M237" t="s">
+        <v>22</v>
+      </c>
+      <c r="N237" t="s">
+        <v>23</v>
+      </c>
+      <c r="O237" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P237" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>24</v>
+      </c>
+      <c r="R237" t="s">
+        <v>41</v>
+      </c>
+      <c r="S237" t="s">
+        <v>630</v>
+      </c>
+      <c r="T237" t="s">
+        <v>42</v>
+      </c>
+      <c r="U237" t="s">
+        <v>43</v>
+      </c>
+      <c r="V237" t="s">
+        <v>44</v>
+      </c>
+      <c r="W237" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>645</v>
+      </c>
+      <c r="B238" t="s">
+        <v>646</v>
+      </c>
+      <c r="C238" t="s">
+        <v>34</v>
+      </c>
+      <c r="D238" t="s">
+        <v>35</v>
+      </c>
+      <c r="E238" t="s">
+        <v>36</v>
+      </c>
+      <c r="F238" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G238" t="s">
+        <v>294</v>
+      </c>
+      <c r="H238" t="s">
+        <v>295</v>
+      </c>
+      <c r="I238" t="s">
+        <v>296</v>
+      </c>
+      <c r="J238">
+        <v>2</v>
+      </c>
+      <c r="K238">
+        <v>8.76</v>
+      </c>
+      <c r="L238">
+        <v>17.52</v>
+      </c>
+      <c r="M238" t="s">
+        <v>22</v>
+      </c>
+      <c r="N238" t="s">
+        <v>23</v>
+      </c>
+      <c r="O238" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P238" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>24</v>
+      </c>
+      <c r="R238" t="s">
+        <v>41</v>
+      </c>
+      <c r="S238" t="s">
+        <v>630</v>
+      </c>
+      <c r="T238" t="s">
+        <v>42</v>
+      </c>
+      <c r="U238" t="s">
+        <v>43</v>
+      </c>
+      <c r="V238" t="s">
+        <v>44</v>
+      </c>
+      <c r="W238" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>645</v>
+      </c>
+      <c r="B239" t="s">
+        <v>646</v>
+      </c>
+      <c r="C239" t="s">
+        <v>34</v>
+      </c>
+      <c r="D239" t="s">
+        <v>35</v>
+      </c>
+      <c r="E239" t="s">
+        <v>36</v>
+      </c>
+      <c r="F239" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G239" t="s">
+        <v>654</v>
+      </c>
+      <c r="H239" t="s">
+        <v>655</v>
+      </c>
+      <c r="I239" t="s">
+        <v>656</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239">
+        <v>20.45</v>
+      </c>
+      <c r="L239">
+        <v>20.45</v>
+      </c>
+      <c r="M239" t="s">
+        <v>22</v>
+      </c>
+      <c r="N239" t="s">
+        <v>23</v>
+      </c>
+      <c r="O239" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P239" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>24</v>
+      </c>
+      <c r="R239" t="s">
+        <v>41</v>
+      </c>
+      <c r="S239" t="s">
+        <v>630</v>
+      </c>
+      <c r="T239" t="s">
+        <v>42</v>
+      </c>
+      <c r="U239" t="s">
+        <v>43</v>
+      </c>
+      <c r="V239" t="s">
+        <v>44</v>
+      </c>
+      <c r="W239" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>645</v>
+      </c>
+      <c r="B240" t="s">
+        <v>646</v>
+      </c>
+      <c r="C240" t="s">
+        <v>34</v>
+      </c>
+      <c r="D240" t="s">
+        <v>35</v>
+      </c>
+      <c r="E240" t="s">
+        <v>36</v>
+      </c>
+      <c r="F240" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G240" t="s">
+        <v>657</v>
+      </c>
+      <c r="H240" t="s">
+        <v>658</v>
+      </c>
+      <c r="I240" t="s">
+        <v>659</v>
+      </c>
+      <c r="J240">
+        <v>1</v>
+      </c>
+      <c r="K240">
+        <v>20.45</v>
+      </c>
+      <c r="L240">
+        <v>20.45</v>
+      </c>
+      <c r="M240" t="s">
+        <v>22</v>
+      </c>
+      <c r="N240" t="s">
+        <v>23</v>
+      </c>
+      <c r="O240" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P240" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>24</v>
+      </c>
+      <c r="R240" t="s">
+        <v>41</v>
+      </c>
+      <c r="S240" t="s">
+        <v>630</v>
+      </c>
+      <c r="T240" t="s">
+        <v>42</v>
+      </c>
+      <c r="U240" t="s">
+        <v>43</v>
+      </c>
+      <c r="V240" t="s">
+        <v>44</v>
+      </c>
+      <c r="W240" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>645</v>
+      </c>
+      <c r="B241" t="s">
+        <v>646</v>
+      </c>
+      <c r="C241" t="s">
+        <v>34</v>
+      </c>
+      <c r="D241" t="s">
+        <v>35</v>
+      </c>
+      <c r="E241" t="s">
+        <v>36</v>
+      </c>
+      <c r="F241" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G241" t="s">
+        <v>660</v>
+      </c>
+      <c r="H241" t="s">
+        <v>661</v>
+      </c>
+      <c r="I241" t="s">
+        <v>662</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>24.55</v>
+      </c>
+      <c r="L241">
+        <v>24.55</v>
+      </c>
+      <c r="M241" t="s">
+        <v>22</v>
+      </c>
+      <c r="N241" t="s">
+        <v>23</v>
+      </c>
+      <c r="O241" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P241" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>24</v>
+      </c>
+      <c r="R241" t="s">
+        <v>41</v>
+      </c>
+      <c r="S241" t="s">
+        <v>630</v>
+      </c>
+      <c r="T241" t="s">
+        <v>42</v>
+      </c>
+      <c r="U241" t="s">
+        <v>43</v>
+      </c>
+      <c r="V241" t="s">
+        <v>44</v>
+      </c>
+      <c r="W241" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>645</v>
+      </c>
+      <c r="B242" t="s">
+        <v>646</v>
+      </c>
+      <c r="C242" t="s">
+        <v>34</v>
+      </c>
+      <c r="D242" t="s">
+        <v>35</v>
+      </c>
+      <c r="E242" t="s">
+        <v>36</v>
+      </c>
+      <c r="F242" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G242" t="s">
+        <v>199</v>
+      </c>
+      <c r="H242" t="s">
+        <v>200</v>
+      </c>
+      <c r="I242" t="s">
+        <v>201</v>
+      </c>
+      <c r="J242">
+        <v>1</v>
+      </c>
+      <c r="K242">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="L242">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="M242" t="s">
+        <v>22</v>
+      </c>
+      <c r="N242" t="s">
+        <v>23</v>
+      </c>
+      <c r="O242" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P242" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>24</v>
+      </c>
+      <c r="R242" t="s">
+        <v>41</v>
+      </c>
+      <c r="S242" t="s">
+        <v>630</v>
+      </c>
+      <c r="T242" t="s">
+        <v>42</v>
+      </c>
+      <c r="U242" t="s">
+        <v>43</v>
+      </c>
+      <c r="V242" t="s">
+        <v>44</v>
+      </c>
+      <c r="W242" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>645</v>
+      </c>
+      <c r="B243" t="s">
+        <v>646</v>
+      </c>
+      <c r="C243" t="s">
+        <v>34</v>
+      </c>
+      <c r="D243" t="s">
+        <v>35</v>
+      </c>
+      <c r="E243" t="s">
+        <v>36</v>
+      </c>
+      <c r="F243" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G243" t="s">
+        <v>209</v>
+      </c>
+      <c r="H243" t="s">
+        <v>210</v>
+      </c>
+      <c r="I243" t="s">
+        <v>211</v>
+      </c>
+      <c r="J243">
+        <v>2</v>
+      </c>
+      <c r="K243">
+        <v>39.71</v>
+      </c>
+      <c r="L243">
+        <v>79.42</v>
+      </c>
+      <c r="M243" t="s">
+        <v>22</v>
+      </c>
+      <c r="N243" t="s">
+        <v>23</v>
+      </c>
+      <c r="O243" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P243" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>24</v>
+      </c>
+      <c r="R243" t="s">
+        <v>41</v>
+      </c>
+      <c r="S243" t="s">
+        <v>630</v>
+      </c>
+      <c r="T243" t="s">
+        <v>42</v>
+      </c>
+      <c r="U243" t="s">
+        <v>43</v>
+      </c>
+      <c r="V243" t="s">
+        <v>44</v>
+      </c>
+      <c r="W243" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>645</v>
+      </c>
+      <c r="B244" t="s">
+        <v>646</v>
+      </c>
+      <c r="C244" t="s">
+        <v>34</v>
+      </c>
+      <c r="D244" t="s">
+        <v>35</v>
+      </c>
+      <c r="E244" t="s">
+        <v>36</v>
+      </c>
+      <c r="F244" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G244" t="s">
+        <v>529</v>
+      </c>
+      <c r="H244" t="s">
+        <v>530</v>
+      </c>
+      <c r="I244" t="s">
+        <v>531</v>
+      </c>
+      <c r="J244">
+        <v>2</v>
+      </c>
+      <c r="K244">
+        <v>12.86</v>
+      </c>
+      <c r="L244">
+        <v>25.72</v>
+      </c>
+      <c r="M244" t="s">
+        <v>22</v>
+      </c>
+      <c r="N244" t="s">
+        <v>23</v>
+      </c>
+      <c r="O244" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P244" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>24</v>
+      </c>
+      <c r="R244" t="s">
+        <v>41</v>
+      </c>
+      <c r="S244" t="s">
+        <v>630</v>
+      </c>
+      <c r="T244" t="s">
+        <v>42</v>
+      </c>
+      <c r="U244" t="s">
+        <v>43</v>
+      </c>
+      <c r="V244" t="s">
+        <v>44</v>
+      </c>
+      <c r="W244" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>645</v>
+      </c>
+      <c r="B245" t="s">
+        <v>646</v>
+      </c>
+      <c r="C245" t="s">
+        <v>34</v>
+      </c>
+      <c r="D245" t="s">
+        <v>35</v>
+      </c>
+      <c r="E245" t="s">
+        <v>36</v>
+      </c>
+      <c r="F245" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G245" t="s">
+        <v>539</v>
+      </c>
+      <c r="H245" t="s">
+        <v>540</v>
+      </c>
+      <c r="I245" t="s">
+        <v>541</v>
+      </c>
+      <c r="J245">
+        <v>2</v>
+      </c>
+      <c r="K245">
+        <v>12.86</v>
+      </c>
+      <c r="L245">
+        <v>25.72</v>
+      </c>
+      <c r="M245" t="s">
+        <v>22</v>
+      </c>
+      <c r="N245" t="s">
+        <v>23</v>
+      </c>
+      <c r="O245" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P245" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>24</v>
+      </c>
+      <c r="R245" t="s">
+        <v>41</v>
+      </c>
+      <c r="S245" t="s">
+        <v>630</v>
+      </c>
+      <c r="T245" t="s">
+        <v>42</v>
+      </c>
+      <c r="U245" t="s">
+        <v>43</v>
+      </c>
+      <c r="V245" t="s">
+        <v>44</v>
+      </c>
+      <c r="W245" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>645</v>
+      </c>
+      <c r="B246" t="s">
+        <v>646</v>
+      </c>
+      <c r="C246" t="s">
+        <v>34</v>
+      </c>
+      <c r="D246" t="s">
+        <v>35</v>
+      </c>
+      <c r="E246" t="s">
+        <v>36</v>
+      </c>
+      <c r="F246" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G246" t="s">
+        <v>29</v>
+      </c>
+      <c r="H246" t="s">
+        <v>30</v>
+      </c>
+      <c r="I246" t="s">
+        <v>31</v>
+      </c>
+      <c r="J246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="L246">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="M246" t="s">
+        <v>22</v>
+      </c>
+      <c r="N246" t="s">
+        <v>23</v>
+      </c>
+      <c r="O246" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P246" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>24</v>
+      </c>
+      <c r="R246" t="s">
+        <v>41</v>
+      </c>
+      <c r="S246" t="s">
+        <v>630</v>
+      </c>
+      <c r="T246" t="s">
+        <v>42</v>
+      </c>
+      <c r="U246" t="s">
+        <v>43</v>
+      </c>
+      <c r="V246" t="s">
+        <v>44</v>
+      </c>
+      <c r="W246" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>645</v>
+      </c>
+      <c r="B247" t="s">
+        <v>646</v>
+      </c>
+      <c r="C247" t="s">
+        <v>34</v>
+      </c>
+      <c r="D247" t="s">
+        <v>35</v>
+      </c>
+      <c r="E247" t="s">
+        <v>36</v>
+      </c>
+      <c r="F247" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G247" t="s">
+        <v>663</v>
+      </c>
+      <c r="H247" t="s">
+        <v>664</v>
+      </c>
+      <c r="I247" t="s">
+        <v>665</v>
+      </c>
+      <c r="J247">
+        <v>4</v>
+      </c>
+      <c r="K247">
+        <v>15.85</v>
+      </c>
+      <c r="L247">
+        <v>63.4</v>
+      </c>
+      <c r="M247" t="s">
+        <v>22</v>
+      </c>
+      <c r="N247" t="s">
+        <v>23</v>
+      </c>
+      <c r="O247" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P247" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>24</v>
+      </c>
+      <c r="R247" t="s">
+        <v>41</v>
+      </c>
+      <c r="S247" t="s">
+        <v>630</v>
+      </c>
+      <c r="T247" t="s">
+        <v>42</v>
+      </c>
+      <c r="U247" t="s">
+        <v>43</v>
+      </c>
+      <c r="V247" t="s">
+        <v>44</v>
+      </c>
+      <c r="W247" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>645</v>
+      </c>
+      <c r="B248" t="s">
+        <v>646</v>
+      </c>
+      <c r="C248" t="s">
+        <v>34</v>
+      </c>
+      <c r="D248" t="s">
+        <v>35</v>
+      </c>
+      <c r="E248" t="s">
+        <v>36</v>
+      </c>
+      <c r="F248" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G248" t="s">
+        <v>666</v>
+      </c>
+      <c r="H248" t="s">
+        <v>667</v>
+      </c>
+      <c r="I248" t="s">
+        <v>668</v>
+      </c>
+      <c r="J248">
+        <v>1</v>
+      </c>
+      <c r="K248">
+        <v>22.48</v>
+      </c>
+      <c r="L248">
+        <v>22.48</v>
+      </c>
+      <c r="M248" t="s">
+        <v>22</v>
+      </c>
+      <c r="N248" t="s">
+        <v>23</v>
+      </c>
+      <c r="O248" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P248" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>24</v>
+      </c>
+      <c r="R248" t="s">
+        <v>41</v>
+      </c>
+      <c r="S248" t="s">
+        <v>630</v>
+      </c>
+      <c r="T248" t="s">
+        <v>42</v>
+      </c>
+      <c r="U248" t="s">
+        <v>43</v>
+      </c>
+      <c r="V248" t="s">
+        <v>44</v>
+      </c>
+      <c r="W248" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>645</v>
+      </c>
+      <c r="B249" t="s">
+        <v>646</v>
+      </c>
+      <c r="C249" t="s">
+        <v>34</v>
+      </c>
+      <c r="D249" t="s">
+        <v>35</v>
+      </c>
+      <c r="E249" t="s">
+        <v>36</v>
+      </c>
+      <c r="F249" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G249" t="s">
+        <v>221</v>
+      </c>
+      <c r="H249" t="s">
+        <v>222</v>
+      </c>
+      <c r="I249" t="s">
+        <v>223</v>
+      </c>
+      <c r="J249">
+        <v>4</v>
+      </c>
+      <c r="K249">
+        <v>15.13</v>
+      </c>
+      <c r="L249">
+        <v>60.52</v>
+      </c>
+      <c r="M249" t="s">
+        <v>22</v>
+      </c>
+      <c r="N249" t="s">
+        <v>23</v>
+      </c>
+      <c r="O249" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P249" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>24</v>
+      </c>
+      <c r="R249" t="s">
+        <v>41</v>
+      </c>
+      <c r="S249" t="s">
+        <v>630</v>
+      </c>
+      <c r="T249" t="s">
+        <v>42</v>
+      </c>
+      <c r="U249" t="s">
+        <v>43</v>
+      </c>
+      <c r="V249" t="s">
+        <v>44</v>
+      </c>
+      <c r="W249" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>645</v>
+      </c>
+      <c r="B250" t="s">
+        <v>646</v>
+      </c>
+      <c r="C250" t="s">
+        <v>34</v>
+      </c>
+      <c r="D250" t="s">
+        <v>35</v>
+      </c>
+      <c r="E250" t="s">
+        <v>36</v>
+      </c>
+      <c r="F250" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G250" t="s">
+        <v>26</v>
+      </c>
+      <c r="H250" t="s">
+        <v>27</v>
+      </c>
+      <c r="I250" t="s">
+        <v>28</v>
+      </c>
+      <c r="J250">
+        <v>36</v>
+      </c>
+      <c r="K250">
+        <v>2.69</v>
+      </c>
+      <c r="L250">
+        <v>96.84</v>
+      </c>
+      <c r="M250" t="s">
+        <v>22</v>
+      </c>
+      <c r="N250" t="s">
+        <v>23</v>
+      </c>
+      <c r="O250" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P250" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>24</v>
+      </c>
+      <c r="R250" t="s">
+        <v>41</v>
+      </c>
+      <c r="S250" t="s">
+        <v>630</v>
+      </c>
+      <c r="T250" t="s">
+        <v>42</v>
+      </c>
+      <c r="U250" t="s">
+        <v>43</v>
+      </c>
+      <c r="V250" t="s">
+        <v>44</v>
+      </c>
+      <c r="W250" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>645</v>
+      </c>
+      <c r="B251" t="s">
+        <v>646</v>
+      </c>
+      <c r="C251" t="s">
+        <v>34</v>
+      </c>
+      <c r="D251" t="s">
+        <v>35</v>
+      </c>
+      <c r="E251" t="s">
+        <v>36</v>
+      </c>
+      <c r="F251" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G251" t="s">
+        <v>111</v>
+      </c>
+      <c r="H251" t="s">
+        <v>112</v>
+      </c>
+      <c r="I251" t="s">
+        <v>113</v>
+      </c>
+      <c r="J251">
+        <v>5</v>
+      </c>
+      <c r="K251">
+        <v>11.43</v>
+      </c>
+      <c r="L251">
+        <v>57.15</v>
+      </c>
+      <c r="M251" t="s">
+        <v>22</v>
+      </c>
+      <c r="N251" t="s">
+        <v>23</v>
+      </c>
+      <c r="O251" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P251" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>24</v>
+      </c>
+      <c r="R251" t="s">
+        <v>41</v>
+      </c>
+      <c r="S251" t="s">
+        <v>630</v>
+      </c>
+      <c r="T251" t="s">
+        <v>42</v>
+      </c>
+      <c r="U251" t="s">
+        <v>43</v>
+      </c>
+      <c r="V251" t="s">
+        <v>44</v>
+      </c>
+      <c r="W251" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>669</v>
+      </c>
+      <c r="B252" t="s">
+        <v>670</v>
+      </c>
+      <c r="C252" t="s">
+        <v>34</v>
+      </c>
+      <c r="D252" t="s">
+        <v>35</v>
+      </c>
+      <c r="E252" t="s">
+        <v>36</v>
+      </c>
+      <c r="F252" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G252" t="s">
+        <v>671</v>
+      </c>
+      <c r="H252" t="s">
+        <v>672</v>
+      </c>
+      <c r="I252" t="s">
+        <v>673</v>
+      </c>
+      <c r="J252">
+        <v>5</v>
+      </c>
+      <c r="K252">
+        <v>15.59</v>
+      </c>
+      <c r="L252">
+        <v>77.95</v>
+      </c>
+      <c r="M252" t="s">
+        <v>22</v>
+      </c>
+      <c r="N252" t="s">
+        <v>23</v>
+      </c>
+      <c r="O252" s="1">
+        <v>46127</v>
+      </c>
+      <c r="P252" t="s">
+        <v>674</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>24</v>
+      </c>
+      <c r="R252" t="s">
+        <v>41</v>
+      </c>
+      <c r="S252" t="s">
+        <v>630</v>
+      </c>
+      <c r="T252" t="s">
+        <v>42</v>
+      </c>
+      <c r="U252" t="s">
+        <v>43</v>
+      </c>
+      <c r="V252" t="s">
+        <v>44</v>
+      </c>
+      <c r="W252" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>675</v>
+      </c>
+      <c r="B253" t="s">
+        <v>676</v>
+      </c>
+      <c r="C253" t="s">
+        <v>34</v>
+      </c>
+      <c r="D253" t="s">
+        <v>35</v>
+      </c>
+      <c r="E253" t="s">
+        <v>36</v>
+      </c>
+      <c r="F253" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G253" t="s">
+        <v>287</v>
+      </c>
+      <c r="H253" t="s">
+        <v>288</v>
+      </c>
+      <c r="I253" t="s">
+        <v>289</v>
+      </c>
+      <c r="J253">
+        <v>12</v>
+      </c>
+      <c r="K253">
+        <v>11.1</v>
+      </c>
+      <c r="L253">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="M253" t="s">
+        <v>22</v>
+      </c>
+      <c r="N253" t="s">
+        <v>23</v>
+      </c>
+      <c r="O253" s="1">
+        <v>46128</v>
+      </c>
+      <c r="P253" t="s">
+        <v>677</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>24</v>
+      </c>
+      <c r="R253" t="s">
+        <v>41</v>
+      </c>
+      <c r="S253" t="s">
+        <v>630</v>
+      </c>
+      <c r="T253" t="s">
+        <v>42</v>
+      </c>
+      <c r="U253" t="s">
+        <v>43</v>
+      </c>
+      <c r="V253" t="s">
+        <v>44</v>
+      </c>
+      <c r="W253" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>678</v>
+      </c>
+      <c r="B254" t="s">
+        <v>679</v>
+      </c>
+      <c r="C254" t="s">
+        <v>34</v>
+      </c>
+      <c r="D254" t="s">
+        <v>35</v>
+      </c>
+      <c r="E254" t="s">
+        <v>36</v>
+      </c>
+      <c r="F254" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G254" t="s">
+        <v>287</v>
+      </c>
+      <c r="H254" t="s">
+        <v>288</v>
+      </c>
+      <c r="I254" t="s">
+        <v>289</v>
+      </c>
+      <c r="J254">
+        <v>12</v>
+      </c>
+      <c r="K254">
+        <v>11.1</v>
+      </c>
+      <c r="L254">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="M254" t="s">
+        <v>22</v>
+      </c>
+      <c r="N254" t="s">
+        <v>23</v>
+      </c>
+      <c r="O254" s="1">
+        <v>46129</v>
+      </c>
+      <c r="P254" t="s">
+        <v>680</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>24</v>
+      </c>
+      <c r="R254" t="s">
+        <v>41</v>
+      </c>
+      <c r="S254" t="s">
+        <v>630</v>
+      </c>
+      <c r="T254" t="s">
+        <v>42</v>
+      </c>
+      <c r="U254" t="s">
+        <v>43</v>
+      </c>
+      <c r="V254" t="s">
+        <v>44</v>
+      </c>
+      <c r="W254" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>678</v>
+      </c>
+      <c r="B255" t="s">
+        <v>679</v>
+      </c>
+      <c r="C255" t="s">
+        <v>34</v>
+      </c>
+      <c r="D255" t="s">
+        <v>35</v>
+      </c>
+      <c r="E255" t="s">
+        <v>36</v>
+      </c>
+      <c r="F255" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G255" t="s">
+        <v>185</v>
+      </c>
+      <c r="H255" t="s">
+        <v>186</v>
+      </c>
+      <c r="I255" t="s">
+        <v>187</v>
+      </c>
+      <c r="J255">
+        <v>2</v>
+      </c>
+      <c r="K255">
+        <v>7.49</v>
+      </c>
+      <c r="L255">
+        <v>14.98</v>
+      </c>
+      <c r="M255" t="s">
+        <v>22</v>
+      </c>
+      <c r="N255" t="s">
+        <v>23</v>
+      </c>
+      <c r="O255" s="1">
+        <v>46129</v>
+      </c>
+      <c r="P255" t="s">
+        <v>680</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>24</v>
+      </c>
+      <c r="R255" t="s">
+        <v>41</v>
+      </c>
+      <c r="S255" t="s">
+        <v>630</v>
+      </c>
+      <c r="T255" t="s">
+        <v>42</v>
+      </c>
+      <c r="U255" t="s">
+        <v>43</v>
+      </c>
+      <c r="V255" t="s">
+        <v>44</v>
+      </c>
+      <c r="W255" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>678</v>
+      </c>
+      <c r="B256" t="s">
+        <v>679</v>
+      </c>
+      <c r="C256" t="s">
+        <v>34</v>
+      </c>
+      <c r="D256" t="s">
+        <v>35</v>
+      </c>
+      <c r="E256" t="s">
+        <v>36</v>
+      </c>
+      <c r="F256" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G256" t="s">
+        <v>381</v>
+      </c>
+      <c r="H256" t="s">
+        <v>382</v>
+      </c>
+      <c r="I256" t="s">
+        <v>383</v>
+      </c>
+      <c r="J256">
+        <v>1</v>
+      </c>
+      <c r="K256">
+        <v>22.68</v>
+      </c>
+      <c r="L256">
+        <v>22.68</v>
+      </c>
+      <c r="M256" t="s">
+        <v>22</v>
+      </c>
+      <c r="N256" t="s">
+        <v>23</v>
+      </c>
+      <c r="O256" s="1">
+        <v>46129</v>
+      </c>
+      <c r="P256" t="s">
+        <v>680</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>24</v>
+      </c>
+      <c r="R256" t="s">
+        <v>41</v>
+      </c>
+      <c r="S256" t="s">
+        <v>630</v>
+      </c>
+      <c r="T256" t="s">
+        <v>42</v>
+      </c>
+      <c r="U256" t="s">
+        <v>43</v>
+      </c>
+      <c r="V256" t="s">
+        <v>44</v>
+      </c>
+      <c r="W256" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>678</v>
+      </c>
+      <c r="B257" t="s">
+        <v>679</v>
+      </c>
+      <c r="C257" t="s">
+        <v>34</v>
+      </c>
+      <c r="D257" t="s">
+        <v>35</v>
+      </c>
+      <c r="E257" t="s">
+        <v>36</v>
+      </c>
+      <c r="F257" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G257" t="s">
+        <v>681</v>
+      </c>
+      <c r="H257" t="s">
+        <v>682</v>
+      </c>
+      <c r="I257" t="s">
+        <v>683</v>
+      </c>
+      <c r="J257">
+        <v>1</v>
+      </c>
+      <c r="K257">
+        <v>12.75</v>
+      </c>
+      <c r="L257">
+        <v>12.75</v>
+      </c>
+      <c r="M257" t="s">
+        <v>22</v>
+      </c>
+      <c r="N257" t="s">
+        <v>23</v>
+      </c>
+      <c r="O257" s="1">
+        <v>46129</v>
+      </c>
+      <c r="P257" t="s">
+        <v>680</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>24</v>
+      </c>
+      <c r="R257" t="s">
+        <v>41</v>
+      </c>
+      <c r="S257" t="s">
+        <v>630</v>
+      </c>
+      <c r="T257" t="s">
+        <v>42</v>
+      </c>
+      <c r="U257" t="s">
+        <v>43</v>
+      </c>
+      <c r="V257" t="s">
+        <v>44</v>
+      </c>
+      <c r="W257" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>678</v>
+      </c>
+      <c r="B258" t="s">
+        <v>679</v>
+      </c>
+      <c r="C258" t="s">
+        <v>34</v>
+      </c>
+      <c r="D258" t="s">
+        <v>35</v>
+      </c>
+      <c r="E258" t="s">
+        <v>36</v>
+      </c>
+      <c r="F258" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G258" t="s">
+        <v>633</v>
+      </c>
+      <c r="H258" t="s">
+        <v>634</v>
+      </c>
+      <c r="I258" t="s">
+        <v>635</v>
+      </c>
+      <c r="J258">
+        <v>4</v>
+      </c>
+      <c r="K258">
+        <v>9.9</v>
+      </c>
+      <c r="L258">
+        <v>39.6</v>
+      </c>
+      <c r="M258" t="s">
+        <v>22</v>
+      </c>
+      <c r="N258" t="s">
+        <v>23</v>
+      </c>
+      <c r="O258" s="1">
+        <v>46129</v>
+      </c>
+      <c r="P258" t="s">
+        <v>680</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>24</v>
+      </c>
+      <c r="R258" t="s">
+        <v>41</v>
+      </c>
+      <c r="S258" t="s">
+        <v>630</v>
+      </c>
+      <c r="T258" t="s">
+        <v>42</v>
+      </c>
+      <c r="U258" t="s">
+        <v>43</v>
+      </c>
+      <c r="V258" t="s">
+        <v>44</v>
+      </c>
+      <c r="W258" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>684</v>
+      </c>
+      <c r="B259" t="s">
+        <v>685</v>
+      </c>
+      <c r="C259" t="s">
+        <v>34</v>
+      </c>
+      <c r="D259" t="s">
+        <v>35</v>
+      </c>
+      <c r="E259" t="s">
+        <v>36</v>
+      </c>
+      <c r="F259" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G259" t="s">
+        <v>153</v>
+      </c>
+      <c r="H259" t="s">
+        <v>154</v>
+      </c>
+      <c r="I259" t="s">
+        <v>155</v>
+      </c>
+      <c r="J259">
+        <v>6</v>
+      </c>
+      <c r="K259">
+        <v>15.68</v>
+      </c>
+      <c r="L259">
+        <v>94.08</v>
+      </c>
+      <c r="M259" t="s">
+        <v>22</v>
+      </c>
+      <c r="N259" t="s">
+        <v>23</v>
+      </c>
+      <c r="O259" s="1">
+        <v>46129</v>
+      </c>
+      <c r="P259" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>24</v>
+      </c>
+      <c r="R259" t="s">
+        <v>41</v>
+      </c>
+      <c r="S259" t="s">
+        <v>630</v>
+      </c>
+      <c r="T259" t="s">
+        <v>42</v>
+      </c>
+      <c r="U259" t="s">
+        <v>43</v>
+      </c>
+      <c r="V259" t="s">
+        <v>44</v>
+      </c>
+      <c r="W259" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>686</v>
+      </c>
+      <c r="B260" t="s">
+        <v>687</v>
+      </c>
+      <c r="C260" t="s">
+        <v>34</v>
+      </c>
+      <c r="D260" t="s">
+        <v>35</v>
+      </c>
+      <c r="E260" t="s">
+        <v>36</v>
+      </c>
+      <c r="F260" s="1">
+        <v>46133</v>
+      </c>
+      <c r="G260" t="s">
+        <v>29</v>
+      </c>
+      <c r="H260" t="s">
+        <v>30</v>
+      </c>
+      <c r="I260" t="s">
+        <v>31</v>
+      </c>
+      <c r="J260">
+        <v>2</v>
+      </c>
+      <c r="K260">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="L260">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="M260" t="s">
+        <v>22</v>
+      </c>
+      <c r="N260" t="s">
+        <v>23</v>
+      </c>
+      <c r="O260" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P260" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>24</v>
+      </c>
+      <c r="R260" t="s">
+        <v>41</v>
+      </c>
+      <c r="S260" t="s">
+        <v>630</v>
+      </c>
+      <c r="T260" t="s">
+        <v>42</v>
+      </c>
+      <c r="U260" t="s">
+        <v>43</v>
+      </c>
+      <c r="V260" t="s">
+        <v>44</v>
+      </c>
+      <c r="W260" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>686</v>
+      </c>
+      <c r="B261" t="s">
+        <v>687</v>
+      </c>
+      <c r="C261" t="s">
+        <v>34</v>
+      </c>
+      <c r="D261" t="s">
+        <v>35</v>
+      </c>
+      <c r="E261" t="s">
+        <v>36</v>
+      </c>
+      <c r="F261" s="1">
+        <v>46133</v>
+      </c>
+      <c r="G261" t="s">
+        <v>256</v>
+      </c>
+      <c r="H261" t="s">
+        <v>257</v>
+      </c>
+      <c r="I261" t="s">
+        <v>258</v>
+      </c>
+      <c r="J261">
+        <v>3</v>
+      </c>
+      <c r="K261">
+        <v>19.47</v>
+      </c>
+      <c r="L261">
+        <v>58.41</v>
+      </c>
+      <c r="M261" t="s">
+        <v>22</v>
+      </c>
+      <c r="N261" t="s">
+        <v>23</v>
+      </c>
+      <c r="O261" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P261" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>24</v>
+      </c>
+      <c r="R261" t="s">
+        <v>41</v>
+      </c>
+      <c r="S261" t="s">
+        <v>630</v>
+      </c>
+      <c r="T261" t="s">
+        <v>42</v>
+      </c>
+      <c r="U261" t="s">
+        <v>43</v>
+      </c>
+      <c r="V261" t="s">
+        <v>44</v>
+      </c>
+      <c r="W261" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>686</v>
+      </c>
+      <c r="B262" t="s">
+        <v>687</v>
+      </c>
+      <c r="C262" t="s">
+        <v>34</v>
+      </c>
+      <c r="D262" t="s">
+        <v>35</v>
+      </c>
+      <c r="E262" t="s">
+        <v>36</v>
+      </c>
+      <c r="F262" s="1">
+        <v>46133</v>
+      </c>
+      <c r="G262" t="s">
+        <v>260</v>
+      </c>
+      <c r="H262" t="s">
+        <v>261</v>
+      </c>
+      <c r="I262" t="s">
+        <v>262</v>
+      </c>
+      <c r="J262">
+        <v>3</v>
+      </c>
+      <c r="K262">
+        <v>19.47</v>
+      </c>
+      <c r="L262">
+        <v>58.41</v>
+      </c>
+      <c r="M262" t="s">
+        <v>22</v>
+      </c>
+      <c r="N262" t="s">
+        <v>23</v>
+      </c>
+      <c r="O262" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P262" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>24</v>
+      </c>
+      <c r="R262" t="s">
+        <v>41</v>
+      </c>
+      <c r="S262" t="s">
+        <v>630</v>
+      </c>
+      <c r="T262" t="s">
+        <v>42</v>
+      </c>
+      <c r="U262" t="s">
+        <v>43</v>
+      </c>
+      <c r="V262" t="s">
+        <v>44</v>
+      </c>
+      <c r="W262" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>686</v>
+      </c>
+      <c r="B263" t="s">
+        <v>687</v>
+      </c>
+      <c r="C263" t="s">
+        <v>34</v>
+      </c>
+      <c r="D263" t="s">
+        <v>35</v>
+      </c>
+      <c r="E263" t="s">
+        <v>36</v>
+      </c>
+      <c r="F263" s="1">
+        <v>46133</v>
+      </c>
+      <c r="G263" t="s">
+        <v>405</v>
+      </c>
+      <c r="H263" t="s">
+        <v>406</v>
+      </c>
+      <c r="I263" t="s">
+        <v>407</v>
+      </c>
+      <c r="J263">
+        <v>1</v>
+      </c>
+      <c r="K263">
+        <v>29.7</v>
+      </c>
+      <c r="L263">
+        <v>29.7</v>
+      </c>
+      <c r="M263" t="s">
+        <v>22</v>
+      </c>
+      <c r="N263" t="s">
+        <v>23</v>
+      </c>
+      <c r="O263" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P263" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>24</v>
+      </c>
+      <c r="R263" t="s">
+        <v>41</v>
+      </c>
+      <c r="S263" t="s">
+        <v>630</v>
+      </c>
+      <c r="T263" t="s">
+        <v>42</v>
+      </c>
+      <c r="U263" t="s">
+        <v>43</v>
+      </c>
+      <c r="V263" t="s">
+        <v>44</v>
+      </c>
+      <c r="W263" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>686</v>
+      </c>
+      <c r="B264" t="s">
+        <v>687</v>
+      </c>
+      <c r="C264" t="s">
+        <v>34</v>
+      </c>
+      <c r="D264" t="s">
+        <v>35</v>
+      </c>
+      <c r="E264" t="s">
+        <v>36</v>
+      </c>
+      <c r="F264" s="1">
+        <v>46133</v>
+      </c>
+      <c r="G264" t="s">
+        <v>689</v>
+      </c>
+      <c r="H264" t="s">
+        <v>690</v>
+      </c>
+      <c r="I264" t="s">
+        <v>691</v>
+      </c>
+      <c r="J264">
+        <v>1</v>
+      </c>
+      <c r="K264">
+        <v>7.7</v>
+      </c>
+      <c r="L264">
+        <v>7.7</v>
+      </c>
+      <c r="M264" t="s">
+        <v>22</v>
+      </c>
+      <c r="N264" t="s">
+        <v>23</v>
+      </c>
+      <c r="O264" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P264" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>24</v>
+      </c>
+      <c r="R264" t="s">
+        <v>41</v>
+      </c>
+      <c r="S264" t="s">
+        <v>630</v>
+      </c>
+      <c r="T264" t="s">
+        <v>42</v>
+      </c>
+      <c r="U264" t="s">
+        <v>43</v>
+      </c>
+      <c r="V264" t="s">
+        <v>44</v>
+      </c>
+      <c r="W264" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>686</v>
+      </c>
+      <c r="B265" t="s">
+        <v>687</v>
+      </c>
+      <c r="C265" t="s">
+        <v>34</v>
+      </c>
+      <c r="D265" t="s">
+        <v>35</v>
+      </c>
+      <c r="E265" t="s">
+        <v>36</v>
+      </c>
+      <c r="F265" s="1">
+        <v>46133</v>
+      </c>
+      <c r="G265" t="s">
+        <v>294</v>
+      </c>
+      <c r="H265" t="s">
+        <v>295</v>
+      </c>
+      <c r="I265" t="s">
+        <v>296</v>
+      </c>
+      <c r="J265">
+        <v>6</v>
+      </c>
+      <c r="K265">
+        <v>8.76</v>
+      </c>
+      <c r="L265">
+        <v>52.56</v>
+      </c>
+      <c r="M265" t="s">
+        <v>22</v>
+      </c>
+      <c r="N265" t="s">
+        <v>23</v>
+      </c>
+      <c r="O265" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P265" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>24</v>
+      </c>
+      <c r="R265" t="s">
+        <v>41</v>
+      </c>
+      <c r="S265" t="s">
+        <v>630</v>
+      </c>
+      <c r="T265" t="s">
+        <v>42</v>
+      </c>
+      <c r="U265" t="s">
+        <v>43</v>
+      </c>
+      <c r="V265" t="s">
+        <v>44</v>
+      </c>
+      <c r="W265" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>686</v>
+      </c>
+      <c r="B266" t="s">
+        <v>687</v>
+      </c>
+      <c r="C266" t="s">
+        <v>34</v>
+      </c>
+      <c r="D266" t="s">
+        <v>35</v>
+      </c>
+      <c r="E266" t="s">
+        <v>36</v>
+      </c>
+      <c r="F266" s="1">
+        <v>46133</v>
+      </c>
+      <c r="G266" t="s">
+        <v>425</v>
+      </c>
+      <c r="H266" t="s">
+        <v>426</v>
+      </c>
+      <c r="I266" t="s">
+        <v>427</v>
+      </c>
+      <c r="J266">
+        <v>1</v>
+      </c>
+      <c r="K266">
+        <v>53.4</v>
+      </c>
+      <c r="L266">
+        <v>53.4</v>
+      </c>
+      <c r="M266" t="s">
+        <v>22</v>
+      </c>
+      <c r="N266" t="s">
+        <v>23</v>
+      </c>
+      <c r="O266" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P266" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>24</v>
+      </c>
+      <c r="R266" t="s">
+        <v>41</v>
+      </c>
+      <c r="S266" t="s">
+        <v>630</v>
+      </c>
+      <c r="T266" t="s">
+        <v>42</v>
+      </c>
+      <c r="U266" t="s">
+        <v>43</v>
+      </c>
+      <c r="V266" t="s">
+        <v>44</v>
+      </c>
+      <c r="W266" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>692</v>
+      </c>
+      <c r="B267" t="s">
+        <v>693</v>
+      </c>
+      <c r="C267" t="s">
+        <v>34</v>
+      </c>
+      <c r="D267" t="s">
+        <v>35</v>
+      </c>
+      <c r="E267" t="s">
+        <v>36</v>
+      </c>
+      <c r="F267" s="1">
+        <v>46133</v>
+      </c>
+      <c r="G267" t="s">
+        <v>236</v>
+      </c>
+      <c r="H267" t="s">
+        <v>237</v>
+      </c>
+      <c r="I267" t="s">
+        <v>238</v>
+      </c>
+      <c r="J267">
+        <v>2</v>
+      </c>
+      <c r="K267">
+        <v>12.86</v>
+      </c>
+      <c r="L267">
+        <v>25.72</v>
+      </c>
+      <c r="M267" t="s">
+        <v>22</v>
+      </c>
+      <c r="N267" t="s">
+        <v>23</v>
+      </c>
+      <c r="O267" s="1">
+        <v>46133</v>
+      </c>
+      <c r="P267" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>24</v>
+      </c>
+      <c r="R267" t="s">
+        <v>41</v>
+      </c>
+      <c r="S267" t="s">
+        <v>630</v>
+      </c>
+      <c r="T267" t="s">
+        <v>42</v>
+      </c>
+      <c r="U267" t="s">
+        <v>43</v>
+      </c>
+      <c r="V267" t="s">
+        <v>44</v>
+      </c>
+      <c r="W267" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>694</v>
+      </c>
+      <c r="B268" t="s">
+        <v>695</v>
+      </c>
+      <c r="C268" t="s">
+        <v>34</v>
+      </c>
+      <c r="D268" t="s">
+        <v>35</v>
+      </c>
+      <c r="E268" t="s">
+        <v>36</v>
+      </c>
+      <c r="F268" s="1">
+        <v>46135</v>
+      </c>
+      <c r="G268" t="s">
+        <v>696</v>
+      </c>
+      <c r="H268" t="s">
+        <v>697</v>
+      </c>
+      <c r="I268" t="s">
+        <v>698</v>
+      </c>
+      <c r="J268">
+        <v>1</v>
+      </c>
+      <c r="K268">
+        <v>54.87</v>
+      </c>
+      <c r="L268">
+        <v>54.87</v>
+      </c>
+      <c r="M268" t="s">
+        <v>22</v>
+      </c>
+      <c r="N268" t="s">
+        <v>23</v>
+      </c>
+      <c r="O268" s="1">
+        <v>46135</v>
+      </c>
+      <c r="P268" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>24</v>
+      </c>
+      <c r="R268" t="s">
+        <v>41</v>
+      </c>
+      <c r="S268" t="s">
+        <v>630</v>
+      </c>
+      <c r="T268" t="s">
+        <v>42</v>
+      </c>
+      <c r="U268" t="s">
+        <v>43</v>
+      </c>
+      <c r="V268" t="s">
+        <v>44</v>
+      </c>
+      <c r="W268" t="s">
+        <v>700</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17915,9 +21616,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18059,19 +21763,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18095,9 +21795,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/activitereelford-2026.xlsx
+++ b/activitereelford-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39E769E-EF47-4FCE-80C4-CD660CBA5383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666F1299-505C-46C6-B790-46384CB824F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4837" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5701" uniqueCount="785">
   <si>
     <t>N°commande</t>
   </si>
@@ -2140,6 +2140,258 @@
   </si>
   <si>
     <t>Avril</t>
+  </si>
+  <si>
+    <t>26412210</t>
+  </si>
+  <si>
+    <t>26613041</t>
+  </si>
+  <si>
+    <t>CDE GGE BL AUTO BEAUMONTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85821 11                 </t>
+  </si>
+  <si>
+    <t>85821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT SELF GUIDE EVO NOIR 85814 + 85816                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85814 22                 </t>
+  </si>
+  <si>
+    <t>85814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELF GUIDE EVO NOIR                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86038 00                 </t>
+  </si>
+  <si>
+    <t>86038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRAFES PLATES ST18- 8 MM                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86040 00                 </t>
+  </si>
+  <si>
+    <t>86040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRAFES ONDULEES ST28 - 8 MM                                 </t>
+  </si>
+  <si>
+    <t>26412211</t>
+  </si>
+  <si>
+    <t>26613042</t>
+  </si>
+  <si>
+    <t>26412212</t>
+  </si>
+  <si>
+    <t>26613043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGE BARBE                </t>
+  </si>
+  <si>
+    <t>26412418</t>
+  </si>
+  <si>
+    <t>26613296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87199 22                 </t>
+  </si>
+  <si>
+    <t>87199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMIUM CAR SHAMPOO                                          </t>
+  </si>
+  <si>
+    <t>26412421</t>
+  </si>
+  <si>
+    <t>26613298</t>
+  </si>
+  <si>
+    <t>26615010</t>
+  </si>
+  <si>
+    <t>26412603</t>
+  </si>
+  <si>
+    <t>26613698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87069 02                 </t>
+  </si>
+  <si>
+    <t>87069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT EQUIPEZ VOS COMPAGNONS PACK EVC                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT 87069                </t>
+  </si>
+  <si>
+    <t>26412709</t>
+  </si>
+  <si>
+    <t>26613586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE STOCK MAG            </t>
+  </si>
+  <si>
+    <t>26412980</t>
+  </si>
+  <si>
+    <t>26613836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE MAG+CARR+MECA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87078 22                 </t>
+  </si>
+  <si>
+    <t>87078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFT SURFACE CLEANER ZERO 10L EVOLINE BIDON 10 L             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87185 22                 </t>
+  </si>
+  <si>
+    <t>87185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KE100 CARTON DE 6 x LKEN87176                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87176 22                 </t>
+  </si>
+  <si>
+    <t>87176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KE100 - AER500ML                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86540 16                 </t>
+  </si>
+  <si>
+    <t>86540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUDLOCK ROUGE 50ML                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86703 22                 </t>
+  </si>
+  <si>
+    <t>86703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURBO PU REPAIR LE - BLACK CART 250 ML                       </t>
+  </si>
+  <si>
+    <t>26413119</t>
+  </si>
+  <si>
+    <t>26614047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85956 22                 </t>
+  </si>
+  <si>
+    <t>85956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURBO FAP CLEANER                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE JDM              </t>
+  </si>
+  <si>
+    <t>26413660</t>
+  </si>
+  <si>
+    <t>26614561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGE N&amp;M                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0107 00                 </t>
+  </si>
+  <si>
+    <t>E0107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDE TRESSEE 22 M TW-72                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0226 00                 </t>
+  </si>
+  <si>
+    <t>E0226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIS DE FIXATION LAME EXCALIBUR                               </t>
+  </si>
+  <si>
+    <t>26413744</t>
+  </si>
+  <si>
+    <t>26614595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83972 10                 </t>
+  </si>
+  <si>
+    <t>83972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAISSE CUIVREE HAUTE TEMPERATURE                            </t>
+  </si>
+  <si>
+    <t>26413963</t>
+  </si>
+  <si>
+    <t>26614863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE MECA AUTO 14     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85752 22                 </t>
+  </si>
+  <si>
+    <t>85752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENOVATEUR PNEUS TOPDRESS BASE D'EAU 5L                      </t>
+  </si>
+  <si>
+    <t>26414201</t>
+  </si>
+  <si>
+    <t>26615223</t>
+  </si>
+  <si>
+    <t>Mai</t>
   </si>
 </sst>
 </file>
@@ -2149,10 +2401,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2515,7 +2773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W268"/>
+  <dimension ref="A1:W316"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -21570,8 +21828,3417 @@
         <v>700</v>
       </c>
     </row>
+    <row r="269" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>701</v>
+      </c>
+      <c r="B269" t="s">
+        <v>702</v>
+      </c>
+      <c r="C269" t="s">
+        <v>34</v>
+      </c>
+      <c r="D269" t="s">
+        <v>35</v>
+      </c>
+      <c r="E269" t="s">
+        <v>36</v>
+      </c>
+      <c r="F269" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G269" t="s">
+        <v>503</v>
+      </c>
+      <c r="H269" t="s">
+        <v>504</v>
+      </c>
+      <c r="I269" t="s">
+        <v>505</v>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269">
+        <v>13.06</v>
+      </c>
+      <c r="L269">
+        <v>13.06</v>
+      </c>
+      <c r="M269" t="s">
+        <v>22</v>
+      </c>
+      <c r="N269" t="s">
+        <v>23</v>
+      </c>
+      <c r="O269" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P269" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>24</v>
+      </c>
+      <c r="R269" t="s">
+        <v>41</v>
+      </c>
+      <c r="S269" t="s">
+        <v>630</v>
+      </c>
+      <c r="T269" t="s">
+        <v>42</v>
+      </c>
+      <c r="U269" t="s">
+        <v>43</v>
+      </c>
+      <c r="V269" t="s">
+        <v>44</v>
+      </c>
+      <c r="W269" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>701</v>
+      </c>
+      <c r="B270" t="s">
+        <v>702</v>
+      </c>
+      <c r="C270" t="s">
+        <v>34</v>
+      </c>
+      <c r="D270" t="s">
+        <v>35</v>
+      </c>
+      <c r="E270" t="s">
+        <v>36</v>
+      </c>
+      <c r="F270" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G270" t="s">
+        <v>704</v>
+      </c>
+      <c r="H270" t="s">
+        <v>705</v>
+      </c>
+      <c r="I270" t="s">
+        <v>706</v>
+      </c>
+      <c r="J270">
+        <v>1</v>
+      </c>
+      <c r="K270">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="L270">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="M270" t="s">
+        <v>22</v>
+      </c>
+      <c r="N270" t="s">
+        <v>23</v>
+      </c>
+      <c r="O270" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P270" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>24</v>
+      </c>
+      <c r="R270" t="s">
+        <v>41</v>
+      </c>
+      <c r="S270" t="s">
+        <v>630</v>
+      </c>
+      <c r="T270" t="s">
+        <v>42</v>
+      </c>
+      <c r="U270" t="s">
+        <v>43</v>
+      </c>
+      <c r="V270" t="s">
+        <v>44</v>
+      </c>
+      <c r="W270" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="271" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>701</v>
+      </c>
+      <c r="B271" t="s">
+        <v>702</v>
+      </c>
+      <c r="C271" t="s">
+        <v>34</v>
+      </c>
+      <c r="D271" t="s">
+        <v>35</v>
+      </c>
+      <c r="E271" t="s">
+        <v>36</v>
+      </c>
+      <c r="F271" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G271" t="s">
+        <v>707</v>
+      </c>
+      <c r="H271" t="s">
+        <v>708</v>
+      </c>
+      <c r="I271" t="s">
+        <v>709</v>
+      </c>
+      <c r="J271">
+        <v>1</v>
+      </c>
+      <c r="K271">
+        <v>64.89</v>
+      </c>
+      <c r="L271">
+        <v>0</v>
+      </c>
+      <c r="M271" t="s">
+        <v>22</v>
+      </c>
+      <c r="N271" t="s">
+        <v>23</v>
+      </c>
+      <c r="O271" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P271" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>24</v>
+      </c>
+      <c r="R271" t="s">
+        <v>41</v>
+      </c>
+      <c r="S271" t="s">
+        <v>630</v>
+      </c>
+      <c r="T271" t="s">
+        <v>42</v>
+      </c>
+      <c r="U271" t="s">
+        <v>43</v>
+      </c>
+      <c r="V271" t="s">
+        <v>44</v>
+      </c>
+      <c r="W271" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>701</v>
+      </c>
+      <c r="B272" t="s">
+        <v>702</v>
+      </c>
+      <c r="C272" t="s">
+        <v>34</v>
+      </c>
+      <c r="D272" t="s">
+        <v>35</v>
+      </c>
+      <c r="E272" t="s">
+        <v>36</v>
+      </c>
+      <c r="F272" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G272" t="s">
+        <v>512</v>
+      </c>
+      <c r="H272" t="s">
+        <v>513</v>
+      </c>
+      <c r="I272" t="s">
+        <v>514</v>
+      </c>
+      <c r="J272">
+        <v>1</v>
+      </c>
+      <c r="K272">
+        <v>15.99</v>
+      </c>
+      <c r="L272">
+        <v>0</v>
+      </c>
+      <c r="M272" t="s">
+        <v>22</v>
+      </c>
+      <c r="N272" t="s">
+        <v>23</v>
+      </c>
+      <c r="O272" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P272" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>24</v>
+      </c>
+      <c r="R272" t="s">
+        <v>41</v>
+      </c>
+      <c r="S272" t="s">
+        <v>630</v>
+      </c>
+      <c r="T272" t="s">
+        <v>42</v>
+      </c>
+      <c r="U272" t="s">
+        <v>43</v>
+      </c>
+      <c r="V272" t="s">
+        <v>44</v>
+      </c>
+      <c r="W272" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="273" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>701</v>
+      </c>
+      <c r="B273" t="s">
+        <v>702</v>
+      </c>
+      <c r="C273" t="s">
+        <v>34</v>
+      </c>
+      <c r="D273" t="s">
+        <v>35</v>
+      </c>
+      <c r="E273" t="s">
+        <v>36</v>
+      </c>
+      <c r="F273" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G273" t="s">
+        <v>710</v>
+      </c>
+      <c r="H273" t="s">
+        <v>711</v>
+      </c>
+      <c r="I273" t="s">
+        <v>712</v>
+      </c>
+      <c r="J273">
+        <v>1</v>
+      </c>
+      <c r="K273">
+        <v>17.71</v>
+      </c>
+      <c r="L273">
+        <v>17.71</v>
+      </c>
+      <c r="M273" t="s">
+        <v>22</v>
+      </c>
+      <c r="N273" t="s">
+        <v>23</v>
+      </c>
+      <c r="O273" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P273" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>24</v>
+      </c>
+      <c r="R273" t="s">
+        <v>41</v>
+      </c>
+      <c r="S273" t="s">
+        <v>630</v>
+      </c>
+      <c r="T273" t="s">
+        <v>42</v>
+      </c>
+      <c r="U273" t="s">
+        <v>43</v>
+      </c>
+      <c r="V273" t="s">
+        <v>44</v>
+      </c>
+      <c r="W273" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>701</v>
+      </c>
+      <c r="B274" t="s">
+        <v>702</v>
+      </c>
+      <c r="C274" t="s">
+        <v>34</v>
+      </c>
+      <c r="D274" t="s">
+        <v>35</v>
+      </c>
+      <c r="E274" t="s">
+        <v>36</v>
+      </c>
+      <c r="F274" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G274" t="s">
+        <v>713</v>
+      </c>
+      <c r="H274" t="s">
+        <v>714</v>
+      </c>
+      <c r="I274" t="s">
+        <v>715</v>
+      </c>
+      <c r="J274">
+        <v>1</v>
+      </c>
+      <c r="K274">
+        <v>17.71</v>
+      </c>
+      <c r="L274">
+        <v>17.71</v>
+      </c>
+      <c r="M274" t="s">
+        <v>22</v>
+      </c>
+      <c r="N274" t="s">
+        <v>23</v>
+      </c>
+      <c r="O274" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P274" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>24</v>
+      </c>
+      <c r="R274" t="s">
+        <v>41</v>
+      </c>
+      <c r="S274" t="s">
+        <v>630</v>
+      </c>
+      <c r="T274" t="s">
+        <v>42</v>
+      </c>
+      <c r="U274" t="s">
+        <v>43</v>
+      </c>
+      <c r="V274" t="s">
+        <v>44</v>
+      </c>
+      <c r="W274" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>701</v>
+      </c>
+      <c r="B275" t="s">
+        <v>702</v>
+      </c>
+      <c r="C275" t="s">
+        <v>34</v>
+      </c>
+      <c r="D275" t="s">
+        <v>35</v>
+      </c>
+      <c r="E275" t="s">
+        <v>36</v>
+      </c>
+      <c r="F275" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G275" t="s">
+        <v>102</v>
+      </c>
+      <c r="H275" t="s">
+        <v>103</v>
+      </c>
+      <c r="I275" t="s">
+        <v>104</v>
+      </c>
+      <c r="J275">
+        <v>1</v>
+      </c>
+      <c r="K275">
+        <v>31.74</v>
+      </c>
+      <c r="L275">
+        <v>31.74</v>
+      </c>
+      <c r="M275" t="s">
+        <v>22</v>
+      </c>
+      <c r="N275" t="s">
+        <v>23</v>
+      </c>
+      <c r="O275" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P275" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>24</v>
+      </c>
+      <c r="R275" t="s">
+        <v>41</v>
+      </c>
+      <c r="S275" t="s">
+        <v>630</v>
+      </c>
+      <c r="T275" t="s">
+        <v>42</v>
+      </c>
+      <c r="U275" t="s">
+        <v>43</v>
+      </c>
+      <c r="V275" t="s">
+        <v>44</v>
+      </c>
+      <c r="W275" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>716</v>
+      </c>
+      <c r="B276" t="s">
+        <v>717</v>
+      </c>
+      <c r="C276" t="s">
+        <v>34</v>
+      </c>
+      <c r="D276" t="s">
+        <v>35</v>
+      </c>
+      <c r="E276" t="s">
+        <v>36</v>
+      </c>
+      <c r="F276" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G276" t="s">
+        <v>515</v>
+      </c>
+      <c r="H276" t="s">
+        <v>516</v>
+      </c>
+      <c r="I276" t="s">
+        <v>517</v>
+      </c>
+      <c r="J276">
+        <v>1</v>
+      </c>
+      <c r="K276">
+        <v>15.04</v>
+      </c>
+      <c r="L276">
+        <v>15.04</v>
+      </c>
+      <c r="M276" t="s">
+        <v>22</v>
+      </c>
+      <c r="N276" t="s">
+        <v>23</v>
+      </c>
+      <c r="O276" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P276" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>24</v>
+      </c>
+      <c r="R276" t="s">
+        <v>41</v>
+      </c>
+      <c r="S276" t="s">
+        <v>630</v>
+      </c>
+      <c r="T276" t="s">
+        <v>42</v>
+      </c>
+      <c r="U276" t="s">
+        <v>43</v>
+      </c>
+      <c r="V276" t="s">
+        <v>44</v>
+      </c>
+      <c r="W276" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>716</v>
+      </c>
+      <c r="B277" t="s">
+        <v>717</v>
+      </c>
+      <c r="C277" t="s">
+        <v>34</v>
+      </c>
+      <c r="D277" t="s">
+        <v>35</v>
+      </c>
+      <c r="E277" t="s">
+        <v>36</v>
+      </c>
+      <c r="F277" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G277" t="s">
+        <v>417</v>
+      </c>
+      <c r="H277" t="s">
+        <v>418</v>
+      </c>
+      <c r="I277" t="s">
+        <v>419</v>
+      </c>
+      <c r="J277">
+        <v>1</v>
+      </c>
+      <c r="K277">
+        <v>23.51</v>
+      </c>
+      <c r="L277">
+        <v>23.51</v>
+      </c>
+      <c r="M277" t="s">
+        <v>22</v>
+      </c>
+      <c r="N277" t="s">
+        <v>23</v>
+      </c>
+      <c r="O277" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P277" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>24</v>
+      </c>
+      <c r="R277" t="s">
+        <v>41</v>
+      </c>
+      <c r="S277" t="s">
+        <v>630</v>
+      </c>
+      <c r="T277" t="s">
+        <v>42</v>
+      </c>
+      <c r="U277" t="s">
+        <v>43</v>
+      </c>
+      <c r="V277" t="s">
+        <v>44</v>
+      </c>
+      <c r="W277" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="278" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>718</v>
+      </c>
+      <c r="B278" t="s">
+        <v>719</v>
+      </c>
+      <c r="C278" t="s">
+        <v>34</v>
+      </c>
+      <c r="D278" t="s">
+        <v>35</v>
+      </c>
+      <c r="E278" t="s">
+        <v>36</v>
+      </c>
+      <c r="F278" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G278" t="s">
+        <v>89</v>
+      </c>
+      <c r="H278" t="s">
+        <v>90</v>
+      </c>
+      <c r="I278" t="s">
+        <v>91</v>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278">
+        <v>14.85</v>
+      </c>
+      <c r="L278">
+        <v>14.85</v>
+      </c>
+      <c r="M278" t="s">
+        <v>22</v>
+      </c>
+      <c r="N278" t="s">
+        <v>23</v>
+      </c>
+      <c r="O278" s="1">
+        <v>46147</v>
+      </c>
+      <c r="P278" t="s">
+        <v>720</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>24</v>
+      </c>
+      <c r="R278" t="s">
+        <v>41</v>
+      </c>
+      <c r="S278" t="s">
+        <v>630</v>
+      </c>
+      <c r="T278" t="s">
+        <v>42</v>
+      </c>
+      <c r="U278" t="s">
+        <v>43</v>
+      </c>
+      <c r="V278" t="s">
+        <v>44</v>
+      </c>
+      <c r="W278" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="279" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>721</v>
+      </c>
+      <c r="B279" t="s">
+        <v>722</v>
+      </c>
+      <c r="C279" t="s">
+        <v>34</v>
+      </c>
+      <c r="D279" t="s">
+        <v>35</v>
+      </c>
+      <c r="E279" t="s">
+        <v>36</v>
+      </c>
+      <c r="F279" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G279" t="s">
+        <v>723</v>
+      </c>
+      <c r="H279" t="s">
+        <v>724</v>
+      </c>
+      <c r="I279" t="s">
+        <v>725</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279">
+        <v>71.16</v>
+      </c>
+      <c r="L279">
+        <v>71.16</v>
+      </c>
+      <c r="M279" t="s">
+        <v>22</v>
+      </c>
+      <c r="N279" t="s">
+        <v>23</v>
+      </c>
+      <c r="O279" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P279" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>24</v>
+      </c>
+      <c r="R279" t="s">
+        <v>41</v>
+      </c>
+      <c r="S279" t="s">
+        <v>630</v>
+      </c>
+      <c r="T279" t="s">
+        <v>42</v>
+      </c>
+      <c r="U279" t="s">
+        <v>43</v>
+      </c>
+      <c r="V279" t="s">
+        <v>44</v>
+      </c>
+      <c r="W279" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="280" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>726</v>
+      </c>
+      <c r="B280" t="s">
+        <v>727</v>
+      </c>
+      <c r="C280" t="s">
+        <v>34</v>
+      </c>
+      <c r="D280" t="s">
+        <v>35</v>
+      </c>
+      <c r="E280" t="s">
+        <v>36</v>
+      </c>
+      <c r="F280" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G280" t="s">
+        <v>410</v>
+      </c>
+      <c r="H280" t="s">
+        <v>411</v>
+      </c>
+      <c r="I280" t="s">
+        <v>412</v>
+      </c>
+      <c r="J280">
+        <v>1</v>
+      </c>
+      <c r="K280">
+        <v>27.49</v>
+      </c>
+      <c r="L280">
+        <v>27.49</v>
+      </c>
+      <c r="M280" t="s">
+        <v>22</v>
+      </c>
+      <c r="N280" t="s">
+        <v>23</v>
+      </c>
+      <c r="O280" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P280" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>24</v>
+      </c>
+      <c r="R280" t="s">
+        <v>41</v>
+      </c>
+      <c r="S280" t="s">
+        <v>630</v>
+      </c>
+      <c r="T280" t="s">
+        <v>42</v>
+      </c>
+      <c r="U280" t="s">
+        <v>43</v>
+      </c>
+      <c r="V280" t="s">
+        <v>44</v>
+      </c>
+      <c r="W280" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="281" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>726</v>
+      </c>
+      <c r="B281" t="s">
+        <v>727</v>
+      </c>
+      <c r="C281" t="s">
+        <v>34</v>
+      </c>
+      <c r="D281" t="s">
+        <v>35</v>
+      </c>
+      <c r="E281" t="s">
+        <v>36</v>
+      </c>
+      <c r="F281" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G281" t="s">
+        <v>608</v>
+      </c>
+      <c r="H281" t="s">
+        <v>609</v>
+      </c>
+      <c r="I281" t="s">
+        <v>610</v>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="K281">
+        <v>30.74</v>
+      </c>
+      <c r="L281">
+        <v>30.74</v>
+      </c>
+      <c r="M281" t="s">
+        <v>22</v>
+      </c>
+      <c r="N281" t="s">
+        <v>23</v>
+      </c>
+      <c r="O281" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P281" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>24</v>
+      </c>
+      <c r="R281" t="s">
+        <v>41</v>
+      </c>
+      <c r="S281" t="s">
+        <v>630</v>
+      </c>
+      <c r="T281" t="s">
+        <v>42</v>
+      </c>
+      <c r="U281" t="s">
+        <v>43</v>
+      </c>
+      <c r="V281" t="s">
+        <v>44</v>
+      </c>
+      <c r="W281" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="282" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>726</v>
+      </c>
+      <c r="B282" t="s">
+        <v>727</v>
+      </c>
+      <c r="C282" t="s">
+        <v>34</v>
+      </c>
+      <c r="D282" t="s">
+        <v>35</v>
+      </c>
+      <c r="E282" t="s">
+        <v>36</v>
+      </c>
+      <c r="F282" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G282" t="s">
+        <v>663</v>
+      </c>
+      <c r="H282" t="s">
+        <v>664</v>
+      </c>
+      <c r="I282" t="s">
+        <v>665</v>
+      </c>
+      <c r="J282">
+        <v>1</v>
+      </c>
+      <c r="K282">
+        <v>15.42</v>
+      </c>
+      <c r="L282">
+        <v>15.42</v>
+      </c>
+      <c r="M282" t="s">
+        <v>22</v>
+      </c>
+      <c r="N282" t="s">
+        <v>23</v>
+      </c>
+      <c r="O282" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P282" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>24</v>
+      </c>
+      <c r="R282" t="s">
+        <v>41</v>
+      </c>
+      <c r="S282" t="s">
+        <v>630</v>
+      </c>
+      <c r="T282" t="s">
+        <v>42</v>
+      </c>
+      <c r="U282" t="s">
+        <v>43</v>
+      </c>
+      <c r="V282" t="s">
+        <v>44</v>
+      </c>
+      <c r="W282" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="283" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>726</v>
+      </c>
+      <c r="B283" t="s">
+        <v>727</v>
+      </c>
+      <c r="C283" t="s">
+        <v>34</v>
+      </c>
+      <c r="D283" t="s">
+        <v>35</v>
+      </c>
+      <c r="E283" t="s">
+        <v>36</v>
+      </c>
+      <c r="F283" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G283" t="s">
+        <v>54</v>
+      </c>
+      <c r="H283" t="s">
+        <v>55</v>
+      </c>
+      <c r="I283" t="s">
+        <v>56</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283">
+        <v>12.29</v>
+      </c>
+      <c r="L283">
+        <v>12.29</v>
+      </c>
+      <c r="M283" t="s">
+        <v>22</v>
+      </c>
+      <c r="N283" t="s">
+        <v>23</v>
+      </c>
+      <c r="O283" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P283" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>24</v>
+      </c>
+      <c r="R283" t="s">
+        <v>41</v>
+      </c>
+      <c r="S283" t="s">
+        <v>630</v>
+      </c>
+      <c r="T283" t="s">
+        <v>42</v>
+      </c>
+      <c r="U283" t="s">
+        <v>43</v>
+      </c>
+      <c r="V283" t="s">
+        <v>44</v>
+      </c>
+      <c r="W283" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="284" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>726</v>
+      </c>
+      <c r="B284" t="s">
+        <v>727</v>
+      </c>
+      <c r="C284" t="s">
+        <v>34</v>
+      </c>
+      <c r="D284" t="s">
+        <v>35</v>
+      </c>
+      <c r="E284" t="s">
+        <v>36</v>
+      </c>
+      <c r="F284" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G284" t="s">
+        <v>576</v>
+      </c>
+      <c r="H284" t="s">
+        <v>577</v>
+      </c>
+      <c r="I284" t="s">
+        <v>578</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284">
+        <v>8.25</v>
+      </c>
+      <c r="L284">
+        <v>8.25</v>
+      </c>
+      <c r="M284" t="s">
+        <v>22</v>
+      </c>
+      <c r="N284" t="s">
+        <v>23</v>
+      </c>
+      <c r="O284" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P284" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>24</v>
+      </c>
+      <c r="R284" t="s">
+        <v>41</v>
+      </c>
+      <c r="S284" t="s">
+        <v>630</v>
+      </c>
+      <c r="T284" t="s">
+        <v>42</v>
+      </c>
+      <c r="U284" t="s">
+        <v>43</v>
+      </c>
+      <c r="V284" t="s">
+        <v>44</v>
+      </c>
+      <c r="W284" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="285" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>726</v>
+      </c>
+      <c r="B285" t="s">
+        <v>727</v>
+      </c>
+      <c r="C285" t="s">
+        <v>34</v>
+      </c>
+      <c r="D285" t="s">
+        <v>35</v>
+      </c>
+      <c r="E285" t="s">
+        <v>36</v>
+      </c>
+      <c r="F285" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G285" t="s">
+        <v>221</v>
+      </c>
+      <c r="H285" t="s">
+        <v>222</v>
+      </c>
+      <c r="I285" t="s">
+        <v>223</v>
+      </c>
+      <c r="J285">
+        <v>3</v>
+      </c>
+      <c r="K285">
+        <v>15.86</v>
+      </c>
+      <c r="L285">
+        <v>47.58</v>
+      </c>
+      <c r="M285" t="s">
+        <v>22</v>
+      </c>
+      <c r="N285" t="s">
+        <v>23</v>
+      </c>
+      <c r="O285" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P285" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>24</v>
+      </c>
+      <c r="R285" t="s">
+        <v>41</v>
+      </c>
+      <c r="S285" t="s">
+        <v>630</v>
+      </c>
+      <c r="T285" t="s">
+        <v>42</v>
+      </c>
+      <c r="U285" t="s">
+        <v>43</v>
+      </c>
+      <c r="V285" t="s">
+        <v>44</v>
+      </c>
+      <c r="W285" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="286" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>726</v>
+      </c>
+      <c r="B286" t="s">
+        <v>727</v>
+      </c>
+      <c r="C286" t="s">
+        <v>34</v>
+      </c>
+      <c r="D286" t="s">
+        <v>35</v>
+      </c>
+      <c r="E286" t="s">
+        <v>36</v>
+      </c>
+      <c r="F286" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G286" t="s">
+        <v>343</v>
+      </c>
+      <c r="H286" t="s">
+        <v>344</v>
+      </c>
+      <c r="I286" t="s">
+        <v>345</v>
+      </c>
+      <c r="J286">
+        <v>1</v>
+      </c>
+      <c r="K286">
+        <v>13.12</v>
+      </c>
+      <c r="L286">
+        <v>13.12</v>
+      </c>
+      <c r="M286" t="s">
+        <v>22</v>
+      </c>
+      <c r="N286" t="s">
+        <v>23</v>
+      </c>
+      <c r="O286" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P286" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>24</v>
+      </c>
+      <c r="R286" t="s">
+        <v>41</v>
+      </c>
+      <c r="S286" t="s">
+        <v>630</v>
+      </c>
+      <c r="T286" t="s">
+        <v>42</v>
+      </c>
+      <c r="U286" t="s">
+        <v>43</v>
+      </c>
+      <c r="V286" t="s">
+        <v>44</v>
+      </c>
+      <c r="W286" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="287" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>726</v>
+      </c>
+      <c r="B287" t="s">
+        <v>727</v>
+      </c>
+      <c r="C287" t="s">
+        <v>34</v>
+      </c>
+      <c r="D287" t="s">
+        <v>35</v>
+      </c>
+      <c r="E287" t="s">
+        <v>36</v>
+      </c>
+      <c r="F287" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G287" t="s">
+        <v>460</v>
+      </c>
+      <c r="H287" t="s">
+        <v>461</v>
+      </c>
+      <c r="I287" t="s">
+        <v>462</v>
+      </c>
+      <c r="J287">
+        <v>1</v>
+      </c>
+      <c r="K287">
+        <v>13.12</v>
+      </c>
+      <c r="L287">
+        <v>13.12</v>
+      </c>
+      <c r="M287" t="s">
+        <v>22</v>
+      </c>
+      <c r="N287" t="s">
+        <v>23</v>
+      </c>
+      <c r="O287" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P287" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>24</v>
+      </c>
+      <c r="R287" t="s">
+        <v>41</v>
+      </c>
+      <c r="S287" t="s">
+        <v>630</v>
+      </c>
+      <c r="T287" t="s">
+        <v>42</v>
+      </c>
+      <c r="U287" t="s">
+        <v>43</v>
+      </c>
+      <c r="V287" t="s">
+        <v>44</v>
+      </c>
+      <c r="W287" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="288" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>726</v>
+      </c>
+      <c r="B288" t="s">
+        <v>728</v>
+      </c>
+      <c r="C288" t="s">
+        <v>34</v>
+      </c>
+      <c r="D288" t="s">
+        <v>35</v>
+      </c>
+      <c r="E288" t="s">
+        <v>36</v>
+      </c>
+      <c r="F288" s="1">
+        <v>46170</v>
+      </c>
+      <c r="G288" t="s">
+        <v>206</v>
+      </c>
+      <c r="H288" t="s">
+        <v>207</v>
+      </c>
+      <c r="I288" t="s">
+        <v>208</v>
+      </c>
+      <c r="J288">
+        <v>1</v>
+      </c>
+      <c r="K288">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="L288">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="M288" t="s">
+        <v>22</v>
+      </c>
+      <c r="N288" t="s">
+        <v>23</v>
+      </c>
+      <c r="O288" s="1">
+        <v>46148</v>
+      </c>
+      <c r="P288" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>24</v>
+      </c>
+      <c r="R288" t="s">
+        <v>41</v>
+      </c>
+      <c r="S288" t="s">
+        <v>630</v>
+      </c>
+      <c r="T288" t="s">
+        <v>42</v>
+      </c>
+      <c r="U288" t="s">
+        <v>43</v>
+      </c>
+      <c r="V288" t="s">
+        <v>44</v>
+      </c>
+      <c r="W288" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>729</v>
+      </c>
+      <c r="B289" t="s">
+        <v>730</v>
+      </c>
+      <c r="C289" t="s">
+        <v>34</v>
+      </c>
+      <c r="D289" t="s">
+        <v>35</v>
+      </c>
+      <c r="E289" t="s">
+        <v>36</v>
+      </c>
+      <c r="F289" s="1">
+        <v>46155</v>
+      </c>
+      <c r="G289" t="s">
+        <v>731</v>
+      </c>
+      <c r="H289" t="s">
+        <v>732</v>
+      </c>
+      <c r="I289" t="s">
+        <v>733</v>
+      </c>
+      <c r="J289">
+        <v>1</v>
+      </c>
+      <c r="K289">
+        <v>95.4</v>
+      </c>
+      <c r="L289">
+        <v>95.4</v>
+      </c>
+      <c r="M289" t="s">
+        <v>22</v>
+      </c>
+      <c r="N289" t="s">
+        <v>23</v>
+      </c>
+      <c r="O289" s="1">
+        <v>46153</v>
+      </c>
+      <c r="P289" t="s">
+        <v>734</v>
+      </c>
+      <c r="Q289" t="s">
+        <v>24</v>
+      </c>
+      <c r="R289" t="s">
+        <v>41</v>
+      </c>
+      <c r="S289" t="s">
+        <v>630</v>
+      </c>
+      <c r="T289" t="s">
+        <v>42</v>
+      </c>
+      <c r="U289" t="s">
+        <v>43</v>
+      </c>
+      <c r="V289" t="s">
+        <v>44</v>
+      </c>
+      <c r="W289" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>735</v>
+      </c>
+      <c r="B290" t="s">
+        <v>736</v>
+      </c>
+      <c r="C290" t="s">
+        <v>34</v>
+      </c>
+      <c r="D290" t="s">
+        <v>35</v>
+      </c>
+      <c r="E290" t="s">
+        <v>36</v>
+      </c>
+      <c r="F290" s="1">
+        <v>46154</v>
+      </c>
+      <c r="G290" t="s">
+        <v>287</v>
+      </c>
+      <c r="H290" t="s">
+        <v>288</v>
+      </c>
+      <c r="I290" t="s">
+        <v>289</v>
+      </c>
+      <c r="J290">
+        <v>12</v>
+      </c>
+      <c r="K290">
+        <v>10.8</v>
+      </c>
+      <c r="L290">
+        <v>129.6</v>
+      </c>
+      <c r="M290" t="s">
+        <v>22</v>
+      </c>
+      <c r="N290" t="s">
+        <v>23</v>
+      </c>
+      <c r="O290" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P290" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q290" t="s">
+        <v>24</v>
+      </c>
+      <c r="R290" t="s">
+        <v>41</v>
+      </c>
+      <c r="S290" t="s">
+        <v>630</v>
+      </c>
+      <c r="T290" t="s">
+        <v>42</v>
+      </c>
+      <c r="U290" t="s">
+        <v>43</v>
+      </c>
+      <c r="V290" t="s">
+        <v>44</v>
+      </c>
+      <c r="W290" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>738</v>
+      </c>
+      <c r="B291" t="s">
+        <v>739</v>
+      </c>
+      <c r="C291" t="s">
+        <v>34</v>
+      </c>
+      <c r="D291" t="s">
+        <v>35</v>
+      </c>
+      <c r="E291" t="s">
+        <v>36</v>
+      </c>
+      <c r="F291" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G291" t="s">
+        <v>542</v>
+      </c>
+      <c r="H291" t="s">
+        <v>543</v>
+      </c>
+      <c r="I291" t="s">
+        <v>544</v>
+      </c>
+      <c r="J291">
+        <v>2</v>
+      </c>
+      <c r="K291">
+        <v>15.96</v>
+      </c>
+      <c r="L291">
+        <v>31.92</v>
+      </c>
+      <c r="M291" t="s">
+        <v>22</v>
+      </c>
+      <c r="N291" t="s">
+        <v>23</v>
+      </c>
+      <c r="O291" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P291" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q291" t="s">
+        <v>24</v>
+      </c>
+      <c r="R291" t="s">
+        <v>41</v>
+      </c>
+      <c r="S291" t="s">
+        <v>630</v>
+      </c>
+      <c r="T291" t="s">
+        <v>42</v>
+      </c>
+      <c r="U291" t="s">
+        <v>43</v>
+      </c>
+      <c r="V291" t="s">
+        <v>44</v>
+      </c>
+      <c r="W291" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>738</v>
+      </c>
+      <c r="B292" t="s">
+        <v>739</v>
+      </c>
+      <c r="C292" t="s">
+        <v>34</v>
+      </c>
+      <c r="D292" t="s">
+        <v>35</v>
+      </c>
+      <c r="E292" t="s">
+        <v>36</v>
+      </c>
+      <c r="F292" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G292" t="s">
+        <v>26</v>
+      </c>
+      <c r="H292" t="s">
+        <v>27</v>
+      </c>
+      <c r="I292" t="s">
+        <v>28</v>
+      </c>
+      <c r="J292">
+        <v>36</v>
+      </c>
+      <c r="K292">
+        <v>3.14</v>
+      </c>
+      <c r="L292">
+        <v>113.04</v>
+      </c>
+      <c r="M292" t="s">
+        <v>22</v>
+      </c>
+      <c r="N292" t="s">
+        <v>23</v>
+      </c>
+      <c r="O292" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P292" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q292" t="s">
+        <v>24</v>
+      </c>
+      <c r="R292" t="s">
+        <v>41</v>
+      </c>
+      <c r="S292" t="s">
+        <v>630</v>
+      </c>
+      <c r="T292" t="s">
+        <v>42</v>
+      </c>
+      <c r="U292" t="s">
+        <v>43</v>
+      </c>
+      <c r="V292" t="s">
+        <v>44</v>
+      </c>
+      <c r="W292" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>738</v>
+      </c>
+      <c r="B293" t="s">
+        <v>739</v>
+      </c>
+      <c r="C293" t="s">
+        <v>34</v>
+      </c>
+      <c r="D293" t="s">
+        <v>35</v>
+      </c>
+      <c r="E293" t="s">
+        <v>36</v>
+      </c>
+      <c r="F293" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G293" t="s">
+        <v>741</v>
+      </c>
+      <c r="H293" t="s">
+        <v>742</v>
+      </c>
+      <c r="I293" t="s">
+        <v>743</v>
+      </c>
+      <c r="J293">
+        <v>1</v>
+      </c>
+      <c r="K293">
+        <v>82.93</v>
+      </c>
+      <c r="L293">
+        <v>82.93</v>
+      </c>
+      <c r="M293" t="s">
+        <v>22</v>
+      </c>
+      <c r="N293" t="s">
+        <v>23</v>
+      </c>
+      <c r="O293" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P293" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q293" t="s">
+        <v>24</v>
+      </c>
+      <c r="R293" t="s">
+        <v>41</v>
+      </c>
+      <c r="S293" t="s">
+        <v>630</v>
+      </c>
+      <c r="T293" t="s">
+        <v>42</v>
+      </c>
+      <c r="U293" t="s">
+        <v>43</v>
+      </c>
+      <c r="V293" t="s">
+        <v>44</v>
+      </c>
+      <c r="W293" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>738</v>
+      </c>
+      <c r="B294" t="s">
+        <v>739</v>
+      </c>
+      <c r="C294" t="s">
+        <v>34</v>
+      </c>
+      <c r="D294" t="s">
+        <v>35</v>
+      </c>
+      <c r="E294" t="s">
+        <v>36</v>
+      </c>
+      <c r="F294" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G294" t="s">
+        <v>744</v>
+      </c>
+      <c r="H294" t="s">
+        <v>745</v>
+      </c>
+      <c r="I294" t="s">
+        <v>746</v>
+      </c>
+      <c r="J294">
+        <v>1</v>
+      </c>
+      <c r="K294">
+        <v>23.16</v>
+      </c>
+      <c r="L294">
+        <v>23.16</v>
+      </c>
+      <c r="M294" t="s">
+        <v>22</v>
+      </c>
+      <c r="N294" t="s">
+        <v>23</v>
+      </c>
+      <c r="O294" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P294" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q294" t="s">
+        <v>24</v>
+      </c>
+      <c r="R294" t="s">
+        <v>41</v>
+      </c>
+      <c r="S294" t="s">
+        <v>630</v>
+      </c>
+      <c r="T294" t="s">
+        <v>42</v>
+      </c>
+      <c r="U294" t="s">
+        <v>43</v>
+      </c>
+      <c r="V294" t="s">
+        <v>44</v>
+      </c>
+      <c r="W294" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>738</v>
+      </c>
+      <c r="B295" t="s">
+        <v>739</v>
+      </c>
+      <c r="C295" t="s">
+        <v>34</v>
+      </c>
+      <c r="D295" t="s">
+        <v>35</v>
+      </c>
+      <c r="E295" t="s">
+        <v>36</v>
+      </c>
+      <c r="F295" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G295" t="s">
+        <v>747</v>
+      </c>
+      <c r="H295" t="s">
+        <v>748</v>
+      </c>
+      <c r="I295" t="s">
+        <v>749</v>
+      </c>
+      <c r="J295">
+        <v>6</v>
+      </c>
+      <c r="K295">
+        <v>6.67</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+      <c r="M295" t="s">
+        <v>22</v>
+      </c>
+      <c r="N295" t="s">
+        <v>23</v>
+      </c>
+      <c r="O295" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P295" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q295" t="s">
+        <v>24</v>
+      </c>
+      <c r="R295" t="s">
+        <v>41</v>
+      </c>
+      <c r="S295" t="s">
+        <v>630</v>
+      </c>
+      <c r="T295" t="s">
+        <v>42</v>
+      </c>
+      <c r="U295" t="s">
+        <v>43</v>
+      </c>
+      <c r="V295" t="s">
+        <v>44</v>
+      </c>
+      <c r="W295" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>738</v>
+      </c>
+      <c r="B296" t="s">
+        <v>739</v>
+      </c>
+      <c r="C296" t="s">
+        <v>34</v>
+      </c>
+      <c r="D296" t="s">
+        <v>35</v>
+      </c>
+      <c r="E296" t="s">
+        <v>36</v>
+      </c>
+      <c r="F296" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G296" t="s">
+        <v>386</v>
+      </c>
+      <c r="H296" t="s">
+        <v>387</v>
+      </c>
+      <c r="I296" t="s">
+        <v>388</v>
+      </c>
+      <c r="J296">
+        <v>48</v>
+      </c>
+      <c r="K296">
+        <v>10.83</v>
+      </c>
+      <c r="L296">
+        <v>519.84</v>
+      </c>
+      <c r="M296" t="s">
+        <v>22</v>
+      </c>
+      <c r="N296" t="s">
+        <v>23</v>
+      </c>
+      <c r="O296" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P296" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q296" t="s">
+        <v>24</v>
+      </c>
+      <c r="R296" t="s">
+        <v>41</v>
+      </c>
+      <c r="S296" t="s">
+        <v>630</v>
+      </c>
+      <c r="T296" t="s">
+        <v>42</v>
+      </c>
+      <c r="U296" t="s">
+        <v>43</v>
+      </c>
+      <c r="V296" t="s">
+        <v>44</v>
+      </c>
+      <c r="W296" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>738</v>
+      </c>
+      <c r="B297" t="s">
+        <v>739</v>
+      </c>
+      <c r="C297" t="s">
+        <v>34</v>
+      </c>
+      <c r="D297" t="s">
+        <v>35</v>
+      </c>
+      <c r="E297" t="s">
+        <v>36</v>
+      </c>
+      <c r="F297" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G297" t="s">
+        <v>54</v>
+      </c>
+      <c r="H297" t="s">
+        <v>55</v>
+      </c>
+      <c r="I297" t="s">
+        <v>56</v>
+      </c>
+      <c r="J297">
+        <v>1</v>
+      </c>
+      <c r="K297">
+        <v>12.29</v>
+      </c>
+      <c r="L297">
+        <v>12.29</v>
+      </c>
+      <c r="M297" t="s">
+        <v>22</v>
+      </c>
+      <c r="N297" t="s">
+        <v>23</v>
+      </c>
+      <c r="O297" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P297" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q297" t="s">
+        <v>24</v>
+      </c>
+      <c r="R297" t="s">
+        <v>41</v>
+      </c>
+      <c r="S297" t="s">
+        <v>630</v>
+      </c>
+      <c r="T297" t="s">
+        <v>42</v>
+      </c>
+      <c r="U297" t="s">
+        <v>43</v>
+      </c>
+      <c r="V297" t="s">
+        <v>44</v>
+      </c>
+      <c r="W297" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>738</v>
+      </c>
+      <c r="B298" t="s">
+        <v>739</v>
+      </c>
+      <c r="C298" t="s">
+        <v>34</v>
+      </c>
+      <c r="D298" t="s">
+        <v>35</v>
+      </c>
+      <c r="E298" t="s">
+        <v>36</v>
+      </c>
+      <c r="F298" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G298" t="s">
+        <v>60</v>
+      </c>
+      <c r="H298" t="s">
+        <v>61</v>
+      </c>
+      <c r="I298" t="s">
+        <v>62</v>
+      </c>
+      <c r="J298">
+        <v>2</v>
+      </c>
+      <c r="K298">
+        <v>17.63</v>
+      </c>
+      <c r="L298">
+        <v>35.26</v>
+      </c>
+      <c r="M298" t="s">
+        <v>22</v>
+      </c>
+      <c r="N298" t="s">
+        <v>23</v>
+      </c>
+      <c r="O298" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P298" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q298" t="s">
+        <v>24</v>
+      </c>
+      <c r="R298" t="s">
+        <v>41</v>
+      </c>
+      <c r="S298" t="s">
+        <v>630</v>
+      </c>
+      <c r="T298" t="s">
+        <v>42</v>
+      </c>
+      <c r="U298" t="s">
+        <v>43</v>
+      </c>
+      <c r="V298" t="s">
+        <v>44</v>
+      </c>
+      <c r="W298" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>738</v>
+      </c>
+      <c r="B299" t="s">
+        <v>739</v>
+      </c>
+      <c r="C299" t="s">
+        <v>34</v>
+      </c>
+      <c r="D299" t="s">
+        <v>35</v>
+      </c>
+      <c r="E299" t="s">
+        <v>36</v>
+      </c>
+      <c r="F299" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G299" t="s">
+        <v>642</v>
+      </c>
+      <c r="H299" t="s">
+        <v>643</v>
+      </c>
+      <c r="I299" t="s">
+        <v>644</v>
+      </c>
+      <c r="J299">
+        <v>4</v>
+      </c>
+      <c r="K299">
+        <v>10.52</v>
+      </c>
+      <c r="L299">
+        <v>42.08</v>
+      </c>
+      <c r="M299" t="s">
+        <v>22</v>
+      </c>
+      <c r="N299" t="s">
+        <v>23</v>
+      </c>
+      <c r="O299" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P299" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q299" t="s">
+        <v>24</v>
+      </c>
+      <c r="R299" t="s">
+        <v>41</v>
+      </c>
+      <c r="S299" t="s">
+        <v>630</v>
+      </c>
+      <c r="T299" t="s">
+        <v>42</v>
+      </c>
+      <c r="U299" t="s">
+        <v>43</v>
+      </c>
+      <c r="V299" t="s">
+        <v>44</v>
+      </c>
+      <c r="W299" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>738</v>
+      </c>
+      <c r="B300" t="s">
+        <v>739</v>
+      </c>
+      <c r="C300" t="s">
+        <v>34</v>
+      </c>
+      <c r="D300" t="s">
+        <v>35</v>
+      </c>
+      <c r="E300" t="s">
+        <v>36</v>
+      </c>
+      <c r="F300" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G300" t="s">
+        <v>150</v>
+      </c>
+      <c r="H300" t="s">
+        <v>151</v>
+      </c>
+      <c r="I300" t="s">
+        <v>152</v>
+      </c>
+      <c r="J300">
+        <v>2</v>
+      </c>
+      <c r="K300">
+        <v>13.42</v>
+      </c>
+      <c r="L300">
+        <v>26.84</v>
+      </c>
+      <c r="M300" t="s">
+        <v>22</v>
+      </c>
+      <c r="N300" t="s">
+        <v>23</v>
+      </c>
+      <c r="O300" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P300" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q300" t="s">
+        <v>24</v>
+      </c>
+      <c r="R300" t="s">
+        <v>41</v>
+      </c>
+      <c r="S300" t="s">
+        <v>630</v>
+      </c>
+      <c r="T300" t="s">
+        <v>42</v>
+      </c>
+      <c r="U300" t="s">
+        <v>43</v>
+      </c>
+      <c r="V300" t="s">
+        <v>44</v>
+      </c>
+      <c r="W300" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>738</v>
+      </c>
+      <c r="B301" t="s">
+        <v>739</v>
+      </c>
+      <c r="C301" t="s">
+        <v>34</v>
+      </c>
+      <c r="D301" t="s">
+        <v>35</v>
+      </c>
+      <c r="E301" t="s">
+        <v>36</v>
+      </c>
+      <c r="F301" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G301" t="s">
+        <v>750</v>
+      </c>
+      <c r="H301" t="s">
+        <v>751</v>
+      </c>
+      <c r="I301" t="s">
+        <v>752</v>
+      </c>
+      <c r="J301">
+        <v>1</v>
+      </c>
+      <c r="K301">
+        <v>13.87</v>
+      </c>
+      <c r="L301">
+        <v>13.87</v>
+      </c>
+      <c r="M301" t="s">
+        <v>22</v>
+      </c>
+      <c r="N301" t="s">
+        <v>23</v>
+      </c>
+      <c r="O301" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P301" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q301" t="s">
+        <v>24</v>
+      </c>
+      <c r="R301" t="s">
+        <v>41</v>
+      </c>
+      <c r="S301" t="s">
+        <v>630</v>
+      </c>
+      <c r="T301" t="s">
+        <v>42</v>
+      </c>
+      <c r="U301" t="s">
+        <v>43</v>
+      </c>
+      <c r="V301" t="s">
+        <v>44</v>
+      </c>
+      <c r="W301" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>738</v>
+      </c>
+      <c r="B302" t="s">
+        <v>739</v>
+      </c>
+      <c r="C302" t="s">
+        <v>34</v>
+      </c>
+      <c r="D302" t="s">
+        <v>35</v>
+      </c>
+      <c r="E302" t="s">
+        <v>36</v>
+      </c>
+      <c r="F302" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G302" t="s">
+        <v>105</v>
+      </c>
+      <c r="H302" t="s">
+        <v>106</v>
+      </c>
+      <c r="I302" t="s">
+        <v>107</v>
+      </c>
+      <c r="J302">
+        <v>1</v>
+      </c>
+      <c r="K302">
+        <v>13.87</v>
+      </c>
+      <c r="L302">
+        <v>13.87</v>
+      </c>
+      <c r="M302" t="s">
+        <v>22</v>
+      </c>
+      <c r="N302" t="s">
+        <v>23</v>
+      </c>
+      <c r="O302" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P302" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q302" t="s">
+        <v>24</v>
+      </c>
+      <c r="R302" t="s">
+        <v>41</v>
+      </c>
+      <c r="S302" t="s">
+        <v>630</v>
+      </c>
+      <c r="T302" t="s">
+        <v>42</v>
+      </c>
+      <c r="U302" t="s">
+        <v>43</v>
+      </c>
+      <c r="V302" t="s">
+        <v>44</v>
+      </c>
+      <c r="W302" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>738</v>
+      </c>
+      <c r="B303" t="s">
+        <v>739</v>
+      </c>
+      <c r="C303" t="s">
+        <v>34</v>
+      </c>
+      <c r="D303" t="s">
+        <v>35</v>
+      </c>
+      <c r="E303" t="s">
+        <v>36</v>
+      </c>
+      <c r="F303" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G303" t="s">
+        <v>753</v>
+      </c>
+      <c r="H303" t="s">
+        <v>754</v>
+      </c>
+      <c r="I303" t="s">
+        <v>755</v>
+      </c>
+      <c r="J303">
+        <v>2</v>
+      </c>
+      <c r="K303">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="L303">
+        <v>33.119999999999997</v>
+      </c>
+      <c r="M303" t="s">
+        <v>22</v>
+      </c>
+      <c r="N303" t="s">
+        <v>23</v>
+      </c>
+      <c r="O303" s="1">
+        <v>46157</v>
+      </c>
+      <c r="P303" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q303" t="s">
+        <v>24</v>
+      </c>
+      <c r="R303" t="s">
+        <v>41</v>
+      </c>
+      <c r="S303" t="s">
+        <v>630</v>
+      </c>
+      <c r="T303" t="s">
+        <v>42</v>
+      </c>
+      <c r="U303" t="s">
+        <v>43</v>
+      </c>
+      <c r="V303" t="s">
+        <v>44</v>
+      </c>
+      <c r="W303" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="304" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>756</v>
+      </c>
+      <c r="B304" t="s">
+        <v>757</v>
+      </c>
+      <c r="C304" t="s">
+        <v>34</v>
+      </c>
+      <c r="D304" t="s">
+        <v>35</v>
+      </c>
+      <c r="E304" t="s">
+        <v>36</v>
+      </c>
+      <c r="F304" s="1">
+        <v>46161</v>
+      </c>
+      <c r="G304" t="s">
+        <v>758</v>
+      </c>
+      <c r="H304" t="s">
+        <v>759</v>
+      </c>
+      <c r="I304" t="s">
+        <v>760</v>
+      </c>
+      <c r="J304">
+        <v>1</v>
+      </c>
+      <c r="K304">
+        <v>50.83</v>
+      </c>
+      <c r="L304">
+        <v>50.83</v>
+      </c>
+      <c r="M304" t="s">
+        <v>22</v>
+      </c>
+      <c r="N304" t="s">
+        <v>23</v>
+      </c>
+      <c r="O304" s="1">
+        <v>46160</v>
+      </c>
+      <c r="P304" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q304" t="s">
+        <v>24</v>
+      </c>
+      <c r="R304" t="s">
+        <v>41</v>
+      </c>
+      <c r="S304" t="s">
+        <v>630</v>
+      </c>
+      <c r="T304" t="s">
+        <v>42</v>
+      </c>
+      <c r="U304" t="s">
+        <v>43</v>
+      </c>
+      <c r="V304" t="s">
+        <v>44</v>
+      </c>
+      <c r="W304" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>762</v>
+      </c>
+      <c r="B305" t="s">
+        <v>763</v>
+      </c>
+      <c r="C305" t="s">
+        <v>34</v>
+      </c>
+      <c r="D305" t="s">
+        <v>35</v>
+      </c>
+      <c r="E305" t="s">
+        <v>36</v>
+      </c>
+      <c r="F305" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G305" t="s">
+        <v>150</v>
+      </c>
+      <c r="H305" t="s">
+        <v>151</v>
+      </c>
+      <c r="I305" t="s">
+        <v>152</v>
+      </c>
+      <c r="J305">
+        <v>1</v>
+      </c>
+      <c r="K305">
+        <v>13.42</v>
+      </c>
+      <c r="L305">
+        <v>13.42</v>
+      </c>
+      <c r="M305" t="s">
+        <v>22</v>
+      </c>
+      <c r="N305" t="s">
+        <v>23</v>
+      </c>
+      <c r="O305" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P305" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q305" t="s">
+        <v>24</v>
+      </c>
+      <c r="R305" t="s">
+        <v>41</v>
+      </c>
+      <c r="S305" t="s">
+        <v>630</v>
+      </c>
+      <c r="T305" t="s">
+        <v>42</v>
+      </c>
+      <c r="U305" t="s">
+        <v>43</v>
+      </c>
+      <c r="V305" t="s">
+        <v>44</v>
+      </c>
+      <c r="W305" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>762</v>
+      </c>
+      <c r="B306" t="s">
+        <v>763</v>
+      </c>
+      <c r="C306" t="s">
+        <v>34</v>
+      </c>
+      <c r="D306" t="s">
+        <v>35</v>
+      </c>
+      <c r="E306" t="s">
+        <v>36</v>
+      </c>
+      <c r="F306" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G306" t="s">
+        <v>452</v>
+      </c>
+      <c r="H306" t="s">
+        <v>453</v>
+      </c>
+      <c r="I306" t="s">
+        <v>454</v>
+      </c>
+      <c r="J306">
+        <v>2</v>
+      </c>
+      <c r="K306">
+        <v>15.5</v>
+      </c>
+      <c r="L306">
+        <v>31</v>
+      </c>
+      <c r="M306" t="s">
+        <v>22</v>
+      </c>
+      <c r="N306" t="s">
+        <v>23</v>
+      </c>
+      <c r="O306" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P306" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q306" t="s">
+        <v>24</v>
+      </c>
+      <c r="R306" t="s">
+        <v>41</v>
+      </c>
+      <c r="S306" t="s">
+        <v>630</v>
+      </c>
+      <c r="T306" t="s">
+        <v>42</v>
+      </c>
+      <c r="U306" t="s">
+        <v>43</v>
+      </c>
+      <c r="V306" t="s">
+        <v>44</v>
+      </c>
+      <c r="W306" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="307" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>762</v>
+      </c>
+      <c r="B307" t="s">
+        <v>763</v>
+      </c>
+      <c r="C307" t="s">
+        <v>34</v>
+      </c>
+      <c r="D307" t="s">
+        <v>35</v>
+      </c>
+      <c r="E307" t="s">
+        <v>36</v>
+      </c>
+      <c r="F307" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G307" t="s">
+        <v>422</v>
+      </c>
+      <c r="H307" t="s">
+        <v>423</v>
+      </c>
+      <c r="I307" t="s">
+        <v>424</v>
+      </c>
+      <c r="J307">
+        <v>1</v>
+      </c>
+      <c r="K307">
+        <v>14.79</v>
+      </c>
+      <c r="L307">
+        <v>14.79</v>
+      </c>
+      <c r="M307" t="s">
+        <v>22</v>
+      </c>
+      <c r="N307" t="s">
+        <v>23</v>
+      </c>
+      <c r="O307" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P307" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q307" t="s">
+        <v>24</v>
+      </c>
+      <c r="R307" t="s">
+        <v>41</v>
+      </c>
+      <c r="S307" t="s">
+        <v>630</v>
+      </c>
+      <c r="T307" t="s">
+        <v>42</v>
+      </c>
+      <c r="U307" t="s">
+        <v>43</v>
+      </c>
+      <c r="V307" t="s">
+        <v>44</v>
+      </c>
+      <c r="W307" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="308" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>762</v>
+      </c>
+      <c r="B308" t="s">
+        <v>763</v>
+      </c>
+      <c r="C308" t="s">
+        <v>34</v>
+      </c>
+      <c r="D308" t="s">
+        <v>35</v>
+      </c>
+      <c r="E308" t="s">
+        <v>36</v>
+      </c>
+      <c r="F308" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G308" t="s">
+        <v>765</v>
+      </c>
+      <c r="H308" t="s">
+        <v>766</v>
+      </c>
+      <c r="I308" t="s">
+        <v>767</v>
+      </c>
+      <c r="J308">
+        <v>1</v>
+      </c>
+      <c r="K308">
+        <v>34.880000000000003</v>
+      </c>
+      <c r="L308">
+        <v>34.880000000000003</v>
+      </c>
+      <c r="M308" t="s">
+        <v>22</v>
+      </c>
+      <c r="N308" t="s">
+        <v>23</v>
+      </c>
+      <c r="O308" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P308" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q308" t="s">
+        <v>24</v>
+      </c>
+      <c r="R308" t="s">
+        <v>41</v>
+      </c>
+      <c r="S308" t="s">
+        <v>630</v>
+      </c>
+      <c r="T308" t="s">
+        <v>42</v>
+      </c>
+      <c r="U308" t="s">
+        <v>43</v>
+      </c>
+      <c r="V308" t="s">
+        <v>44</v>
+      </c>
+      <c r="W308" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="309" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>762</v>
+      </c>
+      <c r="B309" t="s">
+        <v>763</v>
+      </c>
+      <c r="C309" t="s">
+        <v>34</v>
+      </c>
+      <c r="D309" t="s">
+        <v>35</v>
+      </c>
+      <c r="E309" t="s">
+        <v>36</v>
+      </c>
+      <c r="F309" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G309" t="s">
+        <v>768</v>
+      </c>
+      <c r="H309" t="s">
+        <v>769</v>
+      </c>
+      <c r="I309" t="s">
+        <v>770</v>
+      </c>
+      <c r="J309">
+        <v>2</v>
+      </c>
+      <c r="K309">
+        <v>3</v>
+      </c>
+      <c r="L309">
+        <v>6</v>
+      </c>
+      <c r="M309" t="s">
+        <v>22</v>
+      </c>
+      <c r="N309" t="s">
+        <v>23</v>
+      </c>
+      <c r="O309" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P309" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q309" t="s">
+        <v>24</v>
+      </c>
+      <c r="R309" t="s">
+        <v>41</v>
+      </c>
+      <c r="S309" t="s">
+        <v>630</v>
+      </c>
+      <c r="T309" t="s">
+        <v>42</v>
+      </c>
+      <c r="U309" t="s">
+        <v>43</v>
+      </c>
+      <c r="V309" t="s">
+        <v>44</v>
+      </c>
+      <c r="W309" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="310" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>771</v>
+      </c>
+      <c r="B310" t="s">
+        <v>772</v>
+      </c>
+      <c r="C310" t="s">
+        <v>34</v>
+      </c>
+      <c r="D310" t="s">
+        <v>35</v>
+      </c>
+      <c r="E310" t="s">
+        <v>36</v>
+      </c>
+      <c r="F310" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G310" t="s">
+        <v>773</v>
+      </c>
+      <c r="H310" t="s">
+        <v>774</v>
+      </c>
+      <c r="I310" t="s">
+        <v>775</v>
+      </c>
+      <c r="J310">
+        <v>1</v>
+      </c>
+      <c r="K310">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="L310">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="M310" t="s">
+        <v>22</v>
+      </c>
+      <c r="N310" t="s">
+        <v>23</v>
+      </c>
+      <c r="O310" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P310" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q310" t="s">
+        <v>24</v>
+      </c>
+      <c r="R310" t="s">
+        <v>41</v>
+      </c>
+      <c r="S310" t="s">
+        <v>630</v>
+      </c>
+      <c r="T310" t="s">
+        <v>42</v>
+      </c>
+      <c r="U310" t="s">
+        <v>43</v>
+      </c>
+      <c r="V310" t="s">
+        <v>44</v>
+      </c>
+      <c r="W310" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="311" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>771</v>
+      </c>
+      <c r="B311" t="s">
+        <v>772</v>
+      </c>
+      <c r="C311" t="s">
+        <v>34</v>
+      </c>
+      <c r="D311" t="s">
+        <v>35</v>
+      </c>
+      <c r="E311" t="s">
+        <v>36</v>
+      </c>
+      <c r="F311" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G311" t="s">
+        <v>242</v>
+      </c>
+      <c r="H311" t="s">
+        <v>243</v>
+      </c>
+      <c r="I311" t="s">
+        <v>244</v>
+      </c>
+      <c r="J311">
+        <v>2</v>
+      </c>
+      <c r="K311">
+        <v>16.420000000000002</v>
+      </c>
+      <c r="L311">
+        <v>32.840000000000003</v>
+      </c>
+      <c r="M311" t="s">
+        <v>22</v>
+      </c>
+      <c r="N311" t="s">
+        <v>23</v>
+      </c>
+      <c r="O311" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P311" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q311" t="s">
+        <v>24</v>
+      </c>
+      <c r="R311" t="s">
+        <v>41</v>
+      </c>
+      <c r="S311" t="s">
+        <v>630</v>
+      </c>
+      <c r="T311" t="s">
+        <v>42</v>
+      </c>
+      <c r="U311" t="s">
+        <v>43</v>
+      </c>
+      <c r="V311" t="s">
+        <v>44</v>
+      </c>
+      <c r="W311" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="312" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>771</v>
+      </c>
+      <c r="B312" t="s">
+        <v>772</v>
+      </c>
+      <c r="C312" t="s">
+        <v>34</v>
+      </c>
+      <c r="D312" t="s">
+        <v>35</v>
+      </c>
+      <c r="E312" t="s">
+        <v>36</v>
+      </c>
+      <c r="F312" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G312" t="s">
+        <v>291</v>
+      </c>
+      <c r="H312" t="s">
+        <v>292</v>
+      </c>
+      <c r="I312" t="s">
+        <v>293</v>
+      </c>
+      <c r="J312">
+        <v>1</v>
+      </c>
+      <c r="K312">
+        <v>11.33</v>
+      </c>
+      <c r="L312">
+        <v>11.33</v>
+      </c>
+      <c r="M312" t="s">
+        <v>22</v>
+      </c>
+      <c r="N312" t="s">
+        <v>23</v>
+      </c>
+      <c r="O312" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P312" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q312" t="s">
+        <v>24</v>
+      </c>
+      <c r="R312" t="s">
+        <v>41</v>
+      </c>
+      <c r="S312" t="s">
+        <v>630</v>
+      </c>
+      <c r="T312" t="s">
+        <v>42</v>
+      </c>
+      <c r="U312" t="s">
+        <v>43</v>
+      </c>
+      <c r="V312" t="s">
+        <v>44</v>
+      </c>
+      <c r="W312" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="313" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>771</v>
+      </c>
+      <c r="B313" t="s">
+        <v>772</v>
+      </c>
+      <c r="C313" t="s">
+        <v>34</v>
+      </c>
+      <c r="D313" t="s">
+        <v>35</v>
+      </c>
+      <c r="E313" t="s">
+        <v>36</v>
+      </c>
+      <c r="F313" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G313" t="s">
+        <v>294</v>
+      </c>
+      <c r="H313" t="s">
+        <v>295</v>
+      </c>
+      <c r="I313" t="s">
+        <v>296</v>
+      </c>
+      <c r="J313">
+        <v>6</v>
+      </c>
+      <c r="K313">
+        <v>8.34</v>
+      </c>
+      <c r="L313">
+        <v>50.04</v>
+      </c>
+      <c r="M313" t="s">
+        <v>22</v>
+      </c>
+      <c r="N313" t="s">
+        <v>23</v>
+      </c>
+      <c r="O313" s="1">
+        <v>46164</v>
+      </c>
+      <c r="P313" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q313" t="s">
+        <v>24</v>
+      </c>
+      <c r="R313" t="s">
+        <v>41</v>
+      </c>
+      <c r="S313" t="s">
+        <v>630</v>
+      </c>
+      <c r="T313" t="s">
+        <v>42</v>
+      </c>
+      <c r="U313" t="s">
+        <v>43</v>
+      </c>
+      <c r="V313" t="s">
+        <v>44</v>
+      </c>
+      <c r="W313" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="314" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>776</v>
+      </c>
+      <c r="B314" t="s">
+        <v>777</v>
+      </c>
+      <c r="C314" t="s">
+        <v>34</v>
+      </c>
+      <c r="D314" t="s">
+        <v>35</v>
+      </c>
+      <c r="E314" t="s">
+        <v>36</v>
+      </c>
+      <c r="F314" s="1">
+        <v>46169</v>
+      </c>
+      <c r="G314" t="s">
+        <v>329</v>
+      </c>
+      <c r="H314" t="s">
+        <v>330</v>
+      </c>
+      <c r="I314" t="s">
+        <v>331</v>
+      </c>
+      <c r="J314">
+        <v>1</v>
+      </c>
+      <c r="K314">
+        <v>11.19</v>
+      </c>
+      <c r="L314">
+        <v>11.19</v>
+      </c>
+      <c r="M314" t="s">
+        <v>22</v>
+      </c>
+      <c r="N314" t="s">
+        <v>23</v>
+      </c>
+      <c r="O314" s="1">
+        <v>46169</v>
+      </c>
+      <c r="P314" t="s">
+        <v>778</v>
+      </c>
+      <c r="Q314" t="s">
+        <v>24</v>
+      </c>
+      <c r="R314" t="s">
+        <v>41</v>
+      </c>
+      <c r="S314" t="s">
+        <v>630</v>
+      </c>
+      <c r="T314" t="s">
+        <v>42</v>
+      </c>
+      <c r="U314" t="s">
+        <v>43</v>
+      </c>
+      <c r="V314" t="s">
+        <v>44</v>
+      </c>
+      <c r="W314" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="315" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>776</v>
+      </c>
+      <c r="B315" t="s">
+        <v>777</v>
+      </c>
+      <c r="C315" t="s">
+        <v>34</v>
+      </c>
+      <c r="D315" t="s">
+        <v>35</v>
+      </c>
+      <c r="E315" t="s">
+        <v>36</v>
+      </c>
+      <c r="F315" s="1">
+        <v>46169</v>
+      </c>
+      <c r="G315" t="s">
+        <v>779</v>
+      </c>
+      <c r="H315" t="s">
+        <v>780</v>
+      </c>
+      <c r="I315" t="s">
+        <v>781</v>
+      </c>
+      <c r="J315">
+        <v>1</v>
+      </c>
+      <c r="K315">
+        <v>11.33</v>
+      </c>
+      <c r="L315">
+        <v>11.33</v>
+      </c>
+      <c r="M315" t="s">
+        <v>22</v>
+      </c>
+      <c r="N315" t="s">
+        <v>23</v>
+      </c>
+      <c r="O315" s="1">
+        <v>46169</v>
+      </c>
+      <c r="P315" t="s">
+        <v>778</v>
+      </c>
+      <c r="Q315" t="s">
+        <v>24</v>
+      </c>
+      <c r="R315" t="s">
+        <v>41</v>
+      </c>
+      <c r="S315" t="s">
+        <v>630</v>
+      </c>
+      <c r="T315" t="s">
+        <v>42</v>
+      </c>
+      <c r="U315" t="s">
+        <v>43</v>
+      </c>
+      <c r="V315" t="s">
+        <v>44</v>
+      </c>
+      <c r="W315" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="316" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>782</v>
+      </c>
+      <c r="B316" t="s">
+        <v>783</v>
+      </c>
+      <c r="C316" t="s">
+        <v>34</v>
+      </c>
+      <c r="D316" t="s">
+        <v>35</v>
+      </c>
+      <c r="E316" t="s">
+        <v>36</v>
+      </c>
+      <c r="F316" s="1">
+        <v>46171</v>
+      </c>
+      <c r="G316" t="s">
+        <v>294</v>
+      </c>
+      <c r="H316" t="s">
+        <v>295</v>
+      </c>
+      <c r="I316" t="s">
+        <v>296</v>
+      </c>
+      <c r="J316">
+        <v>6</v>
+      </c>
+      <c r="K316">
+        <v>8.34</v>
+      </c>
+      <c r="L316">
+        <v>50.04</v>
+      </c>
+      <c r="M316" t="s">
+        <v>22</v>
+      </c>
+      <c r="N316" t="s">
+        <v>23</v>
+      </c>
+      <c r="O316" s="1">
+        <v>46170</v>
+      </c>
+      <c r="P316" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q316" t="s">
+        <v>24</v>
+      </c>
+      <c r="R316" t="s">
+        <v>41</v>
+      </c>
+      <c r="S316" t="s">
+        <v>630</v>
+      </c>
+      <c r="T316" t="s">
+        <v>42</v>
+      </c>
+      <c r="U316" t="s">
+        <v>43</v>
+      </c>
+      <c r="V316" t="s">
+        <v>44</v>
+      </c>
+      <c r="W316" t="s">
+        <v>784</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -21616,12 +25283,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21763,15 +25427,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21795,10 +25463,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/activitereelford-2026.xlsx
+++ b/activitereelford-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666F1299-505C-46C6-B790-46384CB824F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B409BE6D-8676-4DBF-AEAA-9034A4009649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5701" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7195" uniqueCount="893">
   <si>
     <t>N°commande</t>
   </si>
@@ -2392,6 +2392,330 @@
   </si>
   <si>
     <t>Mai</t>
+  </si>
+  <si>
+    <t>26414352</t>
+  </si>
+  <si>
+    <t>26615445</t>
+  </si>
+  <si>
+    <t>CDE FORD HEROUVILLE PREPA</t>
+  </si>
+  <si>
+    <t>26414437</t>
+  </si>
+  <si>
+    <t>26615476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86119 24                 </t>
+  </si>
+  <si>
+    <t>86119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGINE FLUSH SANS SOLVANT                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C DE LEXO PERF           </t>
+  </si>
+  <si>
+    <t>26414533</t>
+  </si>
+  <si>
+    <t>26615582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOCARS CARROSSERIE      </t>
+  </si>
+  <si>
+    <t>26414534</t>
+  </si>
+  <si>
+    <t>26615583</t>
+  </si>
+  <si>
+    <t>CDE MICKA AUTOMOBILES+STO</t>
+  </si>
+  <si>
+    <t>26414760</t>
+  </si>
+  <si>
+    <t>26615795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE HUET+STOCK       </t>
+  </si>
+  <si>
+    <t>26414866</t>
+  </si>
+  <si>
+    <t>26615990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84346 00                 </t>
+  </si>
+  <si>
+    <t>84346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROSSE APPLICATEUR POUR PRESSURE PACK C1200                  </t>
+  </si>
+  <si>
+    <t>26414986</t>
+  </si>
+  <si>
+    <t>26616029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0106 00                 </t>
+  </si>
+  <si>
+    <t>E0106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAQUET DE 5 LAMES 19MM NZ1347                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">83661 02                 </t>
+  </si>
+  <si>
+    <t>83661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIMAIRE PROTECTEUR NOIR                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85776 22                 </t>
+  </si>
+  <si>
+    <t>85776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINEN TAPE - RUBAN TEXTILE ADHESIF 19 MM                     </t>
+  </si>
+  <si>
+    <t>26414987</t>
+  </si>
+  <si>
+    <t>26616030</t>
+  </si>
+  <si>
+    <t>CDE FORD LEGRAND PT AUDEM</t>
+  </si>
+  <si>
+    <t>26415167</t>
+  </si>
+  <si>
+    <t>26616372</t>
+  </si>
+  <si>
+    <t>CDE STOCK MAG FORD HEROUV</t>
+  </si>
+  <si>
+    <t>26415265</t>
+  </si>
+  <si>
+    <t>26616408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE CARR FORD HEROUVILLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85924 00                 </t>
+  </si>
+  <si>
+    <t>85924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMPON MOUSSE ORANGE 150MM X30MM                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85925 00                 </t>
+  </si>
+  <si>
+    <t>85925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMPON MOUSSE NOIR 150MMX 30MM                               </t>
+  </si>
+  <si>
+    <t>26415266</t>
+  </si>
+  <si>
+    <t>26616409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE MECA FPRD HEROUVILLE </t>
+  </si>
+  <si>
+    <t>26415267</t>
+  </si>
+  <si>
+    <t>26616410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE MAG FORD HEROUVILLE  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86669 24                 </t>
+  </si>
+  <si>
+    <t>86669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPF CLEANER ULTRA BOUT. 250ML                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87117 10                 </t>
+  </si>
+  <si>
+    <t>87117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARTON ULTRAFILL 3 - GRIS(x12)                               </t>
+  </si>
+  <si>
+    <t>26415490</t>
+  </si>
+  <si>
+    <t>26616713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOCK MAG HEROUVILLE     </t>
+  </si>
+  <si>
+    <t>26415779</t>
+  </si>
+  <si>
+    <t>26616967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFFERT EC AUTO VU TARIK  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86884 10                 </t>
+  </si>
+  <si>
+    <t>86884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILI GASKET NEUTRAL CART 200ML REMPLACE 85283                </t>
+  </si>
+  <si>
+    <t>26416219</t>
+  </si>
+  <si>
+    <t>26617449</t>
+  </si>
+  <si>
+    <t>26416220</t>
+  </si>
+  <si>
+    <t>26617450</t>
+  </si>
+  <si>
+    <t>CDE CARROSSERIE CALAIS EX</t>
+  </si>
+  <si>
+    <t>26416221</t>
+  </si>
+  <si>
+    <t>26617451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86414 00                 </t>
+  </si>
+  <si>
+    <t>86414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMPON MOUSSE VIOLET 165 MM                                  </t>
+  </si>
+  <si>
+    <t>26416801</t>
+  </si>
+  <si>
+    <t>26617962</t>
+  </si>
+  <si>
+    <t>26416964</t>
+  </si>
+  <si>
+    <t>26618123</t>
+  </si>
+  <si>
+    <t>CDE GGE PIERRE AUTOMOBILE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1340 33                 </t>
+  </si>
+  <si>
+    <t>A1340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISQUES DURALITE 75MM P400 50/PK                             </t>
+  </si>
+  <si>
+    <t>26416994</t>
+  </si>
+  <si>
+    <t>26618238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGE BIWEER AUTO          </t>
+  </si>
+  <si>
+    <t>26416997</t>
+  </si>
+  <si>
+    <t>26618240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1474 00                 </t>
+  </si>
+  <si>
+    <t>A1474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINECUT 4000 77 MM (VERT) P4000   (x10)                      </t>
+  </si>
+  <si>
+    <t>26417173</t>
+  </si>
+  <si>
+    <t>26618407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84835 10                 </t>
+  </si>
+  <si>
+    <t>84835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOS2 NETTOYANT CARBURATEUR 500ML                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE JDM AUTO + STOCK MAG </t>
+  </si>
+  <si>
+    <t>26417354</t>
+  </si>
+  <si>
+    <t>26618550</t>
+  </si>
+  <si>
+    <t>CDE STOCK MAG+ERIC LEMIER</t>
+  </si>
+  <si>
+    <t>26417374</t>
+  </si>
+  <si>
+    <t>26618564</t>
+  </si>
+  <si>
+    <t>Juin</t>
   </si>
 </sst>
 </file>
@@ -2773,7 +3097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W316"/>
+  <dimension ref="A1:W399"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -25236,6 +25560,5899 @@
         <v>784</v>
       </c>
     </row>
+    <row r="317" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>785</v>
+      </c>
+      <c r="B317" t="s">
+        <v>786</v>
+      </c>
+      <c r="C317" t="s">
+        <v>34</v>
+      </c>
+      <c r="D317" t="s">
+        <v>35</v>
+      </c>
+      <c r="E317" t="s">
+        <v>36</v>
+      </c>
+      <c r="F317" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G317" t="s">
+        <v>486</v>
+      </c>
+      <c r="H317" t="s">
+        <v>487</v>
+      </c>
+      <c r="I317" t="s">
+        <v>488</v>
+      </c>
+      <c r="J317">
+        <v>1</v>
+      </c>
+      <c r="K317">
+        <v>527.11</v>
+      </c>
+      <c r="L317">
+        <v>527.11</v>
+      </c>
+      <c r="M317" t="s">
+        <v>22</v>
+      </c>
+      <c r="N317" t="s">
+        <v>23</v>
+      </c>
+      <c r="O317" s="1">
+        <v>46174</v>
+      </c>
+      <c r="P317" t="s">
+        <v>787</v>
+      </c>
+      <c r="Q317" t="s">
+        <v>24</v>
+      </c>
+      <c r="R317" t="s">
+        <v>41</v>
+      </c>
+      <c r="S317" t="s">
+        <v>630</v>
+      </c>
+      <c r="T317" t="s">
+        <v>42</v>
+      </c>
+      <c r="U317" t="s">
+        <v>43</v>
+      </c>
+      <c r="V317" t="s">
+        <v>44</v>
+      </c>
+      <c r="W317" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="318" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>788</v>
+      </c>
+      <c r="B318" t="s">
+        <v>789</v>
+      </c>
+      <c r="C318" t="s">
+        <v>34</v>
+      </c>
+      <c r="D318" t="s">
+        <v>35</v>
+      </c>
+      <c r="E318" t="s">
+        <v>36</v>
+      </c>
+      <c r="F318" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G318" t="s">
+        <v>790</v>
+      </c>
+      <c r="H318" t="s">
+        <v>791</v>
+      </c>
+      <c r="I318" t="s">
+        <v>792</v>
+      </c>
+      <c r="J318">
+        <v>4</v>
+      </c>
+      <c r="K318">
+        <v>6.52</v>
+      </c>
+      <c r="L318">
+        <v>26.08</v>
+      </c>
+      <c r="M318" t="s">
+        <v>22</v>
+      </c>
+      <c r="N318" t="s">
+        <v>23</v>
+      </c>
+      <c r="O318" s="1">
+        <v>46174</v>
+      </c>
+      <c r="P318" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q318" t="s">
+        <v>24</v>
+      </c>
+      <c r="R318" t="s">
+        <v>41</v>
+      </c>
+      <c r="S318" t="s">
+        <v>630</v>
+      </c>
+      <c r="T318" t="s">
+        <v>42</v>
+      </c>
+      <c r="U318" t="s">
+        <v>43</v>
+      </c>
+      <c r="V318" t="s">
+        <v>44</v>
+      </c>
+      <c r="W318" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="319" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>788</v>
+      </c>
+      <c r="B319" t="s">
+        <v>789</v>
+      </c>
+      <c r="C319" t="s">
+        <v>34</v>
+      </c>
+      <c r="D319" t="s">
+        <v>35</v>
+      </c>
+      <c r="E319" t="s">
+        <v>36</v>
+      </c>
+      <c r="F319" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G319" t="s">
+        <v>72</v>
+      </c>
+      <c r="H319" t="s">
+        <v>73</v>
+      </c>
+      <c r="I319" t="s">
+        <v>74</v>
+      </c>
+      <c r="J319">
+        <v>1</v>
+      </c>
+      <c r="K319">
+        <v>50.32</v>
+      </c>
+      <c r="L319">
+        <v>50.32</v>
+      </c>
+      <c r="M319" t="s">
+        <v>22</v>
+      </c>
+      <c r="N319" t="s">
+        <v>23</v>
+      </c>
+      <c r="O319" s="1">
+        <v>46174</v>
+      </c>
+      <c r="P319" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q319" t="s">
+        <v>24</v>
+      </c>
+      <c r="R319" t="s">
+        <v>41</v>
+      </c>
+      <c r="S319" t="s">
+        <v>630</v>
+      </c>
+      <c r="T319" t="s">
+        <v>42</v>
+      </c>
+      <c r="U319" t="s">
+        <v>43</v>
+      </c>
+      <c r="V319" t="s">
+        <v>44</v>
+      </c>
+      <c r="W319" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="320" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>788</v>
+      </c>
+      <c r="B320" t="s">
+        <v>789</v>
+      </c>
+      <c r="C320" t="s">
+        <v>34</v>
+      </c>
+      <c r="D320" t="s">
+        <v>35</v>
+      </c>
+      <c r="E320" t="s">
+        <v>36</v>
+      </c>
+      <c r="F320" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G320" t="s">
+        <v>75</v>
+      </c>
+      <c r="H320" t="s">
+        <v>76</v>
+      </c>
+      <c r="I320" t="s">
+        <v>77</v>
+      </c>
+      <c r="J320">
+        <v>12</v>
+      </c>
+      <c r="K320">
+        <v>9.32</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+      <c r="M320" t="s">
+        <v>22</v>
+      </c>
+      <c r="N320" t="s">
+        <v>23</v>
+      </c>
+      <c r="O320" s="1">
+        <v>46174</v>
+      </c>
+      <c r="P320" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q320" t="s">
+        <v>24</v>
+      </c>
+      <c r="R320" t="s">
+        <v>41</v>
+      </c>
+      <c r="S320" t="s">
+        <v>630</v>
+      </c>
+      <c r="T320" t="s">
+        <v>42</v>
+      </c>
+      <c r="U320" t="s">
+        <v>43</v>
+      </c>
+      <c r="V320" t="s">
+        <v>44</v>
+      </c>
+      <c r="W320" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="321" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>788</v>
+      </c>
+      <c r="B321" t="s">
+        <v>789</v>
+      </c>
+      <c r="C321" t="s">
+        <v>34</v>
+      </c>
+      <c r="D321" t="s">
+        <v>35</v>
+      </c>
+      <c r="E321" t="s">
+        <v>36</v>
+      </c>
+      <c r="F321" s="1">
+        <v>46174</v>
+      </c>
+      <c r="G321" t="s">
+        <v>428</v>
+      </c>
+      <c r="H321" t="s">
+        <v>429</v>
+      </c>
+      <c r="I321" t="s">
+        <v>430</v>
+      </c>
+      <c r="J321">
+        <v>6</v>
+      </c>
+      <c r="K321">
+        <v>4.91</v>
+      </c>
+      <c r="L321">
+        <v>29.46</v>
+      </c>
+      <c r="M321" t="s">
+        <v>22</v>
+      </c>
+      <c r="N321" t="s">
+        <v>23</v>
+      </c>
+      <c r="O321" s="1">
+        <v>46174</v>
+      </c>
+      <c r="P321" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q321" t="s">
+        <v>24</v>
+      </c>
+      <c r="R321" t="s">
+        <v>41</v>
+      </c>
+      <c r="S321" t="s">
+        <v>630</v>
+      </c>
+      <c r="T321" t="s">
+        <v>42</v>
+      </c>
+      <c r="U321" t="s">
+        <v>43</v>
+      </c>
+      <c r="V321" t="s">
+        <v>44</v>
+      </c>
+      <c r="W321" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="322" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>794</v>
+      </c>
+      <c r="B322" t="s">
+        <v>795</v>
+      </c>
+      <c r="C322" t="s">
+        <v>34</v>
+      </c>
+      <c r="D322" t="s">
+        <v>35</v>
+      </c>
+      <c r="E322" t="s">
+        <v>36</v>
+      </c>
+      <c r="F322" s="1">
+        <v>46175</v>
+      </c>
+      <c r="G322" t="s">
+        <v>294</v>
+      </c>
+      <c r="H322" t="s">
+        <v>295</v>
+      </c>
+      <c r="I322" t="s">
+        <v>296</v>
+      </c>
+      <c r="J322">
+        <v>2</v>
+      </c>
+      <c r="K322">
+        <v>8.76</v>
+      </c>
+      <c r="L322">
+        <v>17.52</v>
+      </c>
+      <c r="M322" t="s">
+        <v>22</v>
+      </c>
+      <c r="N322" t="s">
+        <v>23</v>
+      </c>
+      <c r="O322" s="1">
+        <v>46174</v>
+      </c>
+      <c r="P322" t="s">
+        <v>796</v>
+      </c>
+      <c r="Q322" t="s">
+        <v>24</v>
+      </c>
+      <c r="R322" t="s">
+        <v>41</v>
+      </c>
+      <c r="S322" t="s">
+        <v>630</v>
+      </c>
+      <c r="T322" t="s">
+        <v>42</v>
+      </c>
+      <c r="U322" t="s">
+        <v>43</v>
+      </c>
+      <c r="V322" t="s">
+        <v>44</v>
+      </c>
+      <c r="W322" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="323" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>794</v>
+      </c>
+      <c r="B323" t="s">
+        <v>795</v>
+      </c>
+      <c r="C323" t="s">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>35</v>
+      </c>
+      <c r="E323" t="s">
+        <v>36</v>
+      </c>
+      <c r="F323" s="1">
+        <v>46175</v>
+      </c>
+      <c r="G323" t="s">
+        <v>206</v>
+      </c>
+      <c r="H323" t="s">
+        <v>207</v>
+      </c>
+      <c r="I323" t="s">
+        <v>208</v>
+      </c>
+      <c r="J323">
+        <v>1</v>
+      </c>
+      <c r="K323">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="L323">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="M323" t="s">
+        <v>22</v>
+      </c>
+      <c r="N323" t="s">
+        <v>23</v>
+      </c>
+      <c r="O323" s="1">
+        <v>46174</v>
+      </c>
+      <c r="P323" t="s">
+        <v>796</v>
+      </c>
+      <c r="Q323" t="s">
+        <v>24</v>
+      </c>
+      <c r="R323" t="s">
+        <v>41</v>
+      </c>
+      <c r="S323" t="s">
+        <v>630</v>
+      </c>
+      <c r="T323" t="s">
+        <v>42</v>
+      </c>
+      <c r="U323" t="s">
+        <v>43</v>
+      </c>
+      <c r="V323" t="s">
+        <v>44</v>
+      </c>
+      <c r="W323" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="324" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>797</v>
+      </c>
+      <c r="B324" t="s">
+        <v>798</v>
+      </c>
+      <c r="C324" t="s">
+        <v>34</v>
+      </c>
+      <c r="D324" t="s">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>36</v>
+      </c>
+      <c r="F324" s="1">
+        <v>46175</v>
+      </c>
+      <c r="G324" t="s">
+        <v>265</v>
+      </c>
+      <c r="H324" t="s">
+        <v>266</v>
+      </c>
+      <c r="I324" t="s">
+        <v>267</v>
+      </c>
+      <c r="J324">
+        <v>3</v>
+      </c>
+      <c r="K324">
+        <v>83.79</v>
+      </c>
+      <c r="L324">
+        <v>251.37</v>
+      </c>
+      <c r="M324" t="s">
+        <v>22</v>
+      </c>
+      <c r="N324" t="s">
+        <v>23</v>
+      </c>
+      <c r="O324" s="1">
+        <v>46174</v>
+      </c>
+      <c r="P324" t="s">
+        <v>799</v>
+      </c>
+      <c r="Q324" t="s">
+        <v>24</v>
+      </c>
+      <c r="R324" t="s">
+        <v>41</v>
+      </c>
+      <c r="S324" t="s">
+        <v>630</v>
+      </c>
+      <c r="T324" t="s">
+        <v>42</v>
+      </c>
+      <c r="U324" t="s">
+        <v>43</v>
+      </c>
+      <c r="V324" t="s">
+        <v>44</v>
+      </c>
+      <c r="W324" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="325" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>800</v>
+      </c>
+      <c r="B325" t="s">
+        <v>801</v>
+      </c>
+      <c r="C325" t="s">
+        <v>34</v>
+      </c>
+      <c r="D325" t="s">
+        <v>35</v>
+      </c>
+      <c r="E325" t="s">
+        <v>36</v>
+      </c>
+      <c r="F325" s="1">
+        <v>46176</v>
+      </c>
+      <c r="G325" t="s">
+        <v>236</v>
+      </c>
+      <c r="H325" t="s">
+        <v>237</v>
+      </c>
+      <c r="I325" t="s">
+        <v>238</v>
+      </c>
+      <c r="J325">
+        <v>6</v>
+      </c>
+      <c r="K325">
+        <v>12.86</v>
+      </c>
+      <c r="L325">
+        <v>77.16</v>
+      </c>
+      <c r="M325" t="s">
+        <v>22</v>
+      </c>
+      <c r="N325" t="s">
+        <v>23</v>
+      </c>
+      <c r="O325" s="1">
+        <v>46176</v>
+      </c>
+      <c r="P325" t="s">
+        <v>802</v>
+      </c>
+      <c r="Q325" t="s">
+        <v>24</v>
+      </c>
+      <c r="R325" t="s">
+        <v>41</v>
+      </c>
+      <c r="S325" t="s">
+        <v>630</v>
+      </c>
+      <c r="T325" t="s">
+        <v>42</v>
+      </c>
+      <c r="U325" t="s">
+        <v>43</v>
+      </c>
+      <c r="V325" t="s">
+        <v>44</v>
+      </c>
+      <c r="W325" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="326" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>803</v>
+      </c>
+      <c r="B326" t="s">
+        <v>804</v>
+      </c>
+      <c r="C326" t="s">
+        <v>34</v>
+      </c>
+      <c r="D326" t="s">
+        <v>35</v>
+      </c>
+      <c r="E326" t="s">
+        <v>36</v>
+      </c>
+      <c r="F326" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G326" t="s">
+        <v>29</v>
+      </c>
+      <c r="H326" t="s">
+        <v>30</v>
+      </c>
+      <c r="I326" t="s">
+        <v>31</v>
+      </c>
+      <c r="J326">
+        <v>2</v>
+      </c>
+      <c r="K326">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="L326">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="M326" t="s">
+        <v>22</v>
+      </c>
+      <c r="N326" t="s">
+        <v>23</v>
+      </c>
+      <c r="O326" s="1">
+        <v>46176</v>
+      </c>
+      <c r="P326" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q326" t="s">
+        <v>24</v>
+      </c>
+      <c r="R326" t="s">
+        <v>41</v>
+      </c>
+      <c r="S326" t="s">
+        <v>630</v>
+      </c>
+      <c r="T326" t="s">
+        <v>42</v>
+      </c>
+      <c r="U326" t="s">
+        <v>43</v>
+      </c>
+      <c r="V326" t="s">
+        <v>44</v>
+      </c>
+      <c r="W326" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="327" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>803</v>
+      </c>
+      <c r="B327" t="s">
+        <v>804</v>
+      </c>
+      <c r="C327" t="s">
+        <v>34</v>
+      </c>
+      <c r="D327" t="s">
+        <v>35</v>
+      </c>
+      <c r="E327" t="s">
+        <v>36</v>
+      </c>
+      <c r="F327" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G327" t="s">
+        <v>805</v>
+      </c>
+      <c r="H327" t="s">
+        <v>806</v>
+      </c>
+      <c r="I327" t="s">
+        <v>807</v>
+      </c>
+      <c r="J327">
+        <v>5</v>
+      </c>
+      <c r="K327">
+        <v>6.94</v>
+      </c>
+      <c r="L327">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="M327" t="s">
+        <v>22</v>
+      </c>
+      <c r="N327" t="s">
+        <v>23</v>
+      </c>
+      <c r="O327" s="1">
+        <v>46176</v>
+      </c>
+      <c r="P327" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q327" t="s">
+        <v>24</v>
+      </c>
+      <c r="R327" t="s">
+        <v>41</v>
+      </c>
+      <c r="S327" t="s">
+        <v>630</v>
+      </c>
+      <c r="T327" t="s">
+        <v>42</v>
+      </c>
+      <c r="U327" t="s">
+        <v>43</v>
+      </c>
+      <c r="V327" t="s">
+        <v>44</v>
+      </c>
+      <c r="W327" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="328" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>803</v>
+      </c>
+      <c r="B328" t="s">
+        <v>804</v>
+      </c>
+      <c r="C328" t="s">
+        <v>34</v>
+      </c>
+      <c r="D328" t="s">
+        <v>35</v>
+      </c>
+      <c r="E328" t="s">
+        <v>36</v>
+      </c>
+      <c r="F328" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G328" t="s">
+        <v>69</v>
+      </c>
+      <c r="H328" t="s">
+        <v>70</v>
+      </c>
+      <c r="I328" t="s">
+        <v>71</v>
+      </c>
+      <c r="J328">
+        <v>1</v>
+      </c>
+      <c r="K328">
+        <v>10.72</v>
+      </c>
+      <c r="L328">
+        <v>10.72</v>
+      </c>
+      <c r="M328" t="s">
+        <v>22</v>
+      </c>
+      <c r="N328" t="s">
+        <v>23</v>
+      </c>
+      <c r="O328" s="1">
+        <v>46176</v>
+      </c>
+      <c r="P328" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q328" t="s">
+        <v>24</v>
+      </c>
+      <c r="R328" t="s">
+        <v>41</v>
+      </c>
+      <c r="S328" t="s">
+        <v>630</v>
+      </c>
+      <c r="T328" t="s">
+        <v>42</v>
+      </c>
+      <c r="U328" t="s">
+        <v>43</v>
+      </c>
+      <c r="V328" t="s">
+        <v>44</v>
+      </c>
+      <c r="W328" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="329" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>803</v>
+      </c>
+      <c r="B329" t="s">
+        <v>804</v>
+      </c>
+      <c r="C329" t="s">
+        <v>34</v>
+      </c>
+      <c r="D329" t="s">
+        <v>35</v>
+      </c>
+      <c r="E329" t="s">
+        <v>36</v>
+      </c>
+      <c r="F329" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G329" t="s">
+        <v>227</v>
+      </c>
+      <c r="H329" t="s">
+        <v>228</v>
+      </c>
+      <c r="I329" t="s">
+        <v>229</v>
+      </c>
+      <c r="J329">
+        <v>2</v>
+      </c>
+      <c r="K329">
+        <v>16.2</v>
+      </c>
+      <c r="L329">
+        <v>32.4</v>
+      </c>
+      <c r="M329" t="s">
+        <v>22</v>
+      </c>
+      <c r="N329" t="s">
+        <v>23</v>
+      </c>
+      <c r="O329" s="1">
+        <v>46176</v>
+      </c>
+      <c r="P329" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q329" t="s">
+        <v>24</v>
+      </c>
+      <c r="R329" t="s">
+        <v>41</v>
+      </c>
+      <c r="S329" t="s">
+        <v>630</v>
+      </c>
+      <c r="T329" t="s">
+        <v>42</v>
+      </c>
+      <c r="U329" t="s">
+        <v>43</v>
+      </c>
+      <c r="V329" t="s">
+        <v>44</v>
+      </c>
+      <c r="W329" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="330" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>808</v>
+      </c>
+      <c r="B330" t="s">
+        <v>809</v>
+      </c>
+      <c r="C330" t="s">
+        <v>34</v>
+      </c>
+      <c r="D330" t="s">
+        <v>35</v>
+      </c>
+      <c r="E330" t="s">
+        <v>36</v>
+      </c>
+      <c r="F330" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G330" t="s">
+        <v>529</v>
+      </c>
+      <c r="H330" t="s">
+        <v>530</v>
+      </c>
+      <c r="I330" t="s">
+        <v>531</v>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330">
+        <v>12.86</v>
+      </c>
+      <c r="L330">
+        <v>12.86</v>
+      </c>
+      <c r="M330" t="s">
+        <v>22</v>
+      </c>
+      <c r="N330" t="s">
+        <v>23</v>
+      </c>
+      <c r="O330" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P330" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q330" t="s">
+        <v>24</v>
+      </c>
+      <c r="R330" t="s">
+        <v>41</v>
+      </c>
+      <c r="S330" t="s">
+        <v>630</v>
+      </c>
+      <c r="T330" t="s">
+        <v>42</v>
+      </c>
+      <c r="U330" t="s">
+        <v>43</v>
+      </c>
+      <c r="V330" t="s">
+        <v>44</v>
+      </c>
+      <c r="W330" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="331" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>808</v>
+      </c>
+      <c r="B331" t="s">
+        <v>809</v>
+      </c>
+      <c r="C331" t="s">
+        <v>34</v>
+      </c>
+      <c r="D331" t="s">
+        <v>35</v>
+      </c>
+      <c r="E331" t="s">
+        <v>36</v>
+      </c>
+      <c r="F331" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G331" t="s">
+        <v>476</v>
+      </c>
+      <c r="H331" t="s">
+        <v>477</v>
+      </c>
+      <c r="I331" t="s">
+        <v>478</v>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331">
+        <v>10.76</v>
+      </c>
+      <c r="L331">
+        <v>10.76</v>
+      </c>
+      <c r="M331" t="s">
+        <v>22</v>
+      </c>
+      <c r="N331" t="s">
+        <v>23</v>
+      </c>
+      <c r="O331" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P331" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q331" t="s">
+        <v>24</v>
+      </c>
+      <c r="R331" t="s">
+        <v>41</v>
+      </c>
+      <c r="S331" t="s">
+        <v>630</v>
+      </c>
+      <c r="T331" t="s">
+        <v>42</v>
+      </c>
+      <c r="U331" t="s">
+        <v>43</v>
+      </c>
+      <c r="V331" t="s">
+        <v>44</v>
+      </c>
+      <c r="W331" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="332" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>808</v>
+      </c>
+      <c r="B332" t="s">
+        <v>809</v>
+      </c>
+      <c r="C332" t="s">
+        <v>34</v>
+      </c>
+      <c r="D332" t="s">
+        <v>35</v>
+      </c>
+      <c r="E332" t="s">
+        <v>36</v>
+      </c>
+      <c r="F332" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G332" t="s">
+        <v>810</v>
+      </c>
+      <c r="H332" t="s">
+        <v>811</v>
+      </c>
+      <c r="I332" t="s">
+        <v>812</v>
+      </c>
+      <c r="J332">
+        <v>1</v>
+      </c>
+      <c r="K332">
+        <v>12.27</v>
+      </c>
+      <c r="L332">
+        <v>12.27</v>
+      </c>
+      <c r="M332" t="s">
+        <v>22</v>
+      </c>
+      <c r="N332" t="s">
+        <v>23</v>
+      </c>
+      <c r="O332" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P332" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q332" t="s">
+        <v>24</v>
+      </c>
+      <c r="R332" t="s">
+        <v>41</v>
+      </c>
+      <c r="S332" t="s">
+        <v>630</v>
+      </c>
+      <c r="T332" t="s">
+        <v>42</v>
+      </c>
+      <c r="U332" t="s">
+        <v>43</v>
+      </c>
+      <c r="V332" t="s">
+        <v>44</v>
+      </c>
+      <c r="W332" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="333" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>808</v>
+      </c>
+      <c r="B333" t="s">
+        <v>809</v>
+      </c>
+      <c r="C333" t="s">
+        <v>34</v>
+      </c>
+      <c r="D333" t="s">
+        <v>35</v>
+      </c>
+      <c r="E333" t="s">
+        <v>36</v>
+      </c>
+      <c r="F333" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G333" t="s">
+        <v>813</v>
+      </c>
+      <c r="H333" t="s">
+        <v>814</v>
+      </c>
+      <c r="I333" t="s">
+        <v>815</v>
+      </c>
+      <c r="J333">
+        <v>5</v>
+      </c>
+      <c r="K333">
+        <v>4.99</v>
+      </c>
+      <c r="L333">
+        <v>24.95</v>
+      </c>
+      <c r="M333" t="s">
+        <v>22</v>
+      </c>
+      <c r="N333" t="s">
+        <v>23</v>
+      </c>
+      <c r="O333" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P333" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q333" t="s">
+        <v>24</v>
+      </c>
+      <c r="R333" t="s">
+        <v>41</v>
+      </c>
+      <c r="S333" t="s">
+        <v>630</v>
+      </c>
+      <c r="T333" t="s">
+        <v>42</v>
+      </c>
+      <c r="U333" t="s">
+        <v>43</v>
+      </c>
+      <c r="V333" t="s">
+        <v>44</v>
+      </c>
+      <c r="W333" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="334" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>808</v>
+      </c>
+      <c r="B334" t="s">
+        <v>809</v>
+      </c>
+      <c r="C334" t="s">
+        <v>34</v>
+      </c>
+      <c r="D334" t="s">
+        <v>35</v>
+      </c>
+      <c r="E334" t="s">
+        <v>36</v>
+      </c>
+      <c r="F334" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G334" t="s">
+        <v>96</v>
+      </c>
+      <c r="H334" t="s">
+        <v>97</v>
+      </c>
+      <c r="I334" t="s">
+        <v>98</v>
+      </c>
+      <c r="J334">
+        <v>1</v>
+      </c>
+      <c r="K334">
+        <v>11.64</v>
+      </c>
+      <c r="L334">
+        <v>11.64</v>
+      </c>
+      <c r="M334" t="s">
+        <v>22</v>
+      </c>
+      <c r="N334" t="s">
+        <v>23</v>
+      </c>
+      <c r="O334" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P334" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q334" t="s">
+        <v>24</v>
+      </c>
+      <c r="R334" t="s">
+        <v>41</v>
+      </c>
+      <c r="S334" t="s">
+        <v>630</v>
+      </c>
+      <c r="T334" t="s">
+        <v>42</v>
+      </c>
+      <c r="U334" t="s">
+        <v>43</v>
+      </c>
+      <c r="V334" t="s">
+        <v>44</v>
+      </c>
+      <c r="W334" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="335" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>808</v>
+      </c>
+      <c r="B335" t="s">
+        <v>809</v>
+      </c>
+      <c r="C335" t="s">
+        <v>34</v>
+      </c>
+      <c r="D335" t="s">
+        <v>35</v>
+      </c>
+      <c r="E335" t="s">
+        <v>36</v>
+      </c>
+      <c r="F335" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G335" t="s">
+        <v>816</v>
+      </c>
+      <c r="H335" t="s">
+        <v>817</v>
+      </c>
+      <c r="I335" t="s">
+        <v>818</v>
+      </c>
+      <c r="J335">
+        <v>3</v>
+      </c>
+      <c r="K335">
+        <v>6.21</v>
+      </c>
+      <c r="L335">
+        <v>18.63</v>
+      </c>
+      <c r="M335" t="s">
+        <v>22</v>
+      </c>
+      <c r="N335" t="s">
+        <v>23</v>
+      </c>
+      <c r="O335" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P335" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q335" t="s">
+        <v>24</v>
+      </c>
+      <c r="R335" t="s">
+        <v>41</v>
+      </c>
+      <c r="S335" t="s">
+        <v>630</v>
+      </c>
+      <c r="T335" t="s">
+        <v>42</v>
+      </c>
+      <c r="U335" t="s">
+        <v>43</v>
+      </c>
+      <c r="V335" t="s">
+        <v>44</v>
+      </c>
+      <c r="W335" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="336" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>808</v>
+      </c>
+      <c r="B336" t="s">
+        <v>809</v>
+      </c>
+      <c r="C336" t="s">
+        <v>34</v>
+      </c>
+      <c r="D336" t="s">
+        <v>35</v>
+      </c>
+      <c r="E336" t="s">
+        <v>36</v>
+      </c>
+      <c r="F336" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G336" t="s">
+        <v>146</v>
+      </c>
+      <c r="H336" t="s">
+        <v>147</v>
+      </c>
+      <c r="I336" t="s">
+        <v>148</v>
+      </c>
+      <c r="J336">
+        <v>1</v>
+      </c>
+      <c r="K336">
+        <v>28.06</v>
+      </c>
+      <c r="L336">
+        <v>28.06</v>
+      </c>
+      <c r="M336" t="s">
+        <v>22</v>
+      </c>
+      <c r="N336" t="s">
+        <v>23</v>
+      </c>
+      <c r="O336" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P336" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q336" t="s">
+        <v>24</v>
+      </c>
+      <c r="R336" t="s">
+        <v>41</v>
+      </c>
+      <c r="S336" t="s">
+        <v>630</v>
+      </c>
+      <c r="T336" t="s">
+        <v>42</v>
+      </c>
+      <c r="U336" t="s">
+        <v>43</v>
+      </c>
+      <c r="V336" t="s">
+        <v>44</v>
+      </c>
+      <c r="W336" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="337" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>808</v>
+      </c>
+      <c r="B337" t="s">
+        <v>809</v>
+      </c>
+      <c r="C337" t="s">
+        <v>34</v>
+      </c>
+      <c r="D337" t="s">
+        <v>35</v>
+      </c>
+      <c r="E337" t="s">
+        <v>36</v>
+      </c>
+      <c r="F337" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G337" t="s">
+        <v>150</v>
+      </c>
+      <c r="H337" t="s">
+        <v>151</v>
+      </c>
+      <c r="I337" t="s">
+        <v>152</v>
+      </c>
+      <c r="J337">
+        <v>1</v>
+      </c>
+      <c r="K337">
+        <v>13.23</v>
+      </c>
+      <c r="L337">
+        <v>13.23</v>
+      </c>
+      <c r="M337" t="s">
+        <v>22</v>
+      </c>
+      <c r="N337" t="s">
+        <v>23</v>
+      </c>
+      <c r="O337" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P337" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q337" t="s">
+        <v>24</v>
+      </c>
+      <c r="R337" t="s">
+        <v>41</v>
+      </c>
+      <c r="S337" t="s">
+        <v>630</v>
+      </c>
+      <c r="T337" t="s">
+        <v>42</v>
+      </c>
+      <c r="U337" t="s">
+        <v>43</v>
+      </c>
+      <c r="V337" t="s">
+        <v>44</v>
+      </c>
+      <c r="W337" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="338" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>808</v>
+      </c>
+      <c r="B338" t="s">
+        <v>809</v>
+      </c>
+      <c r="C338" t="s">
+        <v>34</v>
+      </c>
+      <c r="D338" t="s">
+        <v>35</v>
+      </c>
+      <c r="E338" t="s">
+        <v>36</v>
+      </c>
+      <c r="F338" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G338" t="s">
+        <v>192</v>
+      </c>
+      <c r="H338" t="s">
+        <v>193</v>
+      </c>
+      <c r="I338" t="s">
+        <v>194</v>
+      </c>
+      <c r="J338">
+        <v>1</v>
+      </c>
+      <c r="K338">
+        <v>13.23</v>
+      </c>
+      <c r="L338">
+        <v>13.23</v>
+      </c>
+      <c r="M338" t="s">
+        <v>22</v>
+      </c>
+      <c r="N338" t="s">
+        <v>23</v>
+      </c>
+      <c r="O338" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P338" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q338" t="s">
+        <v>24</v>
+      </c>
+      <c r="R338" t="s">
+        <v>41</v>
+      </c>
+      <c r="S338" t="s">
+        <v>630</v>
+      </c>
+      <c r="T338" t="s">
+        <v>42</v>
+      </c>
+      <c r="U338" t="s">
+        <v>43</v>
+      </c>
+      <c r="V338" t="s">
+        <v>44</v>
+      </c>
+      <c r="W338" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="339" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>808</v>
+      </c>
+      <c r="B339" t="s">
+        <v>809</v>
+      </c>
+      <c r="C339" t="s">
+        <v>34</v>
+      </c>
+      <c r="D339" t="s">
+        <v>35</v>
+      </c>
+      <c r="E339" t="s">
+        <v>36</v>
+      </c>
+      <c r="F339" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G339" t="s">
+        <v>579</v>
+      </c>
+      <c r="H339" t="s">
+        <v>580</v>
+      </c>
+      <c r="I339" t="s">
+        <v>581</v>
+      </c>
+      <c r="J339">
+        <v>1</v>
+      </c>
+      <c r="K339">
+        <v>6.93</v>
+      </c>
+      <c r="L339">
+        <v>6.93</v>
+      </c>
+      <c r="M339" t="s">
+        <v>22</v>
+      </c>
+      <c r="N339" t="s">
+        <v>23</v>
+      </c>
+      <c r="O339" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P339" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q339" t="s">
+        <v>24</v>
+      </c>
+      <c r="R339" t="s">
+        <v>41</v>
+      </c>
+      <c r="S339" t="s">
+        <v>630</v>
+      </c>
+      <c r="T339" t="s">
+        <v>42</v>
+      </c>
+      <c r="U339" t="s">
+        <v>43</v>
+      </c>
+      <c r="V339" t="s">
+        <v>44</v>
+      </c>
+      <c r="W339" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="340" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>808</v>
+      </c>
+      <c r="B340" t="s">
+        <v>809</v>
+      </c>
+      <c r="C340" t="s">
+        <v>34</v>
+      </c>
+      <c r="D340" t="s">
+        <v>35</v>
+      </c>
+      <c r="E340" t="s">
+        <v>36</v>
+      </c>
+      <c r="F340" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G340" t="s">
+        <v>108</v>
+      </c>
+      <c r="H340" t="s">
+        <v>109</v>
+      </c>
+      <c r="I340" t="s">
+        <v>110</v>
+      </c>
+      <c r="J340">
+        <v>1</v>
+      </c>
+      <c r="K340">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="L340">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="M340" t="s">
+        <v>22</v>
+      </c>
+      <c r="N340" t="s">
+        <v>23</v>
+      </c>
+      <c r="O340" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P340" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q340" t="s">
+        <v>24</v>
+      </c>
+      <c r="R340" t="s">
+        <v>41</v>
+      </c>
+      <c r="S340" t="s">
+        <v>630</v>
+      </c>
+      <c r="T340" t="s">
+        <v>42</v>
+      </c>
+      <c r="U340" t="s">
+        <v>43</v>
+      </c>
+      <c r="V340" t="s">
+        <v>44</v>
+      </c>
+      <c r="W340" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="341" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>819</v>
+      </c>
+      <c r="B341" t="s">
+        <v>820</v>
+      </c>
+      <c r="C341" t="s">
+        <v>34</v>
+      </c>
+      <c r="D341" t="s">
+        <v>35</v>
+      </c>
+      <c r="E341" t="s">
+        <v>36</v>
+      </c>
+      <c r="F341" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G341" t="s">
+        <v>146</v>
+      </c>
+      <c r="H341" t="s">
+        <v>147</v>
+      </c>
+      <c r="I341" t="s">
+        <v>148</v>
+      </c>
+      <c r="J341">
+        <v>1</v>
+      </c>
+      <c r="K341">
+        <v>28.06</v>
+      </c>
+      <c r="L341">
+        <v>28.06</v>
+      </c>
+      <c r="M341" t="s">
+        <v>22</v>
+      </c>
+      <c r="N341" t="s">
+        <v>23</v>
+      </c>
+      <c r="O341" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P341" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q341" t="s">
+        <v>24</v>
+      </c>
+      <c r="R341" t="s">
+        <v>41</v>
+      </c>
+      <c r="S341" t="s">
+        <v>630</v>
+      </c>
+      <c r="T341" t="s">
+        <v>42</v>
+      </c>
+      <c r="U341" t="s">
+        <v>43</v>
+      </c>
+      <c r="V341" t="s">
+        <v>44</v>
+      </c>
+      <c r="W341" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="342" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>819</v>
+      </c>
+      <c r="B342" t="s">
+        <v>820</v>
+      </c>
+      <c r="C342" t="s">
+        <v>34</v>
+      </c>
+      <c r="D342" t="s">
+        <v>35</v>
+      </c>
+      <c r="E342" t="s">
+        <v>36</v>
+      </c>
+      <c r="F342" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G342" t="s">
+        <v>256</v>
+      </c>
+      <c r="H342" t="s">
+        <v>257</v>
+      </c>
+      <c r="I342" t="s">
+        <v>258</v>
+      </c>
+      <c r="J342">
+        <v>5</v>
+      </c>
+      <c r="K342">
+        <v>19.47</v>
+      </c>
+      <c r="L342">
+        <v>97.35</v>
+      </c>
+      <c r="M342" t="s">
+        <v>22</v>
+      </c>
+      <c r="N342" t="s">
+        <v>23</v>
+      </c>
+      <c r="O342" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P342" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q342" t="s">
+        <v>24</v>
+      </c>
+      <c r="R342" t="s">
+        <v>41</v>
+      </c>
+      <c r="S342" t="s">
+        <v>630</v>
+      </c>
+      <c r="T342" t="s">
+        <v>42</v>
+      </c>
+      <c r="U342" t="s">
+        <v>43</v>
+      </c>
+      <c r="V342" t="s">
+        <v>44</v>
+      </c>
+      <c r="W342" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="343" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>819</v>
+      </c>
+      <c r="B343" t="s">
+        <v>820</v>
+      </c>
+      <c r="C343" t="s">
+        <v>34</v>
+      </c>
+      <c r="D343" t="s">
+        <v>35</v>
+      </c>
+      <c r="E343" t="s">
+        <v>36</v>
+      </c>
+      <c r="F343" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G343" t="s">
+        <v>753</v>
+      </c>
+      <c r="H343" t="s">
+        <v>754</v>
+      </c>
+      <c r="I343" t="s">
+        <v>755</v>
+      </c>
+      <c r="J343">
+        <v>2</v>
+      </c>
+      <c r="K343">
+        <v>15.96</v>
+      </c>
+      <c r="L343">
+        <v>31.92</v>
+      </c>
+      <c r="M343" t="s">
+        <v>22</v>
+      </c>
+      <c r="N343" t="s">
+        <v>23</v>
+      </c>
+      <c r="O343" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P343" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q343" t="s">
+        <v>24</v>
+      </c>
+      <c r="R343" t="s">
+        <v>41</v>
+      </c>
+      <c r="S343" t="s">
+        <v>630</v>
+      </c>
+      <c r="T343" t="s">
+        <v>42</v>
+      </c>
+      <c r="U343" t="s">
+        <v>43</v>
+      </c>
+      <c r="V343" t="s">
+        <v>44</v>
+      </c>
+      <c r="W343" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="344" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>819</v>
+      </c>
+      <c r="B344" t="s">
+        <v>820</v>
+      </c>
+      <c r="C344" t="s">
+        <v>34</v>
+      </c>
+      <c r="D344" t="s">
+        <v>35</v>
+      </c>
+      <c r="E344" t="s">
+        <v>36</v>
+      </c>
+      <c r="F344" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G344" t="s">
+        <v>452</v>
+      </c>
+      <c r="H344" t="s">
+        <v>453</v>
+      </c>
+      <c r="I344" t="s">
+        <v>454</v>
+      </c>
+      <c r="J344">
+        <v>5</v>
+      </c>
+      <c r="K344">
+        <v>15.69</v>
+      </c>
+      <c r="L344">
+        <v>78.45</v>
+      </c>
+      <c r="M344" t="s">
+        <v>22</v>
+      </c>
+      <c r="N344" t="s">
+        <v>23</v>
+      </c>
+      <c r="O344" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P344" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q344" t="s">
+        <v>24</v>
+      </c>
+      <c r="R344" t="s">
+        <v>41</v>
+      </c>
+      <c r="S344" t="s">
+        <v>630</v>
+      </c>
+      <c r="T344" t="s">
+        <v>42</v>
+      </c>
+      <c r="U344" t="s">
+        <v>43</v>
+      </c>
+      <c r="V344" t="s">
+        <v>44</v>
+      </c>
+      <c r="W344" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="345" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>819</v>
+      </c>
+      <c r="B345" t="s">
+        <v>820</v>
+      </c>
+      <c r="C345" t="s">
+        <v>34</v>
+      </c>
+      <c r="D345" t="s">
+        <v>35</v>
+      </c>
+      <c r="E345" t="s">
+        <v>36</v>
+      </c>
+      <c r="F345" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G345" t="s">
+        <v>185</v>
+      </c>
+      <c r="H345" t="s">
+        <v>186</v>
+      </c>
+      <c r="I345" t="s">
+        <v>187</v>
+      </c>
+      <c r="J345">
+        <v>5</v>
+      </c>
+      <c r="K345">
+        <v>7.49</v>
+      </c>
+      <c r="L345">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="M345" t="s">
+        <v>22</v>
+      </c>
+      <c r="N345" t="s">
+        <v>23</v>
+      </c>
+      <c r="O345" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P345" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q345" t="s">
+        <v>24</v>
+      </c>
+      <c r="R345" t="s">
+        <v>41</v>
+      </c>
+      <c r="S345" t="s">
+        <v>630</v>
+      </c>
+      <c r="T345" t="s">
+        <v>42</v>
+      </c>
+      <c r="U345" t="s">
+        <v>43</v>
+      </c>
+      <c r="V345" t="s">
+        <v>44</v>
+      </c>
+      <c r="W345" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="346" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>819</v>
+      </c>
+      <c r="B346" t="s">
+        <v>820</v>
+      </c>
+      <c r="C346" t="s">
+        <v>34</v>
+      </c>
+      <c r="D346" t="s">
+        <v>35</v>
+      </c>
+      <c r="E346" t="s">
+        <v>36</v>
+      </c>
+      <c r="F346" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G346" t="s">
+        <v>242</v>
+      </c>
+      <c r="H346" t="s">
+        <v>243</v>
+      </c>
+      <c r="I346" t="s">
+        <v>244</v>
+      </c>
+      <c r="J346">
+        <v>6</v>
+      </c>
+      <c r="K346">
+        <v>16.87</v>
+      </c>
+      <c r="L346">
+        <v>101.22</v>
+      </c>
+      <c r="M346" t="s">
+        <v>22</v>
+      </c>
+      <c r="N346" t="s">
+        <v>23</v>
+      </c>
+      <c r="O346" s="1">
+        <v>46177</v>
+      </c>
+      <c r="P346" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q346" t="s">
+        <v>24</v>
+      </c>
+      <c r="R346" t="s">
+        <v>41</v>
+      </c>
+      <c r="S346" t="s">
+        <v>630</v>
+      </c>
+      <c r="T346" t="s">
+        <v>42</v>
+      </c>
+      <c r="U346" t="s">
+        <v>43</v>
+      </c>
+      <c r="V346" t="s">
+        <v>44</v>
+      </c>
+      <c r="W346" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="347" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>822</v>
+      </c>
+      <c r="B347" t="s">
+        <v>823</v>
+      </c>
+      <c r="C347" t="s">
+        <v>34</v>
+      </c>
+      <c r="D347" t="s">
+        <v>35</v>
+      </c>
+      <c r="E347" t="s">
+        <v>36</v>
+      </c>
+      <c r="F347" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G347" t="s">
+        <v>236</v>
+      </c>
+      <c r="H347" t="s">
+        <v>237</v>
+      </c>
+      <c r="I347" t="s">
+        <v>238</v>
+      </c>
+      <c r="J347">
+        <v>6</v>
+      </c>
+      <c r="K347">
+        <v>12.86</v>
+      </c>
+      <c r="L347">
+        <v>77.16</v>
+      </c>
+      <c r="M347" t="s">
+        <v>22</v>
+      </c>
+      <c r="N347" t="s">
+        <v>23</v>
+      </c>
+      <c r="O347" s="1">
+        <v>46178</v>
+      </c>
+      <c r="P347" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q347" t="s">
+        <v>24</v>
+      </c>
+      <c r="R347" t="s">
+        <v>41</v>
+      </c>
+      <c r="S347" t="s">
+        <v>630</v>
+      </c>
+      <c r="T347" t="s">
+        <v>42</v>
+      </c>
+      <c r="U347" t="s">
+        <v>43</v>
+      </c>
+      <c r="V347" t="s">
+        <v>44</v>
+      </c>
+      <c r="W347" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="348" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>825</v>
+      </c>
+      <c r="B348" t="s">
+        <v>826</v>
+      </c>
+      <c r="C348" t="s">
+        <v>34</v>
+      </c>
+      <c r="D348" t="s">
+        <v>35</v>
+      </c>
+      <c r="E348" t="s">
+        <v>36</v>
+      </c>
+      <c r="F348" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G348" t="s">
+        <v>54</v>
+      </c>
+      <c r="H348" t="s">
+        <v>55</v>
+      </c>
+      <c r="I348" t="s">
+        <v>56</v>
+      </c>
+      <c r="J348">
+        <v>1</v>
+      </c>
+      <c r="K348">
+        <v>12.76</v>
+      </c>
+      <c r="L348">
+        <v>12.76</v>
+      </c>
+      <c r="M348" t="s">
+        <v>22</v>
+      </c>
+      <c r="N348" t="s">
+        <v>23</v>
+      </c>
+      <c r="O348" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P348" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q348" t="s">
+        <v>24</v>
+      </c>
+      <c r="R348" t="s">
+        <v>41</v>
+      </c>
+      <c r="S348" t="s">
+        <v>630</v>
+      </c>
+      <c r="T348" t="s">
+        <v>42</v>
+      </c>
+      <c r="U348" t="s">
+        <v>43</v>
+      </c>
+      <c r="V348" t="s">
+        <v>44</v>
+      </c>
+      <c r="W348" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="349" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>825</v>
+      </c>
+      <c r="B349" t="s">
+        <v>826</v>
+      </c>
+      <c r="C349" t="s">
+        <v>34</v>
+      </c>
+      <c r="D349" t="s">
+        <v>35</v>
+      </c>
+      <c r="E349" t="s">
+        <v>36</v>
+      </c>
+      <c r="F349" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G349" t="s">
+        <v>828</v>
+      </c>
+      <c r="H349" t="s">
+        <v>829</v>
+      </c>
+      <c r="I349" t="s">
+        <v>830</v>
+      </c>
+      <c r="J349">
+        <v>1</v>
+      </c>
+      <c r="K349">
+        <v>10.68</v>
+      </c>
+      <c r="L349">
+        <v>10.68</v>
+      </c>
+      <c r="M349" t="s">
+        <v>22</v>
+      </c>
+      <c r="N349" t="s">
+        <v>23</v>
+      </c>
+      <c r="O349" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P349" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q349" t="s">
+        <v>24</v>
+      </c>
+      <c r="R349" t="s">
+        <v>41</v>
+      </c>
+      <c r="S349" t="s">
+        <v>630</v>
+      </c>
+      <c r="T349" t="s">
+        <v>42</v>
+      </c>
+      <c r="U349" t="s">
+        <v>43</v>
+      </c>
+      <c r="V349" t="s">
+        <v>44</v>
+      </c>
+      <c r="W349" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="350" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>825</v>
+      </c>
+      <c r="B350" t="s">
+        <v>826</v>
+      </c>
+      <c r="C350" t="s">
+        <v>34</v>
+      </c>
+      <c r="D350" t="s">
+        <v>35</v>
+      </c>
+      <c r="E350" t="s">
+        <v>36</v>
+      </c>
+      <c r="F350" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G350" t="s">
+        <v>831</v>
+      </c>
+      <c r="H350" t="s">
+        <v>832</v>
+      </c>
+      <c r="I350" t="s">
+        <v>833</v>
+      </c>
+      <c r="J350">
+        <v>1</v>
+      </c>
+      <c r="K350">
+        <v>7.37</v>
+      </c>
+      <c r="L350">
+        <v>7.37</v>
+      </c>
+      <c r="M350" t="s">
+        <v>22</v>
+      </c>
+      <c r="N350" t="s">
+        <v>23</v>
+      </c>
+      <c r="O350" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P350" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q350" t="s">
+        <v>24</v>
+      </c>
+      <c r="R350" t="s">
+        <v>41</v>
+      </c>
+      <c r="S350" t="s">
+        <v>630</v>
+      </c>
+      <c r="T350" t="s">
+        <v>42</v>
+      </c>
+      <c r="U350" t="s">
+        <v>43</v>
+      </c>
+      <c r="V350" t="s">
+        <v>44</v>
+      </c>
+      <c r="W350" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="351" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>825</v>
+      </c>
+      <c r="B351" t="s">
+        <v>826</v>
+      </c>
+      <c r="C351" t="s">
+        <v>34</v>
+      </c>
+      <c r="D351" t="s">
+        <v>35</v>
+      </c>
+      <c r="E351" t="s">
+        <v>36</v>
+      </c>
+      <c r="F351" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G351" t="s">
+        <v>713</v>
+      </c>
+      <c r="H351" t="s">
+        <v>714</v>
+      </c>
+      <c r="I351" t="s">
+        <v>715</v>
+      </c>
+      <c r="J351">
+        <v>1</v>
+      </c>
+      <c r="K351">
+        <v>17.18</v>
+      </c>
+      <c r="L351">
+        <v>17.18</v>
+      </c>
+      <c r="M351" t="s">
+        <v>22</v>
+      </c>
+      <c r="N351" t="s">
+        <v>23</v>
+      </c>
+      <c r="O351" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P351" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q351" t="s">
+        <v>24</v>
+      </c>
+      <c r="R351" t="s">
+        <v>41</v>
+      </c>
+      <c r="S351" t="s">
+        <v>630</v>
+      </c>
+      <c r="T351" t="s">
+        <v>42</v>
+      </c>
+      <c r="U351" t="s">
+        <v>43</v>
+      </c>
+      <c r="V351" t="s">
+        <v>44</v>
+      </c>
+      <c r="W351" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="352" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>825</v>
+      </c>
+      <c r="B352" t="s">
+        <v>826</v>
+      </c>
+      <c r="C352" t="s">
+        <v>34</v>
+      </c>
+      <c r="D352" t="s">
+        <v>35</v>
+      </c>
+      <c r="E352" t="s">
+        <v>36</v>
+      </c>
+      <c r="F352" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G352" t="s">
+        <v>545</v>
+      </c>
+      <c r="H352" t="s">
+        <v>546</v>
+      </c>
+      <c r="I352" t="s">
+        <v>547</v>
+      </c>
+      <c r="J352">
+        <v>1</v>
+      </c>
+      <c r="K352">
+        <v>9.85</v>
+      </c>
+      <c r="L352">
+        <v>9.85</v>
+      </c>
+      <c r="M352" t="s">
+        <v>22</v>
+      </c>
+      <c r="N352" t="s">
+        <v>23</v>
+      </c>
+      <c r="O352" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P352" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q352" t="s">
+        <v>24</v>
+      </c>
+      <c r="R352" t="s">
+        <v>41</v>
+      </c>
+      <c r="S352" t="s">
+        <v>630</v>
+      </c>
+      <c r="T352" t="s">
+        <v>42</v>
+      </c>
+      <c r="U352" t="s">
+        <v>43</v>
+      </c>
+      <c r="V352" t="s">
+        <v>44</v>
+      </c>
+      <c r="W352" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="353" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>825</v>
+      </c>
+      <c r="B353" t="s">
+        <v>826</v>
+      </c>
+      <c r="C353" t="s">
+        <v>34</v>
+      </c>
+      <c r="D353" t="s">
+        <v>35</v>
+      </c>
+      <c r="E353" t="s">
+        <v>36</v>
+      </c>
+      <c r="F353" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G353" t="s">
+        <v>567</v>
+      </c>
+      <c r="H353" t="s">
+        <v>568</v>
+      </c>
+      <c r="I353" t="s">
+        <v>569</v>
+      </c>
+      <c r="J353">
+        <v>2</v>
+      </c>
+      <c r="K353">
+        <v>6.65</v>
+      </c>
+      <c r="L353">
+        <v>13.3</v>
+      </c>
+      <c r="M353" t="s">
+        <v>22</v>
+      </c>
+      <c r="N353" t="s">
+        <v>23</v>
+      </c>
+      <c r="O353" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P353" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q353" t="s">
+        <v>24</v>
+      </c>
+      <c r="R353" t="s">
+        <v>41</v>
+      </c>
+      <c r="S353" t="s">
+        <v>630</v>
+      </c>
+      <c r="T353" t="s">
+        <v>42</v>
+      </c>
+      <c r="U353" t="s">
+        <v>43</v>
+      </c>
+      <c r="V353" t="s">
+        <v>44</v>
+      </c>
+      <c r="W353" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="354" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>834</v>
+      </c>
+      <c r="B354" t="s">
+        <v>835</v>
+      </c>
+      <c r="C354" t="s">
+        <v>34</v>
+      </c>
+      <c r="D354" t="s">
+        <v>35</v>
+      </c>
+      <c r="E354" t="s">
+        <v>36</v>
+      </c>
+      <c r="F354" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G354" t="s">
+        <v>287</v>
+      </c>
+      <c r="H354" t="s">
+        <v>288</v>
+      </c>
+      <c r="I354" t="s">
+        <v>289</v>
+      </c>
+      <c r="J354">
+        <v>12</v>
+      </c>
+      <c r="K354">
+        <v>11.1</v>
+      </c>
+      <c r="L354">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="M354" t="s">
+        <v>22</v>
+      </c>
+      <c r="N354" t="s">
+        <v>23</v>
+      </c>
+      <c r="O354" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P354" t="s">
+        <v>836</v>
+      </c>
+      <c r="Q354" t="s">
+        <v>24</v>
+      </c>
+      <c r="R354" t="s">
+        <v>41</v>
+      </c>
+      <c r="S354" t="s">
+        <v>630</v>
+      </c>
+      <c r="T354" t="s">
+        <v>42</v>
+      </c>
+      <c r="U354" t="s">
+        <v>43</v>
+      </c>
+      <c r="V354" t="s">
+        <v>44</v>
+      </c>
+      <c r="W354" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="355" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>834</v>
+      </c>
+      <c r="B355" t="s">
+        <v>835</v>
+      </c>
+      <c r="C355" t="s">
+        <v>34</v>
+      </c>
+      <c r="D355" t="s">
+        <v>35</v>
+      </c>
+      <c r="E355" t="s">
+        <v>36</v>
+      </c>
+      <c r="F355" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G355" t="s">
+        <v>26</v>
+      </c>
+      <c r="H355" t="s">
+        <v>27</v>
+      </c>
+      <c r="I355" t="s">
+        <v>28</v>
+      </c>
+      <c r="J355">
+        <v>36</v>
+      </c>
+      <c r="K355">
+        <v>3.23</v>
+      </c>
+      <c r="L355">
+        <v>116.28</v>
+      </c>
+      <c r="M355" t="s">
+        <v>22</v>
+      </c>
+      <c r="N355" t="s">
+        <v>23</v>
+      </c>
+      <c r="O355" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P355" t="s">
+        <v>836</v>
+      </c>
+      <c r="Q355" t="s">
+        <v>24</v>
+      </c>
+      <c r="R355" t="s">
+        <v>41</v>
+      </c>
+      <c r="S355" t="s">
+        <v>630</v>
+      </c>
+      <c r="T355" t="s">
+        <v>42</v>
+      </c>
+      <c r="U355" t="s">
+        <v>43</v>
+      </c>
+      <c r="V355" t="s">
+        <v>44</v>
+      </c>
+      <c r="W355" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="356" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>834</v>
+      </c>
+      <c r="B356" t="s">
+        <v>835</v>
+      </c>
+      <c r="C356" t="s">
+        <v>34</v>
+      </c>
+      <c r="D356" t="s">
+        <v>35</v>
+      </c>
+      <c r="E356" t="s">
+        <v>36</v>
+      </c>
+      <c r="F356" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G356" t="s">
+        <v>242</v>
+      </c>
+      <c r="H356" t="s">
+        <v>243</v>
+      </c>
+      <c r="I356" t="s">
+        <v>244</v>
+      </c>
+      <c r="J356">
+        <v>24</v>
+      </c>
+      <c r="K356">
+        <v>16.87</v>
+      </c>
+      <c r="L356">
+        <v>404.88</v>
+      </c>
+      <c r="M356" t="s">
+        <v>22</v>
+      </c>
+      <c r="N356" t="s">
+        <v>23</v>
+      </c>
+      <c r="O356" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P356" t="s">
+        <v>836</v>
+      </c>
+      <c r="Q356" t="s">
+        <v>24</v>
+      </c>
+      <c r="R356" t="s">
+        <v>41</v>
+      </c>
+      <c r="S356" t="s">
+        <v>630</v>
+      </c>
+      <c r="T356" t="s">
+        <v>42</v>
+      </c>
+      <c r="U356" t="s">
+        <v>43</v>
+      </c>
+      <c r="V356" t="s">
+        <v>44</v>
+      </c>
+      <c r="W356" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="357" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>834</v>
+      </c>
+      <c r="B357" t="s">
+        <v>835</v>
+      </c>
+      <c r="C357" t="s">
+        <v>34</v>
+      </c>
+      <c r="D357" t="s">
+        <v>35</v>
+      </c>
+      <c r="E357" t="s">
+        <v>36</v>
+      </c>
+      <c r="F357" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G357" t="s">
+        <v>455</v>
+      </c>
+      <c r="H357" t="s">
+        <v>456</v>
+      </c>
+      <c r="I357" t="s">
+        <v>457</v>
+      </c>
+      <c r="J357">
+        <v>12</v>
+      </c>
+      <c r="K357">
+        <v>8.42</v>
+      </c>
+      <c r="L357">
+        <v>101.04</v>
+      </c>
+      <c r="M357" t="s">
+        <v>22</v>
+      </c>
+      <c r="N357" t="s">
+        <v>23</v>
+      </c>
+      <c r="O357" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P357" t="s">
+        <v>836</v>
+      </c>
+      <c r="Q357" t="s">
+        <v>24</v>
+      </c>
+      <c r="R357" t="s">
+        <v>41</v>
+      </c>
+      <c r="S357" t="s">
+        <v>630</v>
+      </c>
+      <c r="T357" t="s">
+        <v>42</v>
+      </c>
+      <c r="U357" t="s">
+        <v>43</v>
+      </c>
+      <c r="V357" t="s">
+        <v>44</v>
+      </c>
+      <c r="W357" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="358" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>837</v>
+      </c>
+      <c r="B358" t="s">
+        <v>838</v>
+      </c>
+      <c r="C358" t="s">
+        <v>34</v>
+      </c>
+      <c r="D358" t="s">
+        <v>35</v>
+      </c>
+      <c r="E358" t="s">
+        <v>36</v>
+      </c>
+      <c r="F358" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G358" t="s">
+        <v>287</v>
+      </c>
+      <c r="H358" t="s">
+        <v>288</v>
+      </c>
+      <c r="I358" t="s">
+        <v>289</v>
+      </c>
+      <c r="J358">
+        <v>12</v>
+      </c>
+      <c r="K358">
+        <v>11.1</v>
+      </c>
+      <c r="L358">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="M358" t="s">
+        <v>22</v>
+      </c>
+      <c r="N358" t="s">
+        <v>23</v>
+      </c>
+      <c r="O358" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P358" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q358" t="s">
+        <v>24</v>
+      </c>
+      <c r="R358" t="s">
+        <v>41</v>
+      </c>
+      <c r="S358" t="s">
+        <v>630</v>
+      </c>
+      <c r="T358" t="s">
+        <v>42</v>
+      </c>
+      <c r="U358" t="s">
+        <v>43</v>
+      </c>
+      <c r="V358" t="s">
+        <v>44</v>
+      </c>
+      <c r="W358" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="359" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>837</v>
+      </c>
+      <c r="B359" t="s">
+        <v>838</v>
+      </c>
+      <c r="C359" t="s">
+        <v>34</v>
+      </c>
+      <c r="D359" t="s">
+        <v>35</v>
+      </c>
+      <c r="E359" t="s">
+        <v>36</v>
+      </c>
+      <c r="F359" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G359" t="s">
+        <v>386</v>
+      </c>
+      <c r="H359" t="s">
+        <v>387</v>
+      </c>
+      <c r="I359" t="s">
+        <v>388</v>
+      </c>
+      <c r="J359">
+        <v>24</v>
+      </c>
+      <c r="K359">
+        <v>11.41</v>
+      </c>
+      <c r="L359">
+        <v>273.83999999999997</v>
+      </c>
+      <c r="M359" t="s">
+        <v>22</v>
+      </c>
+      <c r="N359" t="s">
+        <v>23</v>
+      </c>
+      <c r="O359" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P359" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q359" t="s">
+        <v>24</v>
+      </c>
+      <c r="R359" t="s">
+        <v>41</v>
+      </c>
+      <c r="S359" t="s">
+        <v>630</v>
+      </c>
+      <c r="T359" t="s">
+        <v>42</v>
+      </c>
+      <c r="U359" t="s">
+        <v>43</v>
+      </c>
+      <c r="V359" t="s">
+        <v>44</v>
+      </c>
+      <c r="W359" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="360" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>837</v>
+      </c>
+      <c r="B360" t="s">
+        <v>838</v>
+      </c>
+      <c r="C360" t="s">
+        <v>34</v>
+      </c>
+      <c r="D360" t="s">
+        <v>35</v>
+      </c>
+      <c r="E360" t="s">
+        <v>36</v>
+      </c>
+      <c r="F360" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G360" t="s">
+        <v>582</v>
+      </c>
+      <c r="H360" t="s">
+        <v>583</v>
+      </c>
+      <c r="I360" t="s">
+        <v>584</v>
+      </c>
+      <c r="J360">
+        <v>3</v>
+      </c>
+      <c r="K360">
+        <v>12.2</v>
+      </c>
+      <c r="L360">
+        <v>36.6</v>
+      </c>
+      <c r="M360" t="s">
+        <v>22</v>
+      </c>
+      <c r="N360" t="s">
+        <v>23</v>
+      </c>
+      <c r="O360" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P360" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q360" t="s">
+        <v>24</v>
+      </c>
+      <c r="R360" t="s">
+        <v>41</v>
+      </c>
+      <c r="S360" t="s">
+        <v>630</v>
+      </c>
+      <c r="T360" t="s">
+        <v>42</v>
+      </c>
+      <c r="U360" t="s">
+        <v>43</v>
+      </c>
+      <c r="V360" t="s">
+        <v>44</v>
+      </c>
+      <c r="W360" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="361" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>837</v>
+      </c>
+      <c r="B361" t="s">
+        <v>838</v>
+      </c>
+      <c r="C361" t="s">
+        <v>34</v>
+      </c>
+      <c r="D361" t="s">
+        <v>35</v>
+      </c>
+      <c r="E361" t="s">
+        <v>36</v>
+      </c>
+      <c r="F361" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G361" t="s">
+        <v>840</v>
+      </c>
+      <c r="H361" t="s">
+        <v>841</v>
+      </c>
+      <c r="I361" t="s">
+        <v>842</v>
+      </c>
+      <c r="J361">
+        <v>2</v>
+      </c>
+      <c r="K361">
+        <v>16.190000000000001</v>
+      </c>
+      <c r="L361">
+        <v>32.380000000000003</v>
+      </c>
+      <c r="M361" t="s">
+        <v>22</v>
+      </c>
+      <c r="N361" t="s">
+        <v>23</v>
+      </c>
+      <c r="O361" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P361" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q361" t="s">
+        <v>24</v>
+      </c>
+      <c r="R361" t="s">
+        <v>41</v>
+      </c>
+      <c r="S361" t="s">
+        <v>630</v>
+      </c>
+      <c r="T361" t="s">
+        <v>42</v>
+      </c>
+      <c r="U361" t="s">
+        <v>43</v>
+      </c>
+      <c r="V361" t="s">
+        <v>44</v>
+      </c>
+      <c r="W361" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="362" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>837</v>
+      </c>
+      <c r="B362" t="s">
+        <v>838</v>
+      </c>
+      <c r="C362" t="s">
+        <v>34</v>
+      </c>
+      <c r="D362" t="s">
+        <v>35</v>
+      </c>
+      <c r="E362" t="s">
+        <v>36</v>
+      </c>
+      <c r="F362" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G362" t="s">
+        <v>26</v>
+      </c>
+      <c r="H362" t="s">
+        <v>27</v>
+      </c>
+      <c r="I362" t="s">
+        <v>28</v>
+      </c>
+      <c r="J362">
+        <v>12</v>
+      </c>
+      <c r="K362">
+        <v>3.23</v>
+      </c>
+      <c r="L362">
+        <v>38.76</v>
+      </c>
+      <c r="M362" t="s">
+        <v>22</v>
+      </c>
+      <c r="N362" t="s">
+        <v>23</v>
+      </c>
+      <c r="O362" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P362" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q362" t="s">
+        <v>24</v>
+      </c>
+      <c r="R362" t="s">
+        <v>41</v>
+      </c>
+      <c r="S362" t="s">
+        <v>630</v>
+      </c>
+      <c r="T362" t="s">
+        <v>42</v>
+      </c>
+      <c r="U362" t="s">
+        <v>43</v>
+      </c>
+      <c r="V362" t="s">
+        <v>44</v>
+      </c>
+      <c r="W362" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="363" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>837</v>
+      </c>
+      <c r="B363" t="s">
+        <v>838</v>
+      </c>
+      <c r="C363" t="s">
+        <v>34</v>
+      </c>
+      <c r="D363" t="s">
+        <v>35</v>
+      </c>
+      <c r="E363" t="s">
+        <v>36</v>
+      </c>
+      <c r="F363" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G363" t="s">
+        <v>651</v>
+      </c>
+      <c r="H363" t="s">
+        <v>652</v>
+      </c>
+      <c r="I363" t="s">
+        <v>653</v>
+      </c>
+      <c r="J363">
+        <v>2</v>
+      </c>
+      <c r="K363">
+        <v>11.99</v>
+      </c>
+      <c r="L363">
+        <v>23.98</v>
+      </c>
+      <c r="M363" t="s">
+        <v>22</v>
+      </c>
+      <c r="N363" t="s">
+        <v>23</v>
+      </c>
+      <c r="O363" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P363" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q363" t="s">
+        <v>24</v>
+      </c>
+      <c r="R363" t="s">
+        <v>41</v>
+      </c>
+      <c r="S363" t="s">
+        <v>630</v>
+      </c>
+      <c r="T363" t="s">
+        <v>42</v>
+      </c>
+      <c r="U363" t="s">
+        <v>43</v>
+      </c>
+      <c r="V363" t="s">
+        <v>44</v>
+      </c>
+      <c r="W363" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="364" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>837</v>
+      </c>
+      <c r="B364" t="s">
+        <v>838</v>
+      </c>
+      <c r="C364" t="s">
+        <v>34</v>
+      </c>
+      <c r="D364" t="s">
+        <v>35</v>
+      </c>
+      <c r="E364" t="s">
+        <v>36</v>
+      </c>
+      <c r="F364" s="1">
+        <v>46181</v>
+      </c>
+      <c r="G364" t="s">
+        <v>843</v>
+      </c>
+      <c r="H364" t="s">
+        <v>844</v>
+      </c>
+      <c r="I364" t="s">
+        <v>845</v>
+      </c>
+      <c r="J364">
+        <v>1</v>
+      </c>
+      <c r="K364">
+        <v>114.77</v>
+      </c>
+      <c r="L364">
+        <v>114.77</v>
+      </c>
+      <c r="M364" t="s">
+        <v>22</v>
+      </c>
+      <c r="N364" t="s">
+        <v>23</v>
+      </c>
+      <c r="O364" s="1">
+        <v>46181</v>
+      </c>
+      <c r="P364" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q364" t="s">
+        <v>24</v>
+      </c>
+      <c r="R364" t="s">
+        <v>41</v>
+      </c>
+      <c r="S364" t="s">
+        <v>630</v>
+      </c>
+      <c r="T364" t="s">
+        <v>42</v>
+      </c>
+      <c r="U364" t="s">
+        <v>43</v>
+      </c>
+      <c r="V364" t="s">
+        <v>44</v>
+      </c>
+      <c r="W364" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="365" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>846</v>
+      </c>
+      <c r="B365" t="s">
+        <v>847</v>
+      </c>
+      <c r="C365" t="s">
+        <v>34</v>
+      </c>
+      <c r="D365" t="s">
+        <v>35</v>
+      </c>
+      <c r="E365" t="s">
+        <v>36</v>
+      </c>
+      <c r="F365" s="1">
+        <v>46183</v>
+      </c>
+      <c r="G365" t="s">
+        <v>287</v>
+      </c>
+      <c r="H365" t="s">
+        <v>288</v>
+      </c>
+      <c r="I365" t="s">
+        <v>289</v>
+      </c>
+      <c r="J365">
+        <v>12</v>
+      </c>
+      <c r="K365">
+        <v>11.1</v>
+      </c>
+      <c r="L365">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="M365" t="s">
+        <v>22</v>
+      </c>
+      <c r="N365" t="s">
+        <v>23</v>
+      </c>
+      <c r="O365" s="1">
+        <v>46183</v>
+      </c>
+      <c r="P365" t="s">
+        <v>848</v>
+      </c>
+      <c r="Q365" t="s">
+        <v>24</v>
+      </c>
+      <c r="R365" t="s">
+        <v>41</v>
+      </c>
+      <c r="S365" t="s">
+        <v>630</v>
+      </c>
+      <c r="T365" t="s">
+        <v>42</v>
+      </c>
+      <c r="U365" t="s">
+        <v>43</v>
+      </c>
+      <c r="V365" t="s">
+        <v>44</v>
+      </c>
+      <c r="W365" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="366" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>849</v>
+      </c>
+      <c r="B366" t="s">
+        <v>850</v>
+      </c>
+      <c r="C366" t="s">
+        <v>34</v>
+      </c>
+      <c r="D366" t="s">
+        <v>35</v>
+      </c>
+      <c r="E366" t="s">
+        <v>36</v>
+      </c>
+      <c r="F366" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G366" t="s">
+        <v>96</v>
+      </c>
+      <c r="H366" t="s">
+        <v>97</v>
+      </c>
+      <c r="I366" t="s">
+        <v>98</v>
+      </c>
+      <c r="J366">
+        <v>1</v>
+      </c>
+      <c r="K366">
+        <v>11.64</v>
+      </c>
+      <c r="L366">
+        <v>11.64</v>
+      </c>
+      <c r="M366" t="s">
+        <v>22</v>
+      </c>
+      <c r="N366" t="s">
+        <v>23</v>
+      </c>
+      <c r="O366" s="1">
+        <v>46184</v>
+      </c>
+      <c r="P366" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q366" t="s">
+        <v>24</v>
+      </c>
+      <c r="R366" t="s">
+        <v>41</v>
+      </c>
+      <c r="S366" t="s">
+        <v>630</v>
+      </c>
+      <c r="T366" t="s">
+        <v>42</v>
+      </c>
+      <c r="U366" t="s">
+        <v>43</v>
+      </c>
+      <c r="V366" t="s">
+        <v>44</v>
+      </c>
+      <c r="W366" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="367" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>849</v>
+      </c>
+      <c r="B367" t="s">
+        <v>850</v>
+      </c>
+      <c r="C367" t="s">
+        <v>34</v>
+      </c>
+      <c r="D367" t="s">
+        <v>35</v>
+      </c>
+      <c r="E367" t="s">
+        <v>36</v>
+      </c>
+      <c r="F367" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G367" t="s">
+        <v>433</v>
+      </c>
+      <c r="H367" t="s">
+        <v>434</v>
+      </c>
+      <c r="I367" t="s">
+        <v>435</v>
+      </c>
+      <c r="J367">
+        <v>1</v>
+      </c>
+      <c r="K367">
+        <v>14.56</v>
+      </c>
+      <c r="L367">
+        <v>14.56</v>
+      </c>
+      <c r="M367" t="s">
+        <v>22</v>
+      </c>
+      <c r="N367" t="s">
+        <v>23</v>
+      </c>
+      <c r="O367" s="1">
+        <v>46184</v>
+      </c>
+      <c r="P367" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q367" t="s">
+        <v>24</v>
+      </c>
+      <c r="R367" t="s">
+        <v>41</v>
+      </c>
+      <c r="S367" t="s">
+        <v>630</v>
+      </c>
+      <c r="T367" t="s">
+        <v>42</v>
+      </c>
+      <c r="U367" t="s">
+        <v>43</v>
+      </c>
+      <c r="V367" t="s">
+        <v>44</v>
+      </c>
+      <c r="W367" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="368" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>849</v>
+      </c>
+      <c r="B368" t="s">
+        <v>850</v>
+      </c>
+      <c r="C368" t="s">
+        <v>34</v>
+      </c>
+      <c r="D368" t="s">
+        <v>35</v>
+      </c>
+      <c r="E368" t="s">
+        <v>36</v>
+      </c>
+      <c r="F368" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G368" t="s">
+        <v>105</v>
+      </c>
+      <c r="H368" t="s">
+        <v>106</v>
+      </c>
+      <c r="I368" t="s">
+        <v>107</v>
+      </c>
+      <c r="J368">
+        <v>1</v>
+      </c>
+      <c r="K368">
+        <v>14.04</v>
+      </c>
+      <c r="L368">
+        <v>14.04</v>
+      </c>
+      <c r="M368" t="s">
+        <v>22</v>
+      </c>
+      <c r="N368" t="s">
+        <v>23</v>
+      </c>
+      <c r="O368" s="1">
+        <v>46184</v>
+      </c>
+      <c r="P368" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q368" t="s">
+        <v>24</v>
+      </c>
+      <c r="R368" t="s">
+        <v>41</v>
+      </c>
+      <c r="S368" t="s">
+        <v>630</v>
+      </c>
+      <c r="T368" t="s">
+        <v>42</v>
+      </c>
+      <c r="U368" t="s">
+        <v>43</v>
+      </c>
+      <c r="V368" t="s">
+        <v>44</v>
+      </c>
+      <c r="W368" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="369" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>849</v>
+      </c>
+      <c r="B369" t="s">
+        <v>850</v>
+      </c>
+      <c r="C369" t="s">
+        <v>34</v>
+      </c>
+      <c r="D369" t="s">
+        <v>35</v>
+      </c>
+      <c r="E369" t="s">
+        <v>36</v>
+      </c>
+      <c r="F369" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G369" t="s">
+        <v>185</v>
+      </c>
+      <c r="H369" t="s">
+        <v>186</v>
+      </c>
+      <c r="I369" t="s">
+        <v>187</v>
+      </c>
+      <c r="J369">
+        <v>1</v>
+      </c>
+      <c r="K369">
+        <v>7.49</v>
+      </c>
+      <c r="L369">
+        <v>7.49</v>
+      </c>
+      <c r="M369" t="s">
+        <v>22</v>
+      </c>
+      <c r="N369" t="s">
+        <v>23</v>
+      </c>
+      <c r="O369" s="1">
+        <v>46184</v>
+      </c>
+      <c r="P369" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q369" t="s">
+        <v>24</v>
+      </c>
+      <c r="R369" t="s">
+        <v>41</v>
+      </c>
+      <c r="S369" t="s">
+        <v>630</v>
+      </c>
+      <c r="T369" t="s">
+        <v>42</v>
+      </c>
+      <c r="U369" t="s">
+        <v>43</v>
+      </c>
+      <c r="V369" t="s">
+        <v>44</v>
+      </c>
+      <c r="W369" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="370" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>849</v>
+      </c>
+      <c r="B370" t="s">
+        <v>850</v>
+      </c>
+      <c r="C370" t="s">
+        <v>34</v>
+      </c>
+      <c r="D370" t="s">
+        <v>35</v>
+      </c>
+      <c r="E370" t="s">
+        <v>36</v>
+      </c>
+      <c r="F370" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G370" t="s">
+        <v>852</v>
+      </c>
+      <c r="H370" t="s">
+        <v>853</v>
+      </c>
+      <c r="I370" t="s">
+        <v>854</v>
+      </c>
+      <c r="J370">
+        <v>1</v>
+      </c>
+      <c r="K370">
+        <v>12.42</v>
+      </c>
+      <c r="L370">
+        <v>12.42</v>
+      </c>
+      <c r="M370" t="s">
+        <v>22</v>
+      </c>
+      <c r="N370" t="s">
+        <v>23</v>
+      </c>
+      <c r="O370" s="1">
+        <v>46184</v>
+      </c>
+      <c r="P370" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q370" t="s">
+        <v>24</v>
+      </c>
+      <c r="R370" t="s">
+        <v>41</v>
+      </c>
+      <c r="S370" t="s">
+        <v>630</v>
+      </c>
+      <c r="T370" t="s">
+        <v>42</v>
+      </c>
+      <c r="U370" t="s">
+        <v>43</v>
+      </c>
+      <c r="V370" t="s">
+        <v>44</v>
+      </c>
+      <c r="W370" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="371" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>855</v>
+      </c>
+      <c r="B371" t="s">
+        <v>856</v>
+      </c>
+      <c r="C371" t="s">
+        <v>34</v>
+      </c>
+      <c r="D371" t="s">
+        <v>35</v>
+      </c>
+      <c r="E371" t="s">
+        <v>36</v>
+      </c>
+      <c r="F371" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G371" t="s">
+        <v>265</v>
+      </c>
+      <c r="H371" t="s">
+        <v>266</v>
+      </c>
+      <c r="I371" t="s">
+        <v>267</v>
+      </c>
+      <c r="J371">
+        <v>2</v>
+      </c>
+      <c r="K371">
+        <v>83.79</v>
+      </c>
+      <c r="L371">
+        <v>167.58</v>
+      </c>
+      <c r="M371" t="s">
+        <v>22</v>
+      </c>
+      <c r="N371" t="s">
+        <v>23</v>
+      </c>
+      <c r="O371" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P371" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q371" t="s">
+        <v>24</v>
+      </c>
+      <c r="R371" t="s">
+        <v>41</v>
+      </c>
+      <c r="S371" t="s">
+        <v>630</v>
+      </c>
+      <c r="T371" t="s">
+        <v>42</v>
+      </c>
+      <c r="U371" t="s">
+        <v>43</v>
+      </c>
+      <c r="V371" t="s">
+        <v>44</v>
+      </c>
+      <c r="W371" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="372" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>857</v>
+      </c>
+      <c r="B372" t="s">
+        <v>858</v>
+      </c>
+      <c r="C372" t="s">
+        <v>34</v>
+      </c>
+      <c r="D372" t="s">
+        <v>35</v>
+      </c>
+      <c r="E372" t="s">
+        <v>36</v>
+      </c>
+      <c r="F372" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G372" t="s">
+        <v>199</v>
+      </c>
+      <c r="H372" t="s">
+        <v>200</v>
+      </c>
+      <c r="I372" t="s">
+        <v>201</v>
+      </c>
+      <c r="J372">
+        <v>1</v>
+      </c>
+      <c r="K372">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="L372">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="M372" t="s">
+        <v>22</v>
+      </c>
+      <c r="N372" t="s">
+        <v>23</v>
+      </c>
+      <c r="O372" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P372" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q372" t="s">
+        <v>24</v>
+      </c>
+      <c r="R372" t="s">
+        <v>41</v>
+      </c>
+      <c r="S372" t="s">
+        <v>630</v>
+      </c>
+      <c r="T372" t="s">
+        <v>42</v>
+      </c>
+      <c r="U372" t="s">
+        <v>43</v>
+      </c>
+      <c r="V372" t="s">
+        <v>44</v>
+      </c>
+      <c r="W372" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="373" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>857</v>
+      </c>
+      <c r="B373" t="s">
+        <v>858</v>
+      </c>
+      <c r="C373" t="s">
+        <v>34</v>
+      </c>
+      <c r="D373" t="s">
+        <v>35</v>
+      </c>
+      <c r="E373" t="s">
+        <v>36</v>
+      </c>
+      <c r="F373" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G373" t="s">
+        <v>202</v>
+      </c>
+      <c r="H373" t="s">
+        <v>203</v>
+      </c>
+      <c r="I373" t="s">
+        <v>204</v>
+      </c>
+      <c r="J373">
+        <v>1</v>
+      </c>
+      <c r="K373">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="L373">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="M373" t="s">
+        <v>22</v>
+      </c>
+      <c r="N373" t="s">
+        <v>23</v>
+      </c>
+      <c r="O373" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P373" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q373" t="s">
+        <v>24</v>
+      </c>
+      <c r="R373" t="s">
+        <v>41</v>
+      </c>
+      <c r="S373" t="s">
+        <v>630</v>
+      </c>
+      <c r="T373" t="s">
+        <v>42</v>
+      </c>
+      <c r="U373" t="s">
+        <v>43</v>
+      </c>
+      <c r="V373" t="s">
+        <v>44</v>
+      </c>
+      <c r="W373" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="374" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>857</v>
+      </c>
+      <c r="B374" t="s">
+        <v>858</v>
+      </c>
+      <c r="C374" t="s">
+        <v>34</v>
+      </c>
+      <c r="D374" t="s">
+        <v>35</v>
+      </c>
+      <c r="E374" t="s">
+        <v>36</v>
+      </c>
+      <c r="F374" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G374" t="s">
+        <v>206</v>
+      </c>
+      <c r="H374" t="s">
+        <v>207</v>
+      </c>
+      <c r="I374" t="s">
+        <v>208</v>
+      </c>
+      <c r="J374">
+        <v>1</v>
+      </c>
+      <c r="K374">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="L374">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="M374" t="s">
+        <v>22</v>
+      </c>
+      <c r="N374" t="s">
+        <v>23</v>
+      </c>
+      <c r="O374" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P374" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q374" t="s">
+        <v>24</v>
+      </c>
+      <c r="R374" t="s">
+        <v>41</v>
+      </c>
+      <c r="S374" t="s">
+        <v>630</v>
+      </c>
+      <c r="T374" t="s">
+        <v>42</v>
+      </c>
+      <c r="U374" t="s">
+        <v>43</v>
+      </c>
+      <c r="V374" t="s">
+        <v>44</v>
+      </c>
+      <c r="W374" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="375" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>860</v>
+      </c>
+      <c r="B375" t="s">
+        <v>861</v>
+      </c>
+      <c r="C375" t="s">
+        <v>34</v>
+      </c>
+      <c r="D375" t="s">
+        <v>35</v>
+      </c>
+      <c r="E375" t="s">
+        <v>36</v>
+      </c>
+      <c r="F375" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G375" t="s">
+        <v>666</v>
+      </c>
+      <c r="H375" t="s">
+        <v>667</v>
+      </c>
+      <c r="I375" t="s">
+        <v>668</v>
+      </c>
+      <c r="J375">
+        <v>1</v>
+      </c>
+      <c r="K375">
+        <v>22.48</v>
+      </c>
+      <c r="L375">
+        <v>22.48</v>
+      </c>
+      <c r="M375" t="s">
+        <v>22</v>
+      </c>
+      <c r="N375" t="s">
+        <v>23</v>
+      </c>
+      <c r="O375" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P375" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q375" t="s">
+        <v>24</v>
+      </c>
+      <c r="R375" t="s">
+        <v>41</v>
+      </c>
+      <c r="S375" t="s">
+        <v>630</v>
+      </c>
+      <c r="T375" t="s">
+        <v>42</v>
+      </c>
+      <c r="U375" t="s">
+        <v>43</v>
+      </c>
+      <c r="V375" t="s">
+        <v>44</v>
+      </c>
+      <c r="W375" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="376" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>860</v>
+      </c>
+      <c r="B376" t="s">
+        <v>861</v>
+      </c>
+      <c r="C376" t="s">
+        <v>34</v>
+      </c>
+      <c r="D376" t="s">
+        <v>35</v>
+      </c>
+      <c r="E376" t="s">
+        <v>36</v>
+      </c>
+      <c r="F376" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G376" t="s">
+        <v>329</v>
+      </c>
+      <c r="H376" t="s">
+        <v>330</v>
+      </c>
+      <c r="I376" t="s">
+        <v>331</v>
+      </c>
+      <c r="J376">
+        <v>2</v>
+      </c>
+      <c r="K376">
+        <v>11.49</v>
+      </c>
+      <c r="L376">
+        <v>22.98</v>
+      </c>
+      <c r="M376" t="s">
+        <v>22</v>
+      </c>
+      <c r="N376" t="s">
+        <v>23</v>
+      </c>
+      <c r="O376" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P376" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q376" t="s">
+        <v>24</v>
+      </c>
+      <c r="R376" t="s">
+        <v>41</v>
+      </c>
+      <c r="S376" t="s">
+        <v>630</v>
+      </c>
+      <c r="T376" t="s">
+        <v>42</v>
+      </c>
+      <c r="U376" t="s">
+        <v>43</v>
+      </c>
+      <c r="V376" t="s">
+        <v>44</v>
+      </c>
+      <c r="W376" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="377" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>860</v>
+      </c>
+      <c r="B377" t="s">
+        <v>861</v>
+      </c>
+      <c r="C377" t="s">
+        <v>34</v>
+      </c>
+      <c r="D377" t="s">
+        <v>35</v>
+      </c>
+      <c r="E377" t="s">
+        <v>36</v>
+      </c>
+      <c r="F377" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G377" t="s">
+        <v>468</v>
+      </c>
+      <c r="H377" t="s">
+        <v>469</v>
+      </c>
+      <c r="I377" t="s">
+        <v>470</v>
+      </c>
+      <c r="J377">
+        <v>1</v>
+      </c>
+      <c r="K377">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="L377">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="M377" t="s">
+        <v>22</v>
+      </c>
+      <c r="N377" t="s">
+        <v>23</v>
+      </c>
+      <c r="O377" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P377" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q377" t="s">
+        <v>24</v>
+      </c>
+      <c r="R377" t="s">
+        <v>41</v>
+      </c>
+      <c r="S377" t="s">
+        <v>630</v>
+      </c>
+      <c r="T377" t="s">
+        <v>42</v>
+      </c>
+      <c r="U377" t="s">
+        <v>43</v>
+      </c>
+      <c r="V377" t="s">
+        <v>44</v>
+      </c>
+      <c r="W377" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="378" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>860</v>
+      </c>
+      <c r="B378" t="s">
+        <v>861</v>
+      </c>
+      <c r="C378" t="s">
+        <v>34</v>
+      </c>
+      <c r="D378" t="s">
+        <v>35</v>
+      </c>
+      <c r="E378" t="s">
+        <v>36</v>
+      </c>
+      <c r="F378" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G378" t="s">
+        <v>862</v>
+      </c>
+      <c r="H378" t="s">
+        <v>863</v>
+      </c>
+      <c r="I378" t="s">
+        <v>864</v>
+      </c>
+      <c r="J378">
+        <v>1</v>
+      </c>
+      <c r="K378">
+        <v>19.32</v>
+      </c>
+      <c r="L378">
+        <v>19.32</v>
+      </c>
+      <c r="M378" t="s">
+        <v>22</v>
+      </c>
+      <c r="N378" t="s">
+        <v>23</v>
+      </c>
+      <c r="O378" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P378" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q378" t="s">
+        <v>24</v>
+      </c>
+      <c r="R378" t="s">
+        <v>41</v>
+      </c>
+      <c r="S378" t="s">
+        <v>630</v>
+      </c>
+      <c r="T378" t="s">
+        <v>42</v>
+      </c>
+      <c r="U378" t="s">
+        <v>43</v>
+      </c>
+      <c r="V378" t="s">
+        <v>44</v>
+      </c>
+      <c r="W378" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="379" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>865</v>
+      </c>
+      <c r="B379" t="s">
+        <v>866</v>
+      </c>
+      <c r="C379" t="s">
+        <v>34</v>
+      </c>
+      <c r="D379" t="s">
+        <v>35</v>
+      </c>
+      <c r="E379" t="s">
+        <v>36</v>
+      </c>
+      <c r="F379" s="1">
+        <v>46195</v>
+      </c>
+      <c r="G379" t="s">
+        <v>265</v>
+      </c>
+      <c r="H379" t="s">
+        <v>266</v>
+      </c>
+      <c r="I379" t="s">
+        <v>267</v>
+      </c>
+      <c r="J379">
+        <v>2</v>
+      </c>
+      <c r="K379">
+        <v>83.79</v>
+      </c>
+      <c r="L379">
+        <v>167.58</v>
+      </c>
+      <c r="M379" t="s">
+        <v>22</v>
+      </c>
+      <c r="N379" t="s">
+        <v>23</v>
+      </c>
+      <c r="O379" s="1">
+        <v>46195</v>
+      </c>
+      <c r="P379" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q379" t="s">
+        <v>24</v>
+      </c>
+      <c r="R379" t="s">
+        <v>41</v>
+      </c>
+      <c r="S379" t="s">
+        <v>630</v>
+      </c>
+      <c r="T379" t="s">
+        <v>42</v>
+      </c>
+      <c r="U379" t="s">
+        <v>43</v>
+      </c>
+      <c r="V379" t="s">
+        <v>44</v>
+      </c>
+      <c r="W379" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="380" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>867</v>
+      </c>
+      <c r="B380" t="s">
+        <v>868</v>
+      </c>
+      <c r="C380" t="s">
+        <v>34</v>
+      </c>
+      <c r="D380" t="s">
+        <v>35</v>
+      </c>
+      <c r="E380" t="s">
+        <v>36</v>
+      </c>
+      <c r="F380" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G380" t="s">
+        <v>773</v>
+      </c>
+      <c r="H380" t="s">
+        <v>774</v>
+      </c>
+      <c r="I380" t="s">
+        <v>775</v>
+      </c>
+      <c r="J380">
+        <v>2</v>
+      </c>
+      <c r="K380">
+        <v>15.8</v>
+      </c>
+      <c r="L380">
+        <v>31.6</v>
+      </c>
+      <c r="M380" t="s">
+        <v>22</v>
+      </c>
+      <c r="N380" t="s">
+        <v>23</v>
+      </c>
+      <c r="O380" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P380" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q380" t="s">
+        <v>24</v>
+      </c>
+      <c r="R380" t="s">
+        <v>41</v>
+      </c>
+      <c r="S380" t="s">
+        <v>630</v>
+      </c>
+      <c r="T380" t="s">
+        <v>42</v>
+      </c>
+      <c r="U380" t="s">
+        <v>43</v>
+      </c>
+      <c r="V380" t="s">
+        <v>44</v>
+      </c>
+      <c r="W380" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="381" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>867</v>
+      </c>
+      <c r="B381" t="s">
+        <v>868</v>
+      </c>
+      <c r="C381" t="s">
+        <v>34</v>
+      </c>
+      <c r="D381" t="s">
+        <v>35</v>
+      </c>
+      <c r="E381" t="s">
+        <v>36</v>
+      </c>
+      <c r="F381" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G381" t="s">
+        <v>242</v>
+      </c>
+      <c r="H381" t="s">
+        <v>243</v>
+      </c>
+      <c r="I381" t="s">
+        <v>244</v>
+      </c>
+      <c r="J381">
+        <v>1</v>
+      </c>
+      <c r="K381">
+        <v>16.87</v>
+      </c>
+      <c r="L381">
+        <v>16.87</v>
+      </c>
+      <c r="M381" t="s">
+        <v>22</v>
+      </c>
+      <c r="N381" t="s">
+        <v>23</v>
+      </c>
+      <c r="O381" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P381" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q381" t="s">
+        <v>24</v>
+      </c>
+      <c r="R381" t="s">
+        <v>41</v>
+      </c>
+      <c r="S381" t="s">
+        <v>630</v>
+      </c>
+      <c r="T381" t="s">
+        <v>42</v>
+      </c>
+      <c r="U381" t="s">
+        <v>43</v>
+      </c>
+      <c r="V381" t="s">
+        <v>44</v>
+      </c>
+      <c r="W381" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="382" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>867</v>
+      </c>
+      <c r="B382" t="s">
+        <v>868</v>
+      </c>
+      <c r="C382" t="s">
+        <v>34</v>
+      </c>
+      <c r="D382" t="s">
+        <v>35</v>
+      </c>
+      <c r="E382" t="s">
+        <v>36</v>
+      </c>
+      <c r="F382" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G382" t="s">
+        <v>291</v>
+      </c>
+      <c r="H382" t="s">
+        <v>292</v>
+      </c>
+      <c r="I382" t="s">
+        <v>293</v>
+      </c>
+      <c r="J382">
+        <v>2</v>
+      </c>
+      <c r="K382">
+        <v>11.9</v>
+      </c>
+      <c r="L382">
+        <v>23.8</v>
+      </c>
+      <c r="M382" t="s">
+        <v>22</v>
+      </c>
+      <c r="N382" t="s">
+        <v>23</v>
+      </c>
+      <c r="O382" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P382" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q382" t="s">
+        <v>24</v>
+      </c>
+      <c r="R382" t="s">
+        <v>41</v>
+      </c>
+      <c r="S382" t="s">
+        <v>630</v>
+      </c>
+      <c r="T382" t="s">
+        <v>42</v>
+      </c>
+      <c r="U382" t="s">
+        <v>43</v>
+      </c>
+      <c r="V382" t="s">
+        <v>44</v>
+      </c>
+      <c r="W382" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="383" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>867</v>
+      </c>
+      <c r="B383" t="s">
+        <v>868</v>
+      </c>
+      <c r="C383" t="s">
+        <v>34</v>
+      </c>
+      <c r="D383" t="s">
+        <v>35</v>
+      </c>
+      <c r="E383" t="s">
+        <v>36</v>
+      </c>
+      <c r="F383" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G383" t="s">
+        <v>870</v>
+      </c>
+      <c r="H383" t="s">
+        <v>871</v>
+      </c>
+      <c r="I383" t="s">
+        <v>872</v>
+      </c>
+      <c r="J383">
+        <v>1</v>
+      </c>
+      <c r="K383">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="L383">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="M383" t="s">
+        <v>22</v>
+      </c>
+      <c r="N383" t="s">
+        <v>23</v>
+      </c>
+      <c r="O383" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P383" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q383" t="s">
+        <v>24</v>
+      </c>
+      <c r="R383" t="s">
+        <v>41</v>
+      </c>
+      <c r="S383" t="s">
+        <v>630</v>
+      </c>
+      <c r="T383" t="s">
+        <v>42</v>
+      </c>
+      <c r="U383" t="s">
+        <v>43</v>
+      </c>
+      <c r="V383" t="s">
+        <v>44</v>
+      </c>
+      <c r="W383" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="384" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>867</v>
+      </c>
+      <c r="B384" t="s">
+        <v>868</v>
+      </c>
+      <c r="C384" t="s">
+        <v>34</v>
+      </c>
+      <c r="D384" t="s">
+        <v>35</v>
+      </c>
+      <c r="E384" t="s">
+        <v>36</v>
+      </c>
+      <c r="F384" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G384" t="s">
+        <v>297</v>
+      </c>
+      <c r="H384" t="s">
+        <v>298</v>
+      </c>
+      <c r="I384" t="s">
+        <v>299</v>
+      </c>
+      <c r="J384">
+        <v>1</v>
+      </c>
+      <c r="K384">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="L384">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="M384" t="s">
+        <v>22</v>
+      </c>
+      <c r="N384" t="s">
+        <v>23</v>
+      </c>
+      <c r="O384" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P384" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q384" t="s">
+        <v>24</v>
+      </c>
+      <c r="R384" t="s">
+        <v>41</v>
+      </c>
+      <c r="S384" t="s">
+        <v>630</v>
+      </c>
+      <c r="T384" t="s">
+        <v>42</v>
+      </c>
+      <c r="U384" t="s">
+        <v>43</v>
+      </c>
+      <c r="V384" t="s">
+        <v>44</v>
+      </c>
+      <c r="W384" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="385" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>867</v>
+      </c>
+      <c r="B385" t="s">
+        <v>868</v>
+      </c>
+      <c r="C385" t="s">
+        <v>34</v>
+      </c>
+      <c r="D385" t="s">
+        <v>35</v>
+      </c>
+      <c r="E385" t="s">
+        <v>36</v>
+      </c>
+      <c r="F385" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G385" t="s">
+        <v>361</v>
+      </c>
+      <c r="H385" t="s">
+        <v>362</v>
+      </c>
+      <c r="I385" t="s">
+        <v>363</v>
+      </c>
+      <c r="J385">
+        <v>1</v>
+      </c>
+      <c r="K385">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="L385">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="M385" t="s">
+        <v>22</v>
+      </c>
+      <c r="N385" t="s">
+        <v>23</v>
+      </c>
+      <c r="O385" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P385" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q385" t="s">
+        <v>24</v>
+      </c>
+      <c r="R385" t="s">
+        <v>41</v>
+      </c>
+      <c r="S385" t="s">
+        <v>630</v>
+      </c>
+      <c r="T385" t="s">
+        <v>42</v>
+      </c>
+      <c r="U385" t="s">
+        <v>43</v>
+      </c>
+      <c r="V385" t="s">
+        <v>44</v>
+      </c>
+      <c r="W385" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="386" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>867</v>
+      </c>
+      <c r="B386" t="s">
+        <v>868</v>
+      </c>
+      <c r="C386" t="s">
+        <v>34</v>
+      </c>
+      <c r="D386" t="s">
+        <v>35</v>
+      </c>
+      <c r="E386" t="s">
+        <v>36</v>
+      </c>
+      <c r="F386" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G386" t="s">
+        <v>594</v>
+      </c>
+      <c r="H386" t="s">
+        <v>595</v>
+      </c>
+      <c r="I386" t="s">
+        <v>596</v>
+      </c>
+      <c r="J386">
+        <v>1</v>
+      </c>
+      <c r="K386">
+        <v>4.37</v>
+      </c>
+      <c r="L386">
+        <v>4.37</v>
+      </c>
+      <c r="M386" t="s">
+        <v>22</v>
+      </c>
+      <c r="N386" t="s">
+        <v>23</v>
+      </c>
+      <c r="O386" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P386" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q386" t="s">
+        <v>24</v>
+      </c>
+      <c r="R386" t="s">
+        <v>41</v>
+      </c>
+      <c r="S386" t="s">
+        <v>630</v>
+      </c>
+      <c r="T386" t="s">
+        <v>42</v>
+      </c>
+      <c r="U386" t="s">
+        <v>43</v>
+      </c>
+      <c r="V386" t="s">
+        <v>44</v>
+      </c>
+      <c r="W386" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="387" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>867</v>
+      </c>
+      <c r="B387" t="s">
+        <v>868</v>
+      </c>
+      <c r="C387" t="s">
+        <v>34</v>
+      </c>
+      <c r="D387" t="s">
+        <v>35</v>
+      </c>
+      <c r="E387" t="s">
+        <v>36</v>
+      </c>
+      <c r="F387" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G387" t="s">
+        <v>300</v>
+      </c>
+      <c r="H387" t="s">
+        <v>301</v>
+      </c>
+      <c r="I387" t="s">
+        <v>302</v>
+      </c>
+      <c r="J387">
+        <v>1</v>
+      </c>
+      <c r="K387">
+        <v>13.66</v>
+      </c>
+      <c r="L387">
+        <v>13.66</v>
+      </c>
+      <c r="M387" t="s">
+        <v>22</v>
+      </c>
+      <c r="N387" t="s">
+        <v>23</v>
+      </c>
+      <c r="O387" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P387" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q387" t="s">
+        <v>24</v>
+      </c>
+      <c r="R387" t="s">
+        <v>41</v>
+      </c>
+      <c r="S387" t="s">
+        <v>630</v>
+      </c>
+      <c r="T387" t="s">
+        <v>42</v>
+      </c>
+      <c r="U387" t="s">
+        <v>43</v>
+      </c>
+      <c r="V387" t="s">
+        <v>44</v>
+      </c>
+      <c r="W387" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="388" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>867</v>
+      </c>
+      <c r="B388" t="s">
+        <v>868</v>
+      </c>
+      <c r="C388" t="s">
+        <v>34</v>
+      </c>
+      <c r="D388" t="s">
+        <v>35</v>
+      </c>
+      <c r="E388" t="s">
+        <v>36</v>
+      </c>
+      <c r="F388" s="1">
+        <v>46196</v>
+      </c>
+      <c r="G388" t="s">
+        <v>303</v>
+      </c>
+      <c r="H388" t="s">
+        <v>304</v>
+      </c>
+      <c r="I388" t="s">
+        <v>305</v>
+      </c>
+      <c r="J388">
+        <v>1</v>
+      </c>
+      <c r="K388">
+        <v>13.66</v>
+      </c>
+      <c r="L388">
+        <v>13.66</v>
+      </c>
+      <c r="M388" t="s">
+        <v>22</v>
+      </c>
+      <c r="N388" t="s">
+        <v>23</v>
+      </c>
+      <c r="O388" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P388" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q388" t="s">
+        <v>24</v>
+      </c>
+      <c r="R388" t="s">
+        <v>41</v>
+      </c>
+      <c r="S388" t="s">
+        <v>630</v>
+      </c>
+      <c r="T388" t="s">
+        <v>42</v>
+      </c>
+      <c r="U388" t="s">
+        <v>43</v>
+      </c>
+      <c r="V388" t="s">
+        <v>44</v>
+      </c>
+      <c r="W388" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="389" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>873</v>
+      </c>
+      <c r="B389" t="s">
+        <v>874</v>
+      </c>
+      <c r="C389" t="s">
+        <v>34</v>
+      </c>
+      <c r="D389" t="s">
+        <v>35</v>
+      </c>
+      <c r="E389" t="s">
+        <v>36</v>
+      </c>
+      <c r="F389" s="1">
+        <v>46197</v>
+      </c>
+      <c r="G389" t="s">
+        <v>287</v>
+      </c>
+      <c r="H389" t="s">
+        <v>288</v>
+      </c>
+      <c r="I389" t="s">
+        <v>289</v>
+      </c>
+      <c r="J389">
+        <v>12</v>
+      </c>
+      <c r="K389">
+        <v>11.1</v>
+      </c>
+      <c r="L389">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="M389" t="s">
+        <v>22</v>
+      </c>
+      <c r="N389" t="s">
+        <v>23</v>
+      </c>
+      <c r="O389" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P389" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q389" t="s">
+        <v>24</v>
+      </c>
+      <c r="R389" t="s">
+        <v>41</v>
+      </c>
+      <c r="S389" t="s">
+        <v>630</v>
+      </c>
+      <c r="T389" t="s">
+        <v>42</v>
+      </c>
+      <c r="U389" t="s">
+        <v>43</v>
+      </c>
+      <c r="V389" t="s">
+        <v>44</v>
+      </c>
+      <c r="W389" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="390" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>873</v>
+      </c>
+      <c r="B390" t="s">
+        <v>874</v>
+      </c>
+      <c r="C390" t="s">
+        <v>34</v>
+      </c>
+      <c r="D390" t="s">
+        <v>35</v>
+      </c>
+      <c r="E390" t="s">
+        <v>36</v>
+      </c>
+      <c r="F390" s="1">
+        <v>46197</v>
+      </c>
+      <c r="G390" t="s">
+        <v>60</v>
+      </c>
+      <c r="H390" t="s">
+        <v>61</v>
+      </c>
+      <c r="I390" t="s">
+        <v>62</v>
+      </c>
+      <c r="J390">
+        <v>1</v>
+      </c>
+      <c r="K390">
+        <v>17.57</v>
+      </c>
+      <c r="L390">
+        <v>17.57</v>
+      </c>
+      <c r="M390" t="s">
+        <v>22</v>
+      </c>
+      <c r="N390" t="s">
+        <v>23</v>
+      </c>
+      <c r="O390" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P390" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q390" t="s">
+        <v>24</v>
+      </c>
+      <c r="R390" t="s">
+        <v>41</v>
+      </c>
+      <c r="S390" t="s">
+        <v>630</v>
+      </c>
+      <c r="T390" t="s">
+        <v>42</v>
+      </c>
+      <c r="U390" t="s">
+        <v>43</v>
+      </c>
+      <c r="V390" t="s">
+        <v>44</v>
+      </c>
+      <c r="W390" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="391" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>873</v>
+      </c>
+      <c r="B391" t="s">
+        <v>874</v>
+      </c>
+      <c r="C391" t="s">
+        <v>34</v>
+      </c>
+      <c r="D391" t="s">
+        <v>35</v>
+      </c>
+      <c r="E391" t="s">
+        <v>36</v>
+      </c>
+      <c r="F391" s="1">
+        <v>46197</v>
+      </c>
+      <c r="G391" t="s">
+        <v>300</v>
+      </c>
+      <c r="H391" t="s">
+        <v>301</v>
+      </c>
+      <c r="I391" t="s">
+        <v>302</v>
+      </c>
+      <c r="J391">
+        <v>1</v>
+      </c>
+      <c r="K391">
+        <v>13.66</v>
+      </c>
+      <c r="L391">
+        <v>13.66</v>
+      </c>
+      <c r="M391" t="s">
+        <v>22</v>
+      </c>
+      <c r="N391" t="s">
+        <v>23</v>
+      </c>
+      <c r="O391" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P391" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q391" t="s">
+        <v>24</v>
+      </c>
+      <c r="R391" t="s">
+        <v>41</v>
+      </c>
+      <c r="S391" t="s">
+        <v>630</v>
+      </c>
+      <c r="T391" t="s">
+        <v>42</v>
+      </c>
+      <c r="U391" t="s">
+        <v>43</v>
+      </c>
+      <c r="V391" t="s">
+        <v>44</v>
+      </c>
+      <c r="W391" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="392" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>876</v>
+      </c>
+      <c r="B392" t="s">
+        <v>877</v>
+      </c>
+      <c r="C392" t="s">
+        <v>34</v>
+      </c>
+      <c r="D392" t="s">
+        <v>35</v>
+      </c>
+      <c r="E392" t="s">
+        <v>36</v>
+      </c>
+      <c r="F392" s="1">
+        <v>46197</v>
+      </c>
+      <c r="G392" t="s">
+        <v>303</v>
+      </c>
+      <c r="H392" t="s">
+        <v>304</v>
+      </c>
+      <c r="I392" t="s">
+        <v>305</v>
+      </c>
+      <c r="J392">
+        <v>1</v>
+      </c>
+      <c r="K392">
+        <v>13.66</v>
+      </c>
+      <c r="L392">
+        <v>13.66</v>
+      </c>
+      <c r="M392" t="s">
+        <v>22</v>
+      </c>
+      <c r="N392" t="s">
+        <v>23</v>
+      </c>
+      <c r="O392" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P392" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q392" t="s">
+        <v>24</v>
+      </c>
+      <c r="R392" t="s">
+        <v>41</v>
+      </c>
+      <c r="S392" t="s">
+        <v>630</v>
+      </c>
+      <c r="T392" t="s">
+        <v>42</v>
+      </c>
+      <c r="U392" t="s">
+        <v>43</v>
+      </c>
+      <c r="V392" t="s">
+        <v>44</v>
+      </c>
+      <c r="W392" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="393" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>876</v>
+      </c>
+      <c r="B393" t="s">
+        <v>877</v>
+      </c>
+      <c r="C393" t="s">
+        <v>34</v>
+      </c>
+      <c r="D393" t="s">
+        <v>35</v>
+      </c>
+      <c r="E393" t="s">
+        <v>36</v>
+      </c>
+      <c r="F393" s="1">
+        <v>46197</v>
+      </c>
+      <c r="G393" t="s">
+        <v>878</v>
+      </c>
+      <c r="H393" t="s">
+        <v>879</v>
+      </c>
+      <c r="I393" t="s">
+        <v>880</v>
+      </c>
+      <c r="J393">
+        <v>1</v>
+      </c>
+      <c r="K393">
+        <v>13.39</v>
+      </c>
+      <c r="L393">
+        <v>13.39</v>
+      </c>
+      <c r="M393" t="s">
+        <v>22</v>
+      </c>
+      <c r="N393" t="s">
+        <v>23</v>
+      </c>
+      <c r="O393" s="1">
+        <v>46196</v>
+      </c>
+      <c r="P393" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q393" t="s">
+        <v>24</v>
+      </c>
+      <c r="R393" t="s">
+        <v>41</v>
+      </c>
+      <c r="S393" t="s">
+        <v>630</v>
+      </c>
+      <c r="T393" t="s">
+        <v>42</v>
+      </c>
+      <c r="U393" t="s">
+        <v>43</v>
+      </c>
+      <c r="V393" t="s">
+        <v>44</v>
+      </c>
+      <c r="W393" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="394" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>881</v>
+      </c>
+      <c r="B394" t="s">
+        <v>882</v>
+      </c>
+      <c r="C394" t="s">
+        <v>34</v>
+      </c>
+      <c r="D394" t="s">
+        <v>35</v>
+      </c>
+      <c r="E394" t="s">
+        <v>36</v>
+      </c>
+      <c r="F394" s="1">
+        <v>46198</v>
+      </c>
+      <c r="G394" t="s">
+        <v>883</v>
+      </c>
+      <c r="H394" t="s">
+        <v>884</v>
+      </c>
+      <c r="I394" t="s">
+        <v>885</v>
+      </c>
+      <c r="J394">
+        <v>6</v>
+      </c>
+      <c r="K394">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="L394">
+        <v>96.36</v>
+      </c>
+      <c r="M394" t="s">
+        <v>22</v>
+      </c>
+      <c r="N394" t="s">
+        <v>23</v>
+      </c>
+      <c r="O394" s="1">
+        <v>46198</v>
+      </c>
+      <c r="P394" t="s">
+        <v>886</v>
+      </c>
+      <c r="Q394" t="s">
+        <v>24</v>
+      </c>
+      <c r="R394" t="s">
+        <v>41</v>
+      </c>
+      <c r="S394" t="s">
+        <v>630</v>
+      </c>
+      <c r="T394" t="s">
+        <v>42</v>
+      </c>
+      <c r="U394" t="s">
+        <v>43</v>
+      </c>
+      <c r="V394" t="s">
+        <v>44</v>
+      </c>
+      <c r="W394" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="395" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>887</v>
+      </c>
+      <c r="B395" t="s">
+        <v>888</v>
+      </c>
+      <c r="C395" t="s">
+        <v>34</v>
+      </c>
+      <c r="D395" t="s">
+        <v>35</v>
+      </c>
+      <c r="E395" t="s">
+        <v>36</v>
+      </c>
+      <c r="F395" s="1">
+        <v>46199</v>
+      </c>
+      <c r="G395" t="s">
+        <v>642</v>
+      </c>
+      <c r="H395" t="s">
+        <v>643</v>
+      </c>
+      <c r="I395" t="s">
+        <v>644</v>
+      </c>
+      <c r="J395">
+        <v>5</v>
+      </c>
+      <c r="K395">
+        <v>10.63</v>
+      </c>
+      <c r="L395">
+        <v>53.15</v>
+      </c>
+      <c r="M395" t="s">
+        <v>22</v>
+      </c>
+      <c r="N395" t="s">
+        <v>23</v>
+      </c>
+      <c r="O395" s="1">
+        <v>46199</v>
+      </c>
+      <c r="P395" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q395" t="s">
+        <v>24</v>
+      </c>
+      <c r="R395" t="s">
+        <v>41</v>
+      </c>
+      <c r="S395" t="s">
+        <v>630</v>
+      </c>
+      <c r="T395" t="s">
+        <v>42</v>
+      </c>
+      <c r="U395" t="s">
+        <v>43</v>
+      </c>
+      <c r="V395" t="s">
+        <v>44</v>
+      </c>
+      <c r="W395" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="396" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>887</v>
+      </c>
+      <c r="B396" t="s">
+        <v>888</v>
+      </c>
+      <c r="C396" t="s">
+        <v>34</v>
+      </c>
+      <c r="D396" t="s">
+        <v>35</v>
+      </c>
+      <c r="E396" t="s">
+        <v>36</v>
+      </c>
+      <c r="F396" s="1">
+        <v>46199</v>
+      </c>
+      <c r="G396" t="s">
+        <v>852</v>
+      </c>
+      <c r="H396" t="s">
+        <v>853</v>
+      </c>
+      <c r="I396" t="s">
+        <v>854</v>
+      </c>
+      <c r="J396">
+        <v>1</v>
+      </c>
+      <c r="K396">
+        <v>12.42</v>
+      </c>
+      <c r="L396">
+        <v>12.42</v>
+      </c>
+      <c r="M396" t="s">
+        <v>22</v>
+      </c>
+      <c r="N396" t="s">
+        <v>23</v>
+      </c>
+      <c r="O396" s="1">
+        <v>46199</v>
+      </c>
+      <c r="P396" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q396" t="s">
+        <v>24</v>
+      </c>
+      <c r="R396" t="s">
+        <v>41</v>
+      </c>
+      <c r="S396" t="s">
+        <v>630</v>
+      </c>
+      <c r="T396" t="s">
+        <v>42</v>
+      </c>
+      <c r="U396" t="s">
+        <v>43</v>
+      </c>
+      <c r="V396" t="s">
+        <v>44</v>
+      </c>
+      <c r="W396" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="397" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>890</v>
+      </c>
+      <c r="B397" t="s">
+        <v>891</v>
+      </c>
+      <c r="C397" t="s">
+        <v>34</v>
+      </c>
+      <c r="D397" t="s">
+        <v>35</v>
+      </c>
+      <c r="E397" t="s">
+        <v>36</v>
+      </c>
+      <c r="F397" s="1">
+        <v>46199</v>
+      </c>
+      <c r="G397" t="s">
+        <v>150</v>
+      </c>
+      <c r="H397" t="s">
+        <v>151</v>
+      </c>
+      <c r="I397" t="s">
+        <v>152</v>
+      </c>
+      <c r="J397">
+        <v>4</v>
+      </c>
+      <c r="K397">
+        <v>13.23</v>
+      </c>
+      <c r="L397">
+        <v>52.92</v>
+      </c>
+      <c r="M397" t="s">
+        <v>22</v>
+      </c>
+      <c r="N397" t="s">
+        <v>23</v>
+      </c>
+      <c r="O397" s="1">
+        <v>46199</v>
+      </c>
+      <c r="P397" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q397" t="s">
+        <v>24</v>
+      </c>
+      <c r="R397" t="s">
+        <v>41</v>
+      </c>
+      <c r="S397" t="s">
+        <v>630</v>
+      </c>
+      <c r="T397" t="s">
+        <v>42</v>
+      </c>
+      <c r="U397" t="s">
+        <v>43</v>
+      </c>
+      <c r="V397" t="s">
+        <v>44</v>
+      </c>
+      <c r="W397" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="398" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>890</v>
+      </c>
+      <c r="B398" t="s">
+        <v>891</v>
+      </c>
+      <c r="C398" t="s">
+        <v>34</v>
+      </c>
+      <c r="D398" t="s">
+        <v>35</v>
+      </c>
+      <c r="E398" t="s">
+        <v>36</v>
+      </c>
+      <c r="F398" s="1">
+        <v>46199</v>
+      </c>
+      <c r="G398" t="s">
+        <v>221</v>
+      </c>
+      <c r="H398" t="s">
+        <v>222</v>
+      </c>
+      <c r="I398" t="s">
+        <v>223</v>
+      </c>
+      <c r="J398">
+        <v>2</v>
+      </c>
+      <c r="K398">
+        <v>15.13</v>
+      </c>
+      <c r="L398">
+        <v>30.26</v>
+      </c>
+      <c r="M398" t="s">
+        <v>22</v>
+      </c>
+      <c r="N398" t="s">
+        <v>23</v>
+      </c>
+      <c r="O398" s="1">
+        <v>46199</v>
+      </c>
+      <c r="P398" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q398" t="s">
+        <v>24</v>
+      </c>
+      <c r="R398" t="s">
+        <v>41</v>
+      </c>
+      <c r="S398" t="s">
+        <v>630</v>
+      </c>
+      <c r="T398" t="s">
+        <v>42</v>
+      </c>
+      <c r="U398" t="s">
+        <v>43</v>
+      </c>
+      <c r="V398" t="s">
+        <v>44</v>
+      </c>
+      <c r="W398" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="399" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>890</v>
+      </c>
+      <c r="B399" t="s">
+        <v>891</v>
+      </c>
+      <c r="C399" t="s">
+        <v>34</v>
+      </c>
+      <c r="D399" t="s">
+        <v>35</v>
+      </c>
+      <c r="E399" t="s">
+        <v>36</v>
+      </c>
+      <c r="F399" s="1">
+        <v>46199</v>
+      </c>
+      <c r="G399" t="s">
+        <v>460</v>
+      </c>
+      <c r="H399" t="s">
+        <v>461</v>
+      </c>
+      <c r="I399" t="s">
+        <v>462</v>
+      </c>
+      <c r="J399">
+        <v>1</v>
+      </c>
+      <c r="K399">
+        <v>10.63</v>
+      </c>
+      <c r="L399">
+        <v>10.63</v>
+      </c>
+      <c r="M399" t="s">
+        <v>22</v>
+      </c>
+      <c r="N399" t="s">
+        <v>23</v>
+      </c>
+      <c r="O399" s="1">
+        <v>46199</v>
+      </c>
+      <c r="P399" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q399" t="s">
+        <v>24</v>
+      </c>
+      <c r="R399" t="s">
+        <v>41</v>
+      </c>
+      <c r="S399" t="s">
+        <v>630</v>
+      </c>
+      <c r="T399" t="s">
+        <v>42</v>
+      </c>
+      <c r="U399" t="s">
+        <v>43</v>
+      </c>
+      <c r="V399" t="s">
+        <v>44</v>
+      </c>
+      <c r="W399" t="s">
+        <v>892</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -25283,12 +31500,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007AF750F8789DE14FB4E04CAEE69C2EC6" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fa8363fe0f9a90aa18bd49cba0a1c92f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ffd56821-1536-474c-aeb3-bbda9de7a36b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7db7e2f66cb7e500deeedabc50b2c1b2" ns2:_="">
     <xsd:import namespace="ffd56821-1536-474c-aeb3-bbda9de7a36b"/>
@@ -25426,6 +31637,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -25436,15 +31653,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48812238-E91C-41E7-80F8-1C9292A4E442}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25462,6 +31670,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
   <ds:schemaRefs>
